--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\junrelfiles\COA\COA-S.A.F.E\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Val Projects\Val Repo\COA-S.A.F.E\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1F4634-F198-47AB-B246-0ABB6D3543BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D0595A-0FA6-413A-8076-649B5BCB3916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,15 +251,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -267,15 +273,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,7 +660,7 @@
     <col min="1" max="1" width="5.796875" customWidth="1"/>
     <col min="2" max="2" width="8.796875" customWidth="1"/>
     <col min="3" max="3" width="40.796875" customWidth="1"/>
-    <col min="4" max="4" width="81.69921875" customWidth="1"/>
+    <col min="4" max="4" width="57.8984375" customWidth="1"/>
     <col min="5" max="5" width="80.796875" customWidth="1"/>
     <col min="6" max="6" width="50.796875" customWidth="1"/>
     <col min="7" max="7" width="15.796875" customWidth="1"/>
@@ -632,621 +670,758 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:10" ht="31.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3">
+    <row r="3" spans="1:10" ht="31.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="G3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.2">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="31.2">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="31.2">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="31.2">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="31.2">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="31.2">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" ht="31.2">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="31.2">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" t="s">
-        <v>14</v>
-      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="31.2">
-      <c r="A12">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="31.2">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" t="s">
-        <v>14</v>
-      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="31.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" t="s">
-        <v>14</v>
-      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="31.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" t="s">
-        <v>14</v>
-      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="31.2">
-      <c r="A16">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" t="s">
-        <v>14</v>
-      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" ht="31.2">
-      <c r="A17">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" t="s">
-        <v>14</v>
-      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" ht="31.2">
-      <c r="A18">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" t="s">
-        <v>14</v>
-      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" ht="31.2">
-      <c r="A19">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" t="s">
-        <v>14</v>
-      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10" ht="31.2">
-      <c r="A20">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G20" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" t="s">
-        <v>14</v>
-      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" ht="31.2">
-      <c r="A21">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" ht="31.2">
-      <c r="A22">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="G23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" t="s">
-        <v>14</v>
-      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" t="s">
-        <v>14</v>
-      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
+      <c r="B26" s="2">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
+      <c r="B27" s="2">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
+      <c r="B28" s="2">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
+      <c r="B29" s="2">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31">
+      <c r="B30" s="2">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" ht="31.2">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B31" s="2">
+        <v>1</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G31" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="G31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32">
-        <v>1</v>
-      </c>
-      <c r="B32">
+      <c r="A32" s="2">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2">
         <v>2</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H32" t="b">
+      <c r="H32" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 A2:B2 D2:J2 A3 D3:F3 I3:J3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 B2 D2:J2 A3 D3:F3 I3:J3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\junrelfiles\COA\COA-S.A.F.E\public\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C14197F-7C70-4B52-8249-90AC0FD1E108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="14580"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Articles" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="138">
   <si>
     <t>Day</t>
   </si>
@@ -63,13 +59,16 @@
     <t>RewardMessage</t>
   </si>
   <si>
+    <t>Survival and development of the child</t>
+  </si>
+  <si>
     <t>Learn about Article 6 (Right to life) - every child's fundamental right to survive and develop.</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://www.unicef.org/child-rights-convention/convention-text-childrens-version</t>
+    <t>/excelPDF/example.pdf</t>
   </si>
   <si>
     <t>individual</t>
@@ -78,10 +77,127 @@
     <t>FALSE</t>
   </si>
   <si>
+    <t>Responsibility of parents</t>
+  </si>
+  <si>
     <t>Explore children's right to healthcare, nutrition, and a safe environment.</t>
   </si>
   <si>
-    <t>https://www.who.int/news-room/fact-sheets/detail/children-s-environmental-health</t>
+    <t>/example.pdf</t>
+  </si>
+  <si>
+    <t>Health and medical services</t>
+  </si>
+  <si>
+    <t>Explain Article 24-26 in simple words (10-15mins), then let the child draw, repeat, or share it with the family.</t>
+  </si>
+  <si>
+    <t>Standard of living</t>
+  </si>
+  <si>
+    <t>Explain Articles 27 and 31  in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Non-discrimination</t>
+  </si>
+  <si>
+    <t>Explain Articles 2 and 11 in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Protection from abuse</t>
+  </si>
+  <si>
+    <t>Explain Articles 19 and 20 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Refugee children</t>
+  </si>
+  <si>
+    <t>Explain Articles 22 and 25 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Child labour</t>
+  </si>
+  <si>
+    <t>Explain Articles 32 and 33 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Protection from sexual exploitation</t>
+  </si>
+  <si>
+    <t>Explain Articles 34 and 35 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Protection from all other forms of exploitation</t>
+  </si>
+  <si>
+    <t>Explain Articles 36 and 37 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>War and armed conflict</t>
+  </si>
+  <si>
+    <t>Explain Articles 38 and 39 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Juvenile justice</t>
+  </si>
+  <si>
+    <t>Explain Article 40 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Respect for parental rights</t>
+  </si>
+  <si>
+    <t>Explain Articles 5 and 7 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Protection of identity</t>
+  </si>
+  <si>
+    <t>Explain Articles 8 and 10 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Adoption</t>
+  </si>
+  <si>
+    <t>Explain Articles 21 and 23 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Disabled children</t>
+  </si>
+  <si>
+    <t>Explain Articles 28 and 29 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Educational aims</t>
+  </si>
+  <si>
+    <t>Explain Article 30 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>The well-being of the child is paramount</t>
+  </si>
+  <si>
+    <t>Explain Article 3 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Freedom of opinion</t>
+  </si>
+  <si>
+    <t>Explain Articles 12 and 13 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Freedom of thought, conscience, and religion</t>
+  </si>
+  <si>
+    <t>Explain Articles 14 and 15 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+  </si>
+  <si>
+    <t>Protection of privacy</t>
+  </si>
+  <si>
+    <t>Explain Articles 16 and 17 in simple words (10–15 mins), then let the child draw, repeat, or share it with family</t>
   </si>
   <si>
     <t>REWARD DAY - Gauntlets of Safety</t>
@@ -102,176 +218,53 @@
     <t>These gloves give you the power to protect yourself, because you know what is right and fair for you.</t>
   </si>
   <si>
+    <t xml:space="preserve"> Add munggo with malunggay or kalabasa. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rich in essential nutrients</t>
+  </si>
+  <si>
     <t>test</t>
   </si>
   <si>
-    <t>family</t>
-  </si>
-  <si>
-    <t>Survival and development of the child</t>
-  </si>
-  <si>
-    <t>Responsibility of parents</t>
-  </si>
-  <si>
-    <t>Health and medical services</t>
-  </si>
-  <si>
-    <t>Standard of living</t>
-  </si>
-  <si>
-    <t>Non-discrimination</t>
-  </si>
-  <si>
-    <t>Protection from abuse</t>
-  </si>
-  <si>
-    <t>Refugee children</t>
-  </si>
-  <si>
-    <t>Child labour</t>
-  </si>
-  <si>
-    <t>Protection from sexual exploitation</t>
-  </si>
-  <si>
-    <t>Protection from all other forms of exploitation</t>
-  </si>
-  <si>
-    <t>War and armed conflict</t>
-  </si>
-  <si>
-    <t>Juvenile justice</t>
-  </si>
-  <si>
-    <t>Respect for parental rights</t>
-  </si>
-  <si>
-    <t>Protection of identity</t>
-  </si>
-  <si>
-    <t>Adoption</t>
-  </si>
-  <si>
-    <t>Disabled children</t>
-  </si>
-  <si>
-    <t>Educational aims</t>
-  </si>
-  <si>
-    <t>The well-being of the child is paramount</t>
-  </si>
-  <si>
-    <t>Freedom of opinion</t>
-  </si>
-  <si>
-    <t>Freedom of thought, conscience, and religion</t>
-  </si>
-  <si>
-    <t>Protection of privacy</t>
-  </si>
-  <si>
-    <t>Explain Article 24-26 in simple words (10-15mins), then let the child draw, repeat, or share it with the family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 27 and 31  in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 2 and 11 in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 19 and 20 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 22 and 25 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 32 and 33 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 34 and 35 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 36 and 37 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 38 and 39 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Article 40 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 5 and 7 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 8 and 10 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 21 and 23 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 28 and 29 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Article 30 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Article 3 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 12 and 13 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 14 and 15 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
-  </si>
-  <si>
-    <t>Explain Articles 16 and 17 in simple words (10–15 mins), then let the child draw, repeat, or share it with family</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Add munggo with malunggay or kalabasa. </t>
-  </si>
-  <si>
-    <t>Add malunggay leaves to tinola, munggo,or intant noodles.</t>
+    <t>Add malunggay leaves to tinola, munggo,or instant noodles.</t>
+  </si>
+  <si>
+    <t>Rich in antioxidants</t>
   </si>
   <si>
     <t>Add boiled egg (split in half if budget is tight)</t>
   </si>
   <si>
+    <t>Contains protein</t>
+  </si>
+  <si>
     <t>Add banana (saging na saba or lakatan) for dessert or merienda</t>
   </si>
   <si>
+    <t>Rich in fiber and potassium</t>
+  </si>
+  <si>
     <t>Add dilis (small dried fish) with egg fried rice.</t>
   </si>
   <si>
+    <t>Rich in calcium</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Add kamote (sweet potato) boiled or fried. </t>
   </si>
   <si>
+    <t>Contains carbs</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Add gabi/taro or squash to a simple sabaw </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Rich in essential nutrients</t>
-  </si>
-  <si>
-    <t>Rich in antioxidants</t>
-  </si>
-  <si>
-    <t>Add malunggay leaves to tinola, munggo,or instant noodles.</t>
-  </si>
-  <si>
-    <t>Contains protein</t>
-  </si>
-  <si>
-    <t>Rich in fiber and potassium</t>
-  </si>
-  <si>
-    <t>Rich in calcium</t>
-  </si>
-  <si>
-    <t>Contains carbs</t>
   </si>
   <si>
     <t xml:space="preserve"> Contains Vitamin C
  and E</t>
+  </si>
+  <si>
+    <t>Add malunggay leaves to tinola, munggo,or intant noodles.</t>
   </si>
   <si>
     <t xml:space="preserve"> Contains Vitamin C and E</t>
@@ -284,6 +277,9 @@
  week)</t>
   </si>
   <si>
+    <t>family</t>
+  </si>
+  <si>
     <t>Take a  Family Meal Photo
  (or, if without camera,
  have  third/final member to share
@@ -310,42 +306,42 @@
     <t>Pick their favorite work from the week (coloring, writing, etc.) and show it. Give a high-five and say, “You worked hard this week, amazing job!”</t>
   </si>
   <si>
+    <t>Family Praise</t>
+  </si>
+  <si>
     <t>Have your child show one coloring page from DICE. The parent will then say “Wow, you made it so colorful! Good job!”</t>
   </si>
   <si>
+    <t>Coloring Pride</t>
+  </si>
+  <si>
     <t>Have your child read at least three words from a book. Repeat the words together with your child and give them a thumbs-up.</t>
   </si>
   <si>
+    <t>Reading Together</t>
+  </si>
+  <si>
     <t>Let your child write a name or a letter on a paper. Trace it, and smile to show appreciation to your child’s work.</t>
   </si>
   <si>
+    <t>Writing Practice</t>
+  </si>
+  <si>
     <t>Count 5 things at home (spoons, buttons, coins, or their fingers) with your child and clap when the child finishes.</t>
   </si>
   <si>
+    <t>Counting Fun</t>
+  </si>
+  <si>
     <t>Let you child share one thing they learned or did at DICE today. Just listen and respons with, “Wow, I’m proud of you”</t>
   </si>
   <si>
+    <t xml:space="preserve"> Story Telling</t>
+  </si>
+  <si>
     <t>Have your child draw one simple thing (house, sun, flower, or stick figure) Guess what it is, then say, “That’s a nice drawing!”</t>
   </si>
   <si>
-    <t>Family Praise</t>
-  </si>
-  <si>
-    <t>Coloring Pride</t>
-  </si>
-  <si>
-    <t>Reading Together</t>
-  </si>
-  <si>
-    <t>Writing Practice</t>
-  </si>
-  <si>
-    <t>Counting Fun</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Story Telling</t>
-  </si>
-  <si>
     <t>Drawing Day</t>
   </si>
   <si>
@@ -362,13 +358,163 @@
   </si>
   <si>
     <t>Awarding</t>
+  </si>
+  <si>
+    <t>Smart Screen Tracker</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 2 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 3 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 4 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 5 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 6 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 7 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 8 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 9 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 10 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 11 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 12 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 13 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 14 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 15 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 16 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 17 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 18 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 19 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 20 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 21 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>where each day, parents limit screen time on her family (e.g., only 22 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t>Tech-Free Bonding Time</t>
+  </si>
+  <si>
+    <t>For 3 days, parents will implement tech-free bonding time with their children. Each day, they will do one simple offline activity together such as:</t>
+  </si>
+  <si>
+    <r>
+      <t>■ </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Karaoke or singing together</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>■ </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Talking time or family storytelling</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>■ </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Playing board games or traditional games</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>■ </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Doing household chores as a team</t>
+    </r>
+  </si>
+  <si>
+    <t>SmartUseofGadgetsChallenge</t>
+  </si>
+  <si>
+    <t>○parents will take a picture of their family during the offline activity (from the individual/family challenges). Post the photo on Facebook with 1 tip about safe internet use they learned from the digital literacy seminar (example: “Remind kids not to talk to strangers online” or “Set limits for gadget use”). Use hashtag #SmartUseofGadgetsChallenge.</t>
+  </si>
+  <si>
+    <t>○parents will take a picture of their family during the offline activity (from the individual/family challenges). Post the photo on Facebook with 2 tip about safe internet use they learned from the digital literacy seminar (example: “Remind kids not to talk to strangers online” or “Set limits for gadget use”). Use hashtag #SmartUseofGadgetsChallenge.</t>
+  </si>
+  <si>
+    <t>○parents will take a picture of their family during the offline activity (from the individual/family challenges). Post the photo on Facebook with 3 tip about safe internet use they learned from the digital literacy seminar (example: “Remind kids not to talk to strangers online” or “Set limits for gadget use”). Use hashtag #SmartUseofGadgetsChallenge.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -377,22 +523,365 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFCC0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -400,28 +889,317 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -743,25 +1521,25 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J121"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="5.796875" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" customWidth="1"/>
-    <col min="3" max="3" width="40.796875" customWidth="1"/>
-    <col min="4" max="4" width="81.69921875" customWidth="1"/>
-    <col min="5" max="5" width="80.796875" customWidth="1"/>
-    <col min="6" max="6" width="50.796875" customWidth="1"/>
-    <col min="7" max="7" width="15.796875" customWidth="1"/>
-    <col min="8" max="8" width="12.796875" customWidth="1"/>
-    <col min="9" max="9" width="30.796875" customWidth="1"/>
-    <col min="10" max="10" width="50.796875" customWidth="1"/>
+    <col min="1" max="1" width="5.79411764705882" customWidth="1"/>
+    <col min="2" max="2" width="8.79411764705882" customWidth="1"/>
+    <col min="3" max="3" width="40.7941176470588" customWidth="1"/>
+    <col min="4" max="4" width="81.6985294117647" customWidth="1"/>
+    <col min="5" max="5" width="80.7941176470588" customWidth="1"/>
+    <col min="6" max="6" width="50.7941176470588" customWidth="1"/>
+    <col min="7" max="7" width="15.7941176470588" customWidth="1"/>
+    <col min="8" max="8" width="12.7941176470588" customWidth="1"/>
+    <col min="9" max="9" width="30.7941176470588" customWidth="1"/>
+    <col min="10" max="10" width="50.7941176470588" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -804,28 +1582,28 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
-      </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -836,31 +1614,31 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
       <c r="I3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="31.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="36" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -868,19 +1646,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" ht="36" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -888,19 +1669,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="36" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -908,19 +1689,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="36" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -928,19 +1709,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="36" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -948,19 +1729,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -968,19 +1749,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" ht="36" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -988,19 +1769,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" ht="36" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1008,19 +1789,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" ht="36" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1031,16 +1812,16 @@
         <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1048,19 +1829,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="36" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1068,19 +1849,19 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="36" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1088,19 +1869,19 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" ht="36" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1108,19 +1889,19 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="36" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1128,19 +1909,19 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1148,19 +1929,19 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1168,19 +1949,19 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" ht="36" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1188,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" ht="36" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1208,19 +1989,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="31.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" ht="36" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1228,19 +2009,19 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1249,13 +2030,13 @@
       </c>
       <c r="C23" s="1"/>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1263,13 +2044,13 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1277,7 +2058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1285,7 +2066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1293,7 +2074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1301,7 +2082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1309,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1325,31 +2106,31 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="J31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" ht="18" spans="1:8">
       <c r="A32">
         <v>1</v>
       </c>
@@ -1357,25 +2138,25 @@
         <v>2</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" t="s">
         <v>65</v>
       </c>
-      <c r="D32" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" t="s">
-        <v>23</v>
-      </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="G32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="31.2">
+    <row r="33" ht="36" spans="1:8">
       <c r="A33">
         <v>2</v>
       </c>
@@ -1383,13 +2164,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -1403,13 +2184,13 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -1423,13 +2204,13 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -1443,13 +2224,13 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
@@ -1463,19 +2244,19 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="31.2">
+    <row r="38" ht="36" spans="1:8">
       <c r="A38">
         <v>7</v>
       </c>
@@ -1483,13 +2264,13 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
@@ -1503,13 +2284,13 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D39" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
@@ -1523,13 +2304,13 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
@@ -1543,13 +2324,13 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
@@ -1563,13 +2344,13 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -1583,13 +2364,13 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D43" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
@@ -1603,19 +2384,19 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D44" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="31.2">
+    <row r="45" ht="36" spans="1:8">
       <c r="A45">
         <v>14</v>
       </c>
@@ -1623,13 +2404,13 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
@@ -1643,13 +2424,13 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D46" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
@@ -1663,13 +2444,13 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D47" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
@@ -1683,19 +2464,19 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D48" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H48" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>18</v>
       </c>
@@ -1703,19 +2484,19 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D49" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H49" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>19</v>
       </c>
@@ -1723,19 +2504,19 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>20</v>
       </c>
@@ -1743,19 +2524,19 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>21</v>
       </c>
@@ -1763,19 +2544,19 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="78">
+    <row r="53" ht="88" spans="1:8">
       <c r="A53">
         <v>22</v>
       </c>
@@ -1783,16 +2564,16 @@
         <v>2</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s">
         <v>81</v>
       </c>
-      <c r="G53" t="s">
-        <v>24</v>
-      </c>
       <c r="H53" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="78">
+    <row r="54" ht="88" spans="1:8">
       <c r="A54">
         <v>23</v>
       </c>
@@ -1800,16 +2581,16 @@
         <v>2</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s">
         <v>81</v>
       </c>
-      <c r="G54" t="s">
-        <v>24</v>
-      </c>
       <c r="H54" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="78">
+    <row r="55" ht="88" spans="1:8">
       <c r="A55">
         <v>24</v>
       </c>
@@ -1820,13 +2601,13 @@
         <v>82</v>
       </c>
       <c r="G55" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="78">
+    <row r="56" ht="88" spans="1:8">
       <c r="A56">
         <v>25</v>
       </c>
@@ -1843,7 +2624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="78">
+    <row r="57" ht="88" spans="1:8">
       <c r="A57">
         <v>26</v>
       </c>
@@ -1860,7 +2641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="78">
+    <row r="58" ht="88" spans="1:8">
       <c r="A58">
         <v>27</v>
       </c>
@@ -1877,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>28</v>
       </c>
@@ -1888,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>29</v>
       </c>
@@ -1896,13 +2677,13 @@
         <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" ht="18" spans="1:10">
       <c r="A61">
         <v>30</v>
       </c>
@@ -1916,19 +2697,19 @@
         <v>86</v>
       </c>
       <c r="G61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="J61" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>1</v>
       </c>
@@ -1939,16 +2720,16 @@
         <v>87</v>
       </c>
       <c r="E62" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H62" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>2</v>
       </c>
@@ -1956,19 +2737,19 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E63" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H63" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>3</v>
       </c>
@@ -1976,13 +2757,13 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E64" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G64" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H64" t="b">
         <v>0</v>
@@ -1996,13 +2777,13 @@
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E65" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
@@ -2016,13 +2797,13 @@
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
@@ -2036,13 +2817,13 @@
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G67" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
@@ -2056,13 +2837,13 @@
         <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E68" t="s">
         <v>100</v>
       </c>
       <c r="G68" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H68" t="b">
         <v>0</v>
@@ -2079,10 +2860,10 @@
         <v>87</v>
       </c>
       <c r="E69" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G69" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H69" t="b">
         <v>0</v>
@@ -2096,13 +2877,13 @@
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E70" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H70" t="b">
         <v>0</v>
@@ -2116,13 +2897,13 @@
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E71" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G71" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
@@ -2136,13 +2917,13 @@
         <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G72" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
@@ -2156,13 +2937,13 @@
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E73" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G73" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
@@ -2176,13 +2957,13 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G74" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
@@ -2196,13 +2977,13 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E75" t="s">
         <v>100</v>
       </c>
       <c r="G75" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
@@ -2219,10 +3000,10 @@
         <v>87</v>
       </c>
       <c r="E76" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
@@ -2236,13 +3017,13 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E77" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G77" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
@@ -2256,13 +3037,13 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E78" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G78" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
@@ -2276,13 +3057,13 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E79" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G79" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
@@ -2296,19 +3077,19 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G80" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:8">
       <c r="A81">
         <v>20</v>
       </c>
@@ -2316,19 +3097,19 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G81" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:8">
       <c r="A82">
         <v>21</v>
       </c>
@@ -2336,19 +3117,19 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E82" t="s">
         <v>100</v>
       </c>
       <c r="G82" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H82" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:8">
       <c r="A83">
         <v>22</v>
       </c>
@@ -2359,13 +3140,13 @@
         <v>101</v>
       </c>
       <c r="G83" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H83" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:8">
       <c r="A84">
         <v>23</v>
       </c>
@@ -2376,13 +3157,13 @@
         <v>101</v>
       </c>
       <c r="G84" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H84" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:8">
       <c r="A85">
         <v>24</v>
       </c>
@@ -2393,13 +3174,13 @@
         <v>101</v>
       </c>
       <c r="G85" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H85" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:8">
       <c r="A86">
         <v>25</v>
       </c>
@@ -2410,13 +3191,13 @@
         <v>101</v>
       </c>
       <c r="G86" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:8">
       <c r="A87">
         <v>26</v>
       </c>
@@ -2427,13 +3208,13 @@
         <v>101</v>
       </c>
       <c r="G87" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H87" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:8">
       <c r="A88">
         <v>27</v>
       </c>
@@ -2450,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:8">
       <c r="A89">
         <v>28</v>
       </c>
@@ -2467,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:8">
       <c r="A90">
         <v>29</v>
       </c>
@@ -2501,23 +3282,442 @@
         <v>105</v>
       </c>
       <c r="G91" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
       </c>
       <c r="I91" t="s">
+        <v>61</v>
+      </c>
+      <c r="J91" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92">
+        <v>1</v>
+      </c>
+      <c r="B92">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>106</v>
+      </c>
+      <c r="D92" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93">
+        <v>2</v>
+      </c>
+      <c r="B93">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>106</v>
+      </c>
+      <c r="D93" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94">
+        <v>3</v>
+      </c>
+      <c r="B94">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>106</v>
+      </c>
+      <c r="D94" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95">
+        <v>4</v>
+      </c>
+      <c r="B95">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>106</v>
+      </c>
+      <c r="D95" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96">
+        <v>5</v>
+      </c>
+      <c r="B96">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>106</v>
+      </c>
+      <c r="D96" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97">
+        <v>6</v>
+      </c>
+      <c r="B97">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98">
+        <v>7</v>
+      </c>
+      <c r="B98">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>106</v>
+      </c>
+      <c r="D98" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99">
+        <v>8</v>
+      </c>
+      <c r="B99">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>106</v>
+      </c>
+      <c r="D99" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100">
+        <v>9</v>
+      </c>
+      <c r="B100">
+        <v>4</v>
+      </c>
+      <c r="C100" t="s">
+        <v>106</v>
+      </c>
+      <c r="D100" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101">
+        <v>10</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>106</v>
+      </c>
+      <c r="D101" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102">
+        <v>11</v>
+      </c>
+      <c r="B102">
+        <v>4</v>
+      </c>
+      <c r="C102" t="s">
+        <v>106</v>
+      </c>
+      <c r="D102" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103">
+        <v>12</v>
+      </c>
+      <c r="B103">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>106</v>
+      </c>
+      <c r="D103" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104">
+        <v>13</v>
+      </c>
+      <c r="B104">
+        <v>4</v>
+      </c>
+      <c r="C104" t="s">
+        <v>106</v>
+      </c>
+      <c r="D104" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105">
+        <v>14</v>
+      </c>
+      <c r="B105">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>106</v>
+      </c>
+      <c r="D105" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106">
+        <v>15</v>
+      </c>
+      <c r="B106">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>106</v>
+      </c>
+      <c r="D106" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107">
+        <v>16</v>
+      </c>
+      <c r="B107">
+        <v>4</v>
+      </c>
+      <c r="C107" t="s">
+        <v>106</v>
+      </c>
+      <c r="D107" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108">
+        <v>17</v>
+      </c>
+      <c r="B108">
+        <v>4</v>
+      </c>
+      <c r="C108" t="s">
+        <v>106</v>
+      </c>
+      <c r="D108" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109">
+        <v>18</v>
+      </c>
+      <c r="B109">
+        <v>4</v>
+      </c>
+      <c r="C109" t="s">
+        <v>106</v>
+      </c>
+      <c r="D109" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110">
+        <v>19</v>
+      </c>
+      <c r="B110">
+        <v>4</v>
+      </c>
+      <c r="C110" t="s">
+        <v>106</v>
+      </c>
+      <c r="D110" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111">
+        <v>20</v>
+      </c>
+      <c r="B111">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>106</v>
+      </c>
+      <c r="D111" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112">
         <v>21</v>
       </c>
-      <c r="J91" t="s">
+      <c r="B112">
+        <v>4</v>
+      </c>
+      <c r="C112" t="s">
+        <v>106</v>
+      </c>
+      <c r="D112" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113">
         <v>22</v>
+      </c>
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
+        <v>128</v>
+      </c>
+      <c r="D113" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114">
+        <v>23</v>
+      </c>
+      <c r="B114">
+        <v>4</v>
+      </c>
+      <c r="C114" t="s">
+        <v>128</v>
+      </c>
+      <c r="D114"/>
+      <c r="E114" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115">
+        <v>24</v>
+      </c>
+      <c r="B115">
+        <v>4</v>
+      </c>
+      <c r="C115" t="s">
+        <v>128</v>
+      </c>
+      <c r="D115"/>
+      <c r="E115" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116">
+        <v>25</v>
+      </c>
+      <c r="B116">
+        <v>4</v>
+      </c>
+      <c r="C116" t="s">
+        <v>128</v>
+      </c>
+      <c r="D116"/>
+      <c r="E116" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>26</v>
+      </c>
+      <c r="B117">
+        <v>4</v>
+      </c>
+      <c r="C117" t="s">
+        <v>128</v>
+      </c>
+      <c r="D117"/>
+      <c r="E117" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118">
+        <v>27</v>
+      </c>
+      <c r="B118">
+        <v>4</v>
+      </c>
+      <c r="C118" t="s">
+        <v>134</v>
+      </c>
+      <c r="D118" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119">
+        <v>28</v>
+      </c>
+      <c r="B119">
+        <v>4</v>
+      </c>
+      <c r="C119" t="s">
+        <v>134</v>
+      </c>
+      <c r="D119" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120">
+        <v>29</v>
+      </c>
+      <c r="B120">
+        <v>4</v>
+      </c>
+      <c r="C120" t="s">
+        <v>134</v>
+      </c>
+      <c r="D120" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>30</v>
+      </c>
+      <c r="B121">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 A2:B2 D2:J2 A3 D3:F3 I3:J3" numberStoredAsText="1"/>
+    <ignoredError sqref="I3:J3 D2:E3 A3 G2:J2 A2:B2 A1:J1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548BD500-791C-48B0-A15D-BECE6DBB8CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="14580"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Articles" sheetId="1" r:id="rId1"/>
@@ -18,16 +24,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="184">
   <si>
     <t>Day</t>
   </si>
@@ -63,9 +70,6 @@
   </si>
   <si>
     <t>Learn about Article 6 (Right to life) - every child's fundamental right to survive and develop.</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>/excelPDF/example.pdf</t>
@@ -411,7 +415,7 @@
     <t>where each day, parents limit screen time on her family (e.g., only 17 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
   </si>
   <si>
-    <t>where each day, parents limit screen time on her family (e.g., only 18 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+    <t>By the end of the day, let your child identify what they’re feeling based on the feelings wheel.</t>
   </si>
   <si>
     <t>where each day, parents limit screen time on her family (e.g., only 19 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
@@ -433,6 +437,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>■ </t>
     </r>
     <r>
@@ -448,6 +458,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>■ </t>
     </r>
     <r>
@@ -463,6 +479,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>■ </t>
     </r>
     <r>
@@ -478,6 +500,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCC0000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>■ </t>
     </r>
     <r>
@@ -503,24 +531,310 @@
   <si>
     <t>○parents will take a picture of their family during the offline activity (from the individual/family challenges). Post the photo on Facebook with 3 tip about safe internet use they learned from the digital literacy seminar (example: “Remind kids not to talk to strangers online” or “Set limits for gadget use”). Use hashtag #SmartUseofGadgetsChallenge.</t>
   </si>
+  <si>
+    <t>Smart Saving</t>
+  </si>
+  <si>
+    <t>Prepare a savings jar with the money tracker. Drop a money every day and mark check on the tracker.</t>
+  </si>
+  <si>
+    <t>#NoGambling</t>
+  </si>
+  <si>
+    <t>Each family members contributes a small coin (₱5-20) to the savings jar.</t>
+  </si>
+  <si>
+    <t>#SavingsNotGambling</t>
+  </si>
+  <si>
+    <t>Post a picture of your savings jar/box with the caption: “I choose saving over gambling. #SavingsNotGambling”</t>
+  </si>
+  <si>
+    <t>Positive Me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The parents and the kids will write one positive phrase about themselves. </t>
+  </si>
+  <si>
+    <t>Family Advice Corner</t>
+  </si>
+  <si>
+    <t>Share one piece of advice to child about focusing on studies before having a family. Children should write it down in a journal.</t>
+  </si>
+  <si>
+    <t>#LessonFromHome</t>
+  </si>
+  <si>
+    <t>Parents will post on social media with a lesson they should share to other parents about preventing early pregnancy with the hashtag.</t>
+  </si>
+  <si>
+    <t>Educational Screen Time</t>
+  </si>
+  <si>
+    <t>Each day, parents and children take time to watch a YouTube video about children's rights.</t>
+  </si>
+  <si>
+    <t>Good touch, Bad touch</t>
+  </si>
+  <si>
+    <t>Before bedtime, teach the children that it is not okay when the buttocks is touched by another person. Teach them to say NO and to tell a teacher, a parent, or a trusted adult immediately.</t>
+  </si>
+  <si>
+    <t>#TouchTellsStories</t>
+  </si>
+  <si>
+    <t>The child draw a kid on a piece of paper, dress it up, and color. Let them mark Xs on areas where bad touch may happen.</t>
+  </si>
+  <si>
+    <t>One Day, one question</t>
+  </si>
+  <si>
+    <t>Kind Words Only</t>
+  </si>
+  <si>
+    <t>All family members must speak and appropriately incorporate the magic words at all times.</t>
+  </si>
+  <si>
+    <t>#KidsAndKindness</t>
+  </si>
+  <si>
+    <t>The parents must make a short reel where their child shares how they can protect others from getting bullied.</t>
+  </si>
+  <si>
+    <t>Tap, Tap, Tap</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">When feeling intense emotions, find an isolated spot, take 3 deep breaths and tap thrice on the chest.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Repeat 5 times.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">What We Feel, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>We Wheel Share</t>
+    </r>
+  </si>
+  <si>
+    <t>Family member each identify what they are feeling based on the feeling wheel and they share calmly what made them feel that way.</t>
+  </si>
+  <si>
+    <t>#BlessingsNotBurden</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Complete the statement “It is wrong to hit my child because _____” and post it on social media.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Use the hashtag.</t>
+    </r>
+  </si>
+  <si>
+    <t>Eco-Swap</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Find an eco-friendly alternative or sustainable material for items that you frequently use. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>ex.: bring your own plate when buying from a karenderya</t>
+    </r>
+  </si>
+  <si>
+    <t>Declutter=Destress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each member of the family will look for 2 things at home to discard permanently. </t>
+  </si>
+  <si>
+    <t>#ReuseRecreate</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">The family must work together to repurpose something old. Cut, paint, or color it. Take a picture and share it online. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Use the hashtag.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Small Task,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Great Responsibility</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Assign small decision-making tasks to children.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>example: let child plan go-grow-glow meals for the week</t>
+    </r>
+  </si>
+  <si>
+    <t>Their Next Chapter</t>
+  </si>
+  <si>
+    <t>Parents will read a story or watch a video about the negative effects of addiction. The child share what they learned thereafter.</t>
+  </si>
+  <si>
+    <t>#TrustInSmallHands</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Parents post a picture taken during the individual challenge with a brief description of what they learned. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Use the hashtag.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tech-Free Night</t>
+  </si>
+  <si>
+    <t>Two hours before bedtime is tech-free time. Let children share what their favorite online activity is.</t>
+  </si>
+  <si>
+    <t>Make Your Move</t>
+  </si>
+  <si>
+    <t>Parents will create scenarios of online risk, let children answer what they would do, then discuss if it is the right thing to do.</t>
+  </si>
+  <si>
+    <t>#ProtectOurSpace</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Parents and children will make a drawing on online safety. Take a photo and post it online.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Use the hashtag.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -529,359 +843,34 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FFCC0000"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -889,317 +878,103 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1210,10 +985,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1251,295 +1026,149 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J121"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J366"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="5.79411764705882" customWidth="1"/>
-    <col min="2" max="2" width="8.79411764705882" customWidth="1"/>
-    <col min="3" max="3" width="40.7941176470588" customWidth="1"/>
-    <col min="4" max="4" width="81.6985294117647" customWidth="1"/>
-    <col min="5" max="5" width="80.7941176470588" customWidth="1"/>
-    <col min="6" max="6" width="50.7941176470588" customWidth="1"/>
-    <col min="7" max="7" width="15.7941176470588" customWidth="1"/>
-    <col min="8" max="8" width="12.7941176470588" customWidth="1"/>
-    <col min="9" max="9" width="30.7941176470588" customWidth="1"/>
-    <col min="10" max="10" width="50.7941176470588" customWidth="1"/>
+    <col min="1" max="1" width="5.796875" customWidth="1"/>
+    <col min="2" max="2" width="8.796875" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="4" max="4" width="97.8984375" customWidth="1"/>
+    <col min="5" max="5" width="80.796875" customWidth="1"/>
+    <col min="6" max="6" width="50.796875" customWidth="1"/>
+    <col min="7" max="7" width="15.796875" customWidth="1"/>
+    <col min="8" max="8" width="12.796875" customWidth="1"/>
+    <col min="9" max="9" width="30.796875" customWidth="1"/>
+    <col min="10" max="10" width="50.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1587,23 +1216,14 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1613,430 +1233,420 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
       <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:8">
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="36" spans="1:8">
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" ht="36" spans="1:8">
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" ht="36" spans="1:8">
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" ht="36" spans="1:8">
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
       <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="36" spans="1:8">
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
         <v>14</v>
       </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" ht="36" spans="1:8">
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
         <v>14</v>
       </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" ht="36" spans="1:8">
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" t="s">
         <v>14</v>
       </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" t="s">
-        <v>38</v>
-      </c>
       <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
         <v>14</v>
       </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" ht="36" spans="1:8">
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
         <v>14</v>
       </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" ht="36" spans="1:8">
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
         <v>14</v>
       </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" ht="36" spans="1:8">
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
         <v>14</v>
       </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" ht="36" spans="1:8">
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
         <v>14</v>
       </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" ht="18" spans="1:8">
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
         <v>14</v>
       </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" ht="18" spans="1:8">
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
         <v>14</v>
       </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" ht="36" spans="1:8">
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
         <v>14</v>
       </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" ht="36" spans="1:8">
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
         <v>14</v>
       </c>
-      <c r="H21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" ht="36" spans="1:8">
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
         <v>14</v>
       </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" s="1"/>
       <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
         <v>14</v>
       </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2044,13 +1654,13 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
         <v>14</v>
       </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2058,7 +1668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2066,7 +1676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2074,7 +1684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2082,7 +1692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2090,7 +1700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2106,73 +1716,72 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" t="s">
         <v>57</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>58</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
         <v>59</v>
       </c>
-      <c r="F31" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>60</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>61</v>
       </c>
-      <c r="J31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" ht="18" spans="1:8">
+    </row>
+    <row r="32" spans="1:10" ht="31.2">
       <c r="A32">
         <v>1</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" t="s">
         <v>63</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>64</v>
       </c>
-      <c r="E32" t="s">
-        <v>65</v>
-      </c>
       <c r="F32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="36" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="31.2">
       <c r="A33">
         <v>2</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" t="s">
         <v>66</v>
       </c>
-      <c r="D33" t="s">
-        <v>67</v>
-      </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H33" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2184,15 +1793,16 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" t="s">
         <v>68</v>
       </c>
-      <c r="D34" t="s">
-        <v>69</v>
-      </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H34" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2204,15 +1814,16 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
         <v>70</v>
       </c>
-      <c r="D35" t="s">
-        <v>71</v>
-      </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2224,15 +1835,16 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" t="s">
         <v>72</v>
       </c>
-      <c r="D36" t="s">
-        <v>73</v>
-      </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H36" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2244,19 +1856,20 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" t="s">
         <v>74</v>
       </c>
-      <c r="D37" t="s">
-        <v>75</v>
-      </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="36" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="31.2">
       <c r="A38">
         <v>7</v>
       </c>
@@ -2264,15 +1877,16 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H38" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2284,15 +1898,16 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" t="s">
         <v>63</v>
       </c>
-      <c r="D39" t="s">
-        <v>64</v>
-      </c>
       <c r="G39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H39" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2304,15 +1919,16 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2324,15 +1940,16 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" t="s">
         <v>68</v>
       </c>
-      <c r="D41" t="s">
-        <v>69</v>
-      </c>
       <c r="G41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H41" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2344,15 +1961,16 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" t="s">
         <v>70</v>
       </c>
-      <c r="D42" t="s">
-        <v>71</v>
-      </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H42" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2364,15 +1982,16 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" t="s">
         <v>72</v>
       </c>
-      <c r="D43" t="s">
-        <v>73</v>
-      </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H43" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2384,19 +2003,20 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
+        <v>73</v>
+      </c>
+      <c r="D44" t="s">
         <v>74</v>
       </c>
-      <c r="D44" t="s">
-        <v>75</v>
-      </c>
       <c r="G44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="36" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="31.2">
       <c r="A45">
         <v>14</v>
       </c>
@@ -2404,15 +2024,16 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
+        <v>75</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="G45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H45" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2424,15 +2045,16 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46" t="s">
         <v>63</v>
       </c>
-      <c r="D46" t="s">
-        <v>64</v>
-      </c>
       <c r="G46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H46" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2444,15 +2066,16 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H47" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2464,19 +2087,20 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
+        <v>67</v>
+      </c>
+      <c r="D48" t="s">
         <v>68</v>
       </c>
-      <c r="D48" t="s">
-        <v>69</v>
-      </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49">
         <v>18</v>
       </c>
@@ -2484,19 +2108,20 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" t="s">
         <v>70</v>
       </c>
-      <c r="D49" t="s">
-        <v>71</v>
-      </c>
       <c r="G49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50">
         <v>19</v>
       </c>
@@ -2504,19 +2129,20 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" t="s">
         <v>72</v>
       </c>
-      <c r="D50" t="s">
-        <v>73</v>
-      </c>
       <c r="G50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51">
         <v>20</v>
       </c>
@@ -2524,19 +2150,20 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" t="s">
         <v>74</v>
       </c>
-      <c r="D51" t="s">
-        <v>75</v>
-      </c>
       <c r="G51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52">
         <v>21</v>
       </c>
@@ -2544,121 +2171,128 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="88" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="78">
       <c r="A53">
         <v>22</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G53" t="s">
         <v>80</v>
       </c>
-      <c r="G53" t="s">
-        <v>81</v>
-      </c>
       <c r="H53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="88" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="78">
       <c r="A54">
         <v>23</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G54" t="s">
         <v>80</v>
       </c>
-      <c r="G54" t="s">
-        <v>81</v>
-      </c>
       <c r="H54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="88" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="78">
       <c r="A55">
         <v>24</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>82</v>
+      <c r="C55" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="G55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="88" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="78">
       <c r="A56">
         <v>25</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" t="s">
         <v>83</v>
       </c>
-      <c r="G56" t="s">
-        <v>84</v>
-      </c>
       <c r="H56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="88" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="78">
       <c r="A57">
         <v>26</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G57" t="s">
         <v>83</v>
       </c>
-      <c r="G57" t="s">
-        <v>84</v>
-      </c>
       <c r="H57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="88" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="78">
       <c r="A58">
         <v>27</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" t="s">
         <v>83</v>
       </c>
-      <c r="G58" t="s">
-        <v>84</v>
-      </c>
       <c r="H58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59">
         <v>28</v>
       </c>
@@ -2666,10 +2300,11 @@
         <v>2</v>
       </c>
       <c r="H59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60">
         <v>29</v>
       </c>
@@ -2677,39 +2312,41 @@
         <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="18" spans="1:10">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>30</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" t="s">
         <v>85</v>
       </c>
-      <c r="D61" t="s">
-        <v>86</v>
-      </c>
       <c r="G61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H61" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I61" t="s">
+        <v>60</v>
+      </c>
+      <c r="J61" t="s">
         <v>61</v>
       </c>
-      <c r="J61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62">
         <v>1</v>
       </c>
@@ -2717,19 +2354,20 @@
         <v>3</v>
       </c>
       <c r="C62" t="s">
+        <v>86</v>
+      </c>
+      <c r="E62" t="s">
         <v>87</v>
       </c>
-      <c r="E62" t="s">
-        <v>88</v>
-      </c>
       <c r="G62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>2</v>
       </c>
@@ -2737,19 +2375,20 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
+        <v>88</v>
+      </c>
+      <c r="E63" t="s">
         <v>89</v>
       </c>
-      <c r="E63" t="s">
-        <v>90</v>
-      </c>
       <c r="G63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>3</v>
       </c>
@@ -2757,15 +2396,16 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" t="s">
         <v>91</v>
       </c>
-      <c r="E64" t="s">
-        <v>92</v>
-      </c>
       <c r="G64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H64" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2777,15 +2417,16 @@
         <v>3</v>
       </c>
       <c r="C65" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" t="s">
         <v>93</v>
       </c>
-      <c r="E65" t="s">
-        <v>94</v>
-      </c>
       <c r="G65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H65" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2797,15 +2438,16 @@
         <v>3</v>
       </c>
       <c r="C66" t="s">
+        <v>94</v>
+      </c>
+      <c r="E66" t="s">
         <v>95</v>
       </c>
-      <c r="E66" t="s">
-        <v>96</v>
-      </c>
       <c r="G66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H66" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2817,15 +2459,16 @@
         <v>3</v>
       </c>
       <c r="C67" t="s">
+        <v>96</v>
+      </c>
+      <c r="E67" t="s">
         <v>97</v>
       </c>
-      <c r="E67" t="s">
-        <v>98</v>
-      </c>
       <c r="G67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H67" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2837,15 +2480,16 @@
         <v>3</v>
       </c>
       <c r="C68" t="s">
+        <v>98</v>
+      </c>
+      <c r="E68" t="s">
         <v>99</v>
       </c>
-      <c r="E68" t="s">
-        <v>100</v>
-      </c>
       <c r="G68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H68" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2857,15 +2501,16 @@
         <v>3</v>
       </c>
       <c r="C69" t="s">
+        <v>86</v>
+      </c>
+      <c r="E69" t="s">
         <v>87</v>
       </c>
-      <c r="E69" t="s">
-        <v>88</v>
-      </c>
       <c r="G69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H69" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2877,15 +2522,16 @@
         <v>3</v>
       </c>
       <c r="C70" t="s">
+        <v>88</v>
+      </c>
+      <c r="E70" t="s">
         <v>89</v>
       </c>
-      <c r="E70" t="s">
-        <v>90</v>
-      </c>
       <c r="G70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H70" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2897,15 +2543,16 @@
         <v>3</v>
       </c>
       <c r="C71" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71" t="s">
         <v>91</v>
       </c>
-      <c r="E71" t="s">
-        <v>92</v>
-      </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H71" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2917,15 +2564,16 @@
         <v>3</v>
       </c>
       <c r="C72" t="s">
+        <v>92</v>
+      </c>
+      <c r="E72" t="s">
         <v>93</v>
       </c>
-      <c r="E72" t="s">
-        <v>94</v>
-      </c>
       <c r="G72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H72" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2937,15 +2585,16 @@
         <v>3</v>
       </c>
       <c r="C73" t="s">
+        <v>94</v>
+      </c>
+      <c r="E73" t="s">
         <v>95</v>
       </c>
-      <c r="E73" t="s">
-        <v>96</v>
-      </c>
       <c r="G73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H73" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2957,15 +2606,16 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
+        <v>96</v>
+      </c>
+      <c r="E74" t="s">
         <v>97</v>
       </c>
-      <c r="E74" t="s">
-        <v>98</v>
-      </c>
       <c r="G74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H74" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2977,15 +2627,16 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
+        <v>98</v>
+      </c>
+      <c r="E75" t="s">
         <v>99</v>
       </c>
-      <c r="E75" t="s">
-        <v>100</v>
-      </c>
       <c r="G75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H75" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -2997,15 +2648,16 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
+        <v>86</v>
+      </c>
+      <c r="E76" t="s">
         <v>87</v>
       </c>
-      <c r="E76" t="s">
-        <v>88</v>
-      </c>
       <c r="G76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H76" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -3017,15 +2669,16 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
+        <v>88</v>
+      </c>
+      <c r="E77" t="s">
         <v>89</v>
       </c>
-      <c r="E77" t="s">
-        <v>90</v>
-      </c>
       <c r="G77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H77" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -3037,15 +2690,16 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
+        <v>90</v>
+      </c>
+      <c r="E78" t="s">
         <v>91</v>
       </c>
-      <c r="E78" t="s">
-        <v>92</v>
-      </c>
       <c r="G78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H78" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -3057,15 +2711,16 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" t="s">
         <v>93</v>
       </c>
-      <c r="E79" t="s">
-        <v>94</v>
-      </c>
       <c r="G79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H79" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -3077,19 +2732,20 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
+        <v>94</v>
+      </c>
+      <c r="E80" t="s">
         <v>95</v>
       </c>
-      <c r="E80" t="s">
-        <v>96</v>
-      </c>
       <c r="G80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81">
         <v>20</v>
       </c>
@@ -3097,19 +2753,20 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
+        <v>96</v>
+      </c>
+      <c r="E81" t="s">
         <v>97</v>
       </c>
-      <c r="E81" t="s">
-        <v>98</v>
-      </c>
       <c r="G81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82">
         <v>21</v>
       </c>
@@ -3117,19 +2774,20 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E82" t="s">
         <v>99</v>
       </c>
-      <c r="E82" t="s">
-        <v>100</v>
-      </c>
       <c r="G82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83">
         <v>22</v>
       </c>
@@ -3137,16 +2795,17 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G83" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84">
         <v>23</v>
       </c>
@@ -3154,16 +2813,17 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G84" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85">
         <v>24</v>
       </c>
@@ -3171,16 +2831,17 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G85" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86">
         <v>25</v>
       </c>
@@ -3188,16 +2849,17 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G86" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87">
         <v>26</v>
       </c>
@@ -3205,16 +2867,17 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G87" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88">
         <v>27</v>
       </c>
@@ -3222,16 +2885,17 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89">
         <v>28</v>
       </c>
@@ -3239,16 +2903,17 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G89" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
+        <f>FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90">
         <v>29</v>
       </c>
@@ -3256,12 +2921,13 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G90" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H90" t="b">
+        <f>FALSE()</f>
         <v>0</v>
       </c>
     </row>
@@ -3273,28 +2939,29 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D91" t="s">
         <v>103</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>104</v>
       </c>
-      <c r="E91" t="s">
-        <v>105</v>
-      </c>
       <c r="G91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H91" t="b">
+        <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="I91" t="s">
+        <v>60</v>
+      </c>
+      <c r="J91" t="s">
         <v>61</v>
       </c>
-      <c r="J91" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92">
         <v>1</v>
       </c>
@@ -3302,13 +2969,16 @@
         <v>4</v>
       </c>
       <c r="C92" t="s">
+        <v>105</v>
+      </c>
+      <c r="D92" t="s">
         <v>106</v>
       </c>
-      <c r="D92" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+      <c r="H92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93">
         <v>2</v>
       </c>
@@ -3316,13 +2986,16 @@
         <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+        <v>107</v>
+      </c>
+      <c r="H93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94">
         <v>3</v>
       </c>
@@ -3330,13 +3003,16 @@
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D94" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+        <v>108</v>
+      </c>
+      <c r="H94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95">
         <v>4</v>
       </c>
@@ -3344,13 +3020,16 @@
         <v>4</v>
       </c>
       <c r="C95" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D95" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+        <v>109</v>
+      </c>
+      <c r="H95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96">
         <v>5</v>
       </c>
@@ -3358,13 +3037,16 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D96" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>110</v>
+      </c>
+      <c r="H96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97">
         <v>6</v>
       </c>
@@ -3372,13 +3054,16 @@
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D97" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>111</v>
+      </c>
+      <c r="H97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98">
         <v>7</v>
       </c>
@@ -3386,13 +3071,16 @@
         <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D98" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+        <v>112</v>
+      </c>
+      <c r="H98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>8</v>
       </c>
@@ -3400,13 +3088,16 @@
         <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D99" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+        <v>113</v>
+      </c>
+      <c r="H99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100">
         <v>9</v>
       </c>
@@ -3414,13 +3105,16 @@
         <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D100" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>114</v>
+      </c>
+      <c r="H100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101">
         <v>10</v>
       </c>
@@ -3428,13 +3122,16 @@
         <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D101" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>115</v>
+      </c>
+      <c r="H101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102">
         <v>11</v>
       </c>
@@ -3442,13 +3139,16 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D102" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+        <v>116</v>
+      </c>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103">
         <v>12</v>
       </c>
@@ -3456,13 +3156,16 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D103" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+        <v>117</v>
+      </c>
+      <c r="H103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104">
         <v>13</v>
       </c>
@@ -3470,13 +3173,16 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D104" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+        <v>118</v>
+      </c>
+      <c r="H104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105">
         <v>14</v>
       </c>
@@ -3484,13 +3190,16 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D105" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+        <v>119</v>
+      </c>
+      <c r="H105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106">
         <v>15</v>
       </c>
@@ -3498,13 +3207,16 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D106" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>120</v>
+      </c>
+      <c r="H106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107">
         <v>16</v>
       </c>
@@ -3512,13 +3224,16 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D107" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
+        <v>121</v>
+      </c>
+      <c r="H107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108">
         <v>17</v>
       </c>
@@ -3526,13 +3241,16 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D108" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
+        <v>122</v>
+      </c>
+      <c r="H108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109">
         <v>18</v>
       </c>
@@ -3540,13 +3258,16 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D109" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
+        <v>123</v>
+      </c>
+      <c r="H109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110">
         <v>19</v>
       </c>
@@ -3554,13 +3275,16 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D110" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
+        <v>124</v>
+      </c>
+      <c r="H110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111">
         <v>20</v>
       </c>
@@ -3568,13 +3292,16 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D111" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+        <v>125</v>
+      </c>
+      <c r="H111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112">
         <v>21</v>
       </c>
@@ -3582,13 +3309,16 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D112" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
+        <v>126</v>
+      </c>
+      <c r="H112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113">
         <v>22</v>
       </c>
@@ -3596,13 +3326,16 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
+        <v>127</v>
+      </c>
+      <c r="D113" t="s">
         <v>128</v>
       </c>
-      <c r="D113" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+      <c r="H113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114">
         <v>23</v>
       </c>
@@ -3610,14 +3343,16 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>128</v>
-      </c>
-      <c r="D114"/>
-      <c r="E114" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>127</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115">
         <v>24</v>
       </c>
@@ -3625,14 +3360,16 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>128</v>
-      </c>
-      <c r="D115"/>
-      <c r="E115" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>127</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116">
         <v>25</v>
       </c>
@@ -3640,14 +3377,16 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>128</v>
-      </c>
-      <c r="D116"/>
-      <c r="E116" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>127</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117">
         <v>26</v>
       </c>
@@ -3655,14 +3394,16 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>128</v>
-      </c>
-      <c r="D117"/>
-      <c r="E117" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
+        <v>127</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118">
         <v>27</v>
       </c>
@@ -3670,13 +3411,16 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
+        <v>133</v>
+      </c>
+      <c r="D118" t="s">
         <v>134</v>
       </c>
-      <c r="D118" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
+      <c r="H118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119">
         <v>28</v>
       </c>
@@ -3684,13 +3428,16 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D119" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
+        <v>135</v>
+      </c>
+      <c r="H119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120">
         <v>29</v>
       </c>
@@ -3698,26 +3445,4800 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D120" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
+        <v>136</v>
+      </c>
+      <c r="H120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121">
         <v>30</v>
       </c>
       <c r="B121">
         <v>4</v>
       </c>
+      <c r="H121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122">
+        <v>1</v>
+      </c>
+      <c r="B122">
+        <v>5</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G122" t="s">
+        <v>13</v>
+      </c>
+      <c r="H122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123">
+        <v>2</v>
+      </c>
+      <c r="B123">
+        <v>5</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G123" t="s">
+        <v>13</v>
+      </c>
+      <c r="H123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124">
+        <v>3</v>
+      </c>
+      <c r="B124">
+        <v>5</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G124" t="s">
+        <v>13</v>
+      </c>
+      <c r="H124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125">
+        <v>4</v>
+      </c>
+      <c r="B125">
+        <v>5</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G125" t="s">
+        <v>13</v>
+      </c>
+      <c r="H125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126">
+        <v>5</v>
+      </c>
+      <c r="B126">
+        <v>5</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G126" t="s">
+        <v>13</v>
+      </c>
+      <c r="H126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127">
+        <v>6</v>
+      </c>
+      <c r="B127">
+        <v>5</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G127" t="s">
+        <v>13</v>
+      </c>
+      <c r="H127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128">
+        <v>7</v>
+      </c>
+      <c r="B128">
+        <v>5</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G128" t="s">
+        <v>13</v>
+      </c>
+      <c r="H128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129">
+        <v>8</v>
+      </c>
+      <c r="B129">
+        <v>5</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G129" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130">
+        <v>9</v>
+      </c>
+      <c r="B130">
+        <v>5</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G130" t="s">
+        <v>13</v>
+      </c>
+      <c r="H130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131">
+        <v>10</v>
+      </c>
+      <c r="B131">
+        <v>5</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G131" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132">
+        <v>11</v>
+      </c>
+      <c r="B132">
+        <v>5</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G132" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133">
+        <v>12</v>
+      </c>
+      <c r="B133">
+        <v>5</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G133" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134">
+        <v>13</v>
+      </c>
+      <c r="B134">
+        <v>5</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G134" t="s">
+        <v>13</v>
+      </c>
+      <c r="H134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135">
+        <v>14</v>
+      </c>
+      <c r="B135">
+        <v>5</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G135" t="s">
+        <v>13</v>
+      </c>
+      <c r="H135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136">
+        <v>15</v>
+      </c>
+      <c r="B136">
+        <v>5</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G136" t="s">
+        <v>13</v>
+      </c>
+      <c r="H136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137">
+        <v>16</v>
+      </c>
+      <c r="B137">
+        <v>5</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G137" t="s">
+        <v>13</v>
+      </c>
+      <c r="H137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138">
+        <v>17</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G138" t="s">
+        <v>13</v>
+      </c>
+      <c r="H138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139">
+        <v>18</v>
+      </c>
+      <c r="B139">
+        <v>5</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G139" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140">
+        <v>19</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G140" t="s">
+        <v>13</v>
+      </c>
+      <c r="H140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141">
+        <v>20</v>
+      </c>
+      <c r="B141">
+        <v>5</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G141" t="s">
+        <v>13</v>
+      </c>
+      <c r="H141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142">
+        <v>21</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G142" t="s">
+        <v>13</v>
+      </c>
+      <c r="H142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143">
+        <v>22</v>
+      </c>
+      <c r="B143">
+        <v>5</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G143" t="s">
+        <v>80</v>
+      </c>
+      <c r="H143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144">
+        <v>23</v>
+      </c>
+      <c r="B144">
+        <v>5</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G144" t="s">
+        <v>80</v>
+      </c>
+      <c r="H144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145">
+        <v>24</v>
+      </c>
+      <c r="B145">
+        <v>5</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G145" t="s">
+        <v>80</v>
+      </c>
+      <c r="H145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146">
+        <v>25</v>
+      </c>
+      <c r="B146">
+        <v>5</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G146" t="s">
+        <v>80</v>
+      </c>
+      <c r="H146" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147">
+        <v>26</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G147" t="s">
+        <v>80</v>
+      </c>
+      <c r="H147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148">
+        <v>27</v>
+      </c>
+      <c r="B148">
+        <v>5</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G148" t="s">
+        <v>83</v>
+      </c>
+      <c r="H148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149">
+        <v>28</v>
+      </c>
+      <c r="B149">
+        <v>5</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G149" t="s">
+        <v>83</v>
+      </c>
+      <c r="H149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150">
+        <v>29</v>
+      </c>
+      <c r="B150">
+        <v>5</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G150" t="s">
+        <v>83</v>
+      </c>
+      <c r="H150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151">
+        <v>30</v>
+      </c>
+      <c r="B151">
+        <v>5</v>
+      </c>
+      <c r="D151" s="1"/>
+      <c r="H151" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152">
+        <v>31</v>
+      </c>
+      <c r="B152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153">
+        <v>1</v>
+      </c>
+      <c r="B153">
+        <v>6</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G153" t="s">
+        <v>13</v>
+      </c>
+      <c r="H153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154">
+        <v>2</v>
+      </c>
+      <c r="B154">
+        <v>6</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G154" t="s">
+        <v>13</v>
+      </c>
+      <c r="H154" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155">
+        <v>3</v>
+      </c>
+      <c r="B155">
+        <v>6</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G155" t="s">
+        <v>13</v>
+      </c>
+      <c r="H155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156">
+        <v>4</v>
+      </c>
+      <c r="B156">
+        <v>6</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G156" t="s">
+        <v>13</v>
+      </c>
+      <c r="H156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157">
+        <v>5</v>
+      </c>
+      <c r="B157">
+        <v>6</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G157" t="s">
+        <v>13</v>
+      </c>
+      <c r="H157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158">
+        <v>6</v>
+      </c>
+      <c r="B158">
+        <v>6</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G158" t="s">
+        <v>13</v>
+      </c>
+      <c r="H158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159">
+        <v>7</v>
+      </c>
+      <c r="B159">
+        <v>6</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G159" t="s">
+        <v>13</v>
+      </c>
+      <c r="H159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160">
+        <v>8</v>
+      </c>
+      <c r="B160">
+        <v>6</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G160" t="s">
+        <v>13</v>
+      </c>
+      <c r="H160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161">
+        <v>9</v>
+      </c>
+      <c r="B161">
+        <v>6</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G161" t="s">
+        <v>13</v>
+      </c>
+      <c r="H161" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162">
+        <v>10</v>
+      </c>
+      <c r="B162">
+        <v>6</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G162" t="s">
+        <v>13</v>
+      </c>
+      <c r="H162" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163">
+        <v>11</v>
+      </c>
+      <c r="B163">
+        <v>6</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G163" t="s">
+        <v>13</v>
+      </c>
+      <c r="H163" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164">
+        <v>12</v>
+      </c>
+      <c r="B164">
+        <v>6</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G164" t="s">
+        <v>13</v>
+      </c>
+      <c r="H164" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165">
+        <v>13</v>
+      </c>
+      <c r="B165">
+        <v>6</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G165" t="s">
+        <v>13</v>
+      </c>
+      <c r="H165" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166">
+        <v>14</v>
+      </c>
+      <c r="B166">
+        <v>6</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G166" t="s">
+        <v>13</v>
+      </c>
+      <c r="H166" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167">
+        <v>15</v>
+      </c>
+      <c r="B167">
+        <v>6</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G167" t="s">
+        <v>13</v>
+      </c>
+      <c r="H167" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168">
+        <v>16</v>
+      </c>
+      <c r="B168">
+        <v>6</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G168" t="s">
+        <v>13</v>
+      </c>
+      <c r="H168" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169">
+        <v>17</v>
+      </c>
+      <c r="B169">
+        <v>6</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G169" t="s">
+        <v>13</v>
+      </c>
+      <c r="H169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170">
+        <v>18</v>
+      </c>
+      <c r="B170">
+        <v>6</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G170" t="s">
+        <v>13</v>
+      </c>
+      <c r="H170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171">
+        <v>19</v>
+      </c>
+      <c r="B171">
+        <v>6</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G171" t="s">
+        <v>13</v>
+      </c>
+      <c r="H171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172">
+        <v>20</v>
+      </c>
+      <c r="B172">
+        <v>6</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G172" t="s">
+        <v>13</v>
+      </c>
+      <c r="H172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173">
+        <v>21</v>
+      </c>
+      <c r="B173">
+        <v>6</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G173" t="s">
+        <v>13</v>
+      </c>
+      <c r="H173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="31.2">
+      <c r="A174">
+        <v>22</v>
+      </c>
+      <c r="B174">
+        <v>6</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G174" t="s">
+        <v>80</v>
+      </c>
+      <c r="H174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="31.2">
+      <c r="A175">
+        <v>23</v>
+      </c>
+      <c r="B175">
+        <v>6</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G175" t="s">
+        <v>80</v>
+      </c>
+      <c r="H175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="31.2">
+      <c r="A176">
+        <v>24</v>
+      </c>
+      <c r="B176">
+        <v>6</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G176" t="s">
+        <v>80</v>
+      </c>
+      <c r="H176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="31.2">
+      <c r="A177">
+        <v>25</v>
+      </c>
+      <c r="B177">
+        <v>6</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G177" t="s">
+        <v>80</v>
+      </c>
+      <c r="H177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="31.2">
+      <c r="A178">
+        <v>26</v>
+      </c>
+      <c r="B178">
+        <v>6</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G178" t="s">
+        <v>80</v>
+      </c>
+      <c r="H178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="31.2">
+      <c r="A179">
+        <v>27</v>
+      </c>
+      <c r="B179">
+        <v>6</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G179" t="s">
+        <v>83</v>
+      </c>
+      <c r="H179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="31.2">
+      <c r="A180">
+        <v>28</v>
+      </c>
+      <c r="B180">
+        <v>6</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G180" t="s">
+        <v>83</v>
+      </c>
+      <c r="H180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181">
+        <v>29</v>
+      </c>
+      <c r="B181">
+        <v>6</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G181" t="s">
+        <v>83</v>
+      </c>
+      <c r="H181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182">
+        <v>30</v>
+      </c>
+      <c r="B182">
+        <v>6</v>
+      </c>
+      <c r="H182" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183">
+        <v>1</v>
+      </c>
+      <c r="B183">
+        <v>7</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G183" t="s">
+        <v>13</v>
+      </c>
+      <c r="H183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184">
+        <v>2</v>
+      </c>
+      <c r="B184">
+        <v>7</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G184" t="s">
+        <v>13</v>
+      </c>
+      <c r="H184" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185">
+        <v>3</v>
+      </c>
+      <c r="B185">
+        <v>7</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G185" t="s">
+        <v>13</v>
+      </c>
+      <c r="H185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186">
+        <v>4</v>
+      </c>
+      <c r="B186">
+        <v>7</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G186" t="s">
+        <v>13</v>
+      </c>
+      <c r="H186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187">
+        <v>5</v>
+      </c>
+      <c r="B187">
+        <v>7</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G187" t="s">
+        <v>13</v>
+      </c>
+      <c r="H187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188">
+        <v>6</v>
+      </c>
+      <c r="B188">
+        <v>7</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G188" t="s">
+        <v>13</v>
+      </c>
+      <c r="H188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189">
+        <v>7</v>
+      </c>
+      <c r="B189">
+        <v>7</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G189" t="s">
+        <v>13</v>
+      </c>
+      <c r="H189" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190">
+        <v>8</v>
+      </c>
+      <c r="B190">
+        <v>7</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G190" t="s">
+        <v>13</v>
+      </c>
+      <c r="H190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191">
+        <v>9</v>
+      </c>
+      <c r="B191">
+        <v>7</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G191" t="s">
+        <v>13</v>
+      </c>
+      <c r="H191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192">
+        <v>10</v>
+      </c>
+      <c r="B192">
+        <v>7</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G192" t="s">
+        <v>13</v>
+      </c>
+      <c r="H192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193">
+        <v>11</v>
+      </c>
+      <c r="B193">
+        <v>7</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G193" t="s">
+        <v>13</v>
+      </c>
+      <c r="H193" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194">
+        <v>12</v>
+      </c>
+      <c r="B194">
+        <v>7</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G194" t="s">
+        <v>13</v>
+      </c>
+      <c r="H194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195">
+        <v>13</v>
+      </c>
+      <c r="B195">
+        <v>7</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G195" t="s">
+        <v>13</v>
+      </c>
+      <c r="H195" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196">
+        <v>14</v>
+      </c>
+      <c r="B196">
+        <v>7</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G196" t="s">
+        <v>13</v>
+      </c>
+      <c r="H196" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197">
+        <v>15</v>
+      </c>
+      <c r="B197">
+        <v>7</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G197" t="s">
+        <v>13</v>
+      </c>
+      <c r="H197" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198">
+        <v>16</v>
+      </c>
+      <c r="B198">
+        <v>7</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G198" t="s">
+        <v>13</v>
+      </c>
+      <c r="H198" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199">
+        <v>17</v>
+      </c>
+      <c r="B199">
+        <v>7</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G199" t="s">
+        <v>13</v>
+      </c>
+      <c r="H199" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200">
+        <v>18</v>
+      </c>
+      <c r="B200">
+        <v>7</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G200" t="s">
+        <v>13</v>
+      </c>
+      <c r="H200" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201">
+        <v>19</v>
+      </c>
+      <c r="B201">
+        <v>7</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G201" t="s">
+        <v>13</v>
+      </c>
+      <c r="H201" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202">
+        <v>20</v>
+      </c>
+      <c r="B202">
+        <v>7</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G202" t="s">
+        <v>13</v>
+      </c>
+      <c r="H202" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203">
+        <v>21</v>
+      </c>
+      <c r="B203">
+        <v>7</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G203" t="s">
+        <v>13</v>
+      </c>
+      <c r="H203" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="31.2">
+      <c r="A204">
+        <v>22</v>
+      </c>
+      <c r="B204">
+        <v>7</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G204" t="s">
+        <v>80</v>
+      </c>
+      <c r="H204" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="31.2">
+      <c r="A205">
+        <v>23</v>
+      </c>
+      <c r="B205">
+        <v>7</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G205" t="s">
+        <v>80</v>
+      </c>
+      <c r="H205" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="31.2">
+      <c r="A206">
+        <v>24</v>
+      </c>
+      <c r="B206">
+        <v>7</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G206" t="s">
+        <v>80</v>
+      </c>
+      <c r="H206" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="31.2">
+      <c r="A207">
+        <v>25</v>
+      </c>
+      <c r="B207">
+        <v>7</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G207" t="s">
+        <v>80</v>
+      </c>
+      <c r="H207" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="31.2">
+      <c r="A208">
+        <v>26</v>
+      </c>
+      <c r="B208">
+        <v>7</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G208" t="s">
+        <v>80</v>
+      </c>
+      <c r="H208" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="31.2">
+      <c r="A209">
+        <v>27</v>
+      </c>
+      <c r="B209">
+        <v>7</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G209" t="s">
+        <v>83</v>
+      </c>
+      <c r="H209" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="31.2">
+      <c r="A210">
+        <v>28</v>
+      </c>
+      <c r="B210">
+        <v>7</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G210" t="s">
+        <v>83</v>
+      </c>
+      <c r="H210" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="31.2">
+      <c r="A211">
+        <v>29</v>
+      </c>
+      <c r="B211">
+        <v>7</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G211" t="s">
+        <v>83</v>
+      </c>
+      <c r="H211" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212">
+        <v>30</v>
+      </c>
+      <c r="B212">
+        <v>7</v>
+      </c>
+      <c r="H212" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213">
+        <v>31</v>
+      </c>
+      <c r="B213">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214">
+        <v>1</v>
+      </c>
+      <c r="B214">
+        <v>8</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G214" t="s">
+        <v>13</v>
+      </c>
+      <c r="H214" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215">
+        <v>2</v>
+      </c>
+      <c r="B215">
+        <v>8</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G215" t="s">
+        <v>13</v>
+      </c>
+      <c r="H215" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216">
+        <v>3</v>
+      </c>
+      <c r="B216">
+        <v>8</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G216" t="s">
+        <v>13</v>
+      </c>
+      <c r="H216" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217">
+        <v>4</v>
+      </c>
+      <c r="B217">
+        <v>8</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G217" t="s">
+        <v>13</v>
+      </c>
+      <c r="H217" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218">
+        <v>5</v>
+      </c>
+      <c r="B218">
+        <v>8</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G218" t="s">
+        <v>13</v>
+      </c>
+      <c r="H218" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219">
+        <v>6</v>
+      </c>
+      <c r="B219">
+        <v>8</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G219" t="s">
+        <v>13</v>
+      </c>
+      <c r="H219" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220">
+        <v>7</v>
+      </c>
+      <c r="B220">
+        <v>8</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G220" t="s">
+        <v>13</v>
+      </c>
+      <c r="H220" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221">
+        <v>8</v>
+      </c>
+      <c r="B221">
+        <v>8</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G221" t="s">
+        <v>13</v>
+      </c>
+      <c r="H221" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222">
+        <v>9</v>
+      </c>
+      <c r="B222">
+        <v>8</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G222" t="s">
+        <v>13</v>
+      </c>
+      <c r="H222" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223">
+        <v>10</v>
+      </c>
+      <c r="B223">
+        <v>8</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G223" t="s">
+        <v>13</v>
+      </c>
+      <c r="H223" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224">
+        <v>11</v>
+      </c>
+      <c r="B224">
+        <v>8</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G224" t="s">
+        <v>13</v>
+      </c>
+      <c r="H224" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225">
+        <v>12</v>
+      </c>
+      <c r="B225">
+        <v>8</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G225" t="s">
+        <v>13</v>
+      </c>
+      <c r="H225" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226">
+        <v>13</v>
+      </c>
+      <c r="B226">
+        <v>8</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G226" t="s">
+        <v>13</v>
+      </c>
+      <c r="H226" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227">
+        <v>14</v>
+      </c>
+      <c r="B227">
+        <v>8</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G227" t="s">
+        <v>13</v>
+      </c>
+      <c r="H227" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228">
+        <v>15</v>
+      </c>
+      <c r="B228">
+        <v>8</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G228" t="s">
+        <v>13</v>
+      </c>
+      <c r="H228" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229">
+        <v>16</v>
+      </c>
+      <c r="B229">
+        <v>8</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G229" t="s">
+        <v>13</v>
+      </c>
+      <c r="H229" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230">
+        <v>17</v>
+      </c>
+      <c r="B230">
+        <v>8</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G230" t="s">
+        <v>13</v>
+      </c>
+      <c r="H230" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231">
+        <v>18</v>
+      </c>
+      <c r="B231">
+        <v>8</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G231" t="s">
+        <v>13</v>
+      </c>
+      <c r="H231" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232">
+        <v>19</v>
+      </c>
+      <c r="B232">
+        <v>8</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G232" t="s">
+        <v>13</v>
+      </c>
+      <c r="H232" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233">
+        <v>20</v>
+      </c>
+      <c r="B233">
+        <v>8</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G233" t="s">
+        <v>13</v>
+      </c>
+      <c r="H233" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234">
+        <v>21</v>
+      </c>
+      <c r="B234">
+        <v>8</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G234" t="s">
+        <v>13</v>
+      </c>
+      <c r="H234" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235">
+        <v>22</v>
+      </c>
+      <c r="B235">
+        <v>8</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G235" t="s">
+        <v>80</v>
+      </c>
+      <c r="H235" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236">
+        <v>23</v>
+      </c>
+      <c r="B236">
+        <v>8</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G236" t="s">
+        <v>80</v>
+      </c>
+      <c r="H236" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237">
+        <v>24</v>
+      </c>
+      <c r="B237">
+        <v>8</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G237" t="s">
+        <v>80</v>
+      </c>
+      <c r="H237" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238">
+        <v>25</v>
+      </c>
+      <c r="B238">
+        <v>8</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G238" t="s">
+        <v>80</v>
+      </c>
+      <c r="H238" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239">
+        <v>26</v>
+      </c>
+      <c r="B239">
+        <v>8</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G239" t="s">
+        <v>80</v>
+      </c>
+      <c r="H239" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240">
+        <v>27</v>
+      </c>
+      <c r="B240">
+        <v>8</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G240" t="s">
+        <v>83</v>
+      </c>
+      <c r="H240" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241">
+        <v>28</v>
+      </c>
+      <c r="B241">
+        <v>8</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G241" t="s">
+        <v>83</v>
+      </c>
+      <c r="H241" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242">
+        <v>29</v>
+      </c>
+      <c r="B242">
+        <v>8</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G242" t="s">
+        <v>83</v>
+      </c>
+      <c r="H242" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243">
+        <v>30</v>
+      </c>
+      <c r="B243">
+        <v>8</v>
+      </c>
+      <c r="H243" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244">
+        <v>31</v>
+      </c>
+      <c r="B244">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="31.2">
+      <c r="A245">
+        <v>1</v>
+      </c>
+      <c r="B245">
+        <v>9</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G245" t="s">
+        <v>13</v>
+      </c>
+      <c r="H245" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="31.2">
+      <c r="A246">
+        <v>2</v>
+      </c>
+      <c r="B246">
+        <v>9</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G246" t="s">
+        <v>13</v>
+      </c>
+      <c r="H246" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="31.2">
+      <c r="A247">
+        <v>3</v>
+      </c>
+      <c r="B247">
+        <v>9</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G247" t="s">
+        <v>13</v>
+      </c>
+      <c r="H247" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="31.2">
+      <c r="A248">
+        <v>4</v>
+      </c>
+      <c r="B248">
+        <v>9</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G248" t="s">
+        <v>13</v>
+      </c>
+      <c r="H248" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="31.2">
+      <c r="A249">
+        <v>5</v>
+      </c>
+      <c r="B249">
+        <v>9</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G249" t="s">
+        <v>13</v>
+      </c>
+      <c r="H249" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="31.2">
+      <c r="A250">
+        <v>6</v>
+      </c>
+      <c r="B250">
+        <v>9</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G250" t="s">
+        <v>13</v>
+      </c>
+      <c r="H250" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="31.2">
+      <c r="A251">
+        <v>7</v>
+      </c>
+      <c r="B251">
+        <v>9</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G251" t="s">
+        <v>13</v>
+      </c>
+      <c r="H251" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="31.2">
+      <c r="A252">
+        <v>8</v>
+      </c>
+      <c r="B252">
+        <v>9</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G252" t="s">
+        <v>13</v>
+      </c>
+      <c r="H252" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="31.2">
+      <c r="A253">
+        <v>9</v>
+      </c>
+      <c r="B253">
+        <v>9</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G253" t="s">
+        <v>13</v>
+      </c>
+      <c r="H253" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="31.2">
+      <c r="A254">
+        <v>10</v>
+      </c>
+      <c r="B254">
+        <v>9</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G254" t="s">
+        <v>13</v>
+      </c>
+      <c r="H254" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="31.2">
+      <c r="A255">
+        <v>11</v>
+      </c>
+      <c r="B255">
+        <v>9</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G255" t="s">
+        <v>13</v>
+      </c>
+      <c r="H255" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="31.2">
+      <c r="A256">
+        <v>12</v>
+      </c>
+      <c r="B256">
+        <v>9</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G256" t="s">
+        <v>13</v>
+      </c>
+      <c r="H256" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="31.2">
+      <c r="A257">
+        <v>13</v>
+      </c>
+      <c r="B257">
+        <v>9</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G257" t="s">
+        <v>13</v>
+      </c>
+      <c r="H257" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="31.2">
+      <c r="A258">
+        <v>14</v>
+      </c>
+      <c r="B258">
+        <v>9</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G258" t="s">
+        <v>13</v>
+      </c>
+      <c r="H258" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="31.2">
+      <c r="A259">
+        <v>15</v>
+      </c>
+      <c r="B259">
+        <v>9</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G259" t="s">
+        <v>13</v>
+      </c>
+      <c r="H259" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="31.2">
+      <c r="A260">
+        <v>16</v>
+      </c>
+      <c r="B260">
+        <v>9</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G260" t="s">
+        <v>13</v>
+      </c>
+      <c r="H260" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="31.2">
+      <c r="A261">
+        <v>17</v>
+      </c>
+      <c r="B261">
+        <v>9</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G261" t="s">
+        <v>13</v>
+      </c>
+      <c r="H261" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="31.2">
+      <c r="A262">
+        <v>18</v>
+      </c>
+      <c r="B262">
+        <v>9</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G262" t="s">
+        <v>13</v>
+      </c>
+      <c r="H262" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="31.2">
+      <c r="A263">
+        <v>19</v>
+      </c>
+      <c r="B263">
+        <v>9</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G263" t="s">
+        <v>13</v>
+      </c>
+      <c r="H263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="31.2">
+      <c r="A264">
+        <v>20</v>
+      </c>
+      <c r="B264">
+        <v>9</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G264" t="s">
+        <v>13</v>
+      </c>
+      <c r="H264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" ht="31.2">
+      <c r="A265">
+        <v>21</v>
+      </c>
+      <c r="B265">
+        <v>9</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G265" t="s">
+        <v>13</v>
+      </c>
+      <c r="H265" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="31.2">
+      <c r="A266">
+        <v>22</v>
+      </c>
+      <c r="B266">
+        <v>9</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G266" t="s">
+        <v>13</v>
+      </c>
+      <c r="H266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="31.2">
+      <c r="A267">
+        <v>23</v>
+      </c>
+      <c r="B267">
+        <v>9</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G267" t="s">
+        <v>13</v>
+      </c>
+      <c r="H267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="31.2">
+      <c r="A268">
+        <v>24</v>
+      </c>
+      <c r="B268">
+        <v>9</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G268" t="s">
+        <v>80</v>
+      </c>
+      <c r="H268" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="31.2">
+      <c r="A269">
+        <v>25</v>
+      </c>
+      <c r="B269">
+        <v>9</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G269" t="s">
+        <v>80</v>
+      </c>
+      <c r="H269" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="31.2">
+      <c r="A270">
+        <v>26</v>
+      </c>
+      <c r="B270">
+        <v>9</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G270" t="s">
+        <v>80</v>
+      </c>
+      <c r="H270" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="31.2">
+      <c r="A271">
+        <v>27</v>
+      </c>
+      <c r="B271">
+        <v>9</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G271" t="s">
+        <v>80</v>
+      </c>
+      <c r="H271" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="31.2">
+      <c r="A272">
+        <v>28</v>
+      </c>
+      <c r="B272">
+        <v>9</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G272" t="s">
+        <v>80</v>
+      </c>
+      <c r="H272" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="31.2">
+      <c r="A273">
+        <v>29</v>
+      </c>
+      <c r="B273">
+        <v>9</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G273" t="s">
+        <v>83</v>
+      </c>
+      <c r="H273" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274">
+        <v>30</v>
+      </c>
+      <c r="B274">
+        <v>9</v>
+      </c>
+      <c r="D274" s="1"/>
+      <c r="H274" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="31.2">
+      <c r="A275">
+        <v>1</v>
+      </c>
+      <c r="B275">
+        <v>10</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G275" t="s">
+        <v>13</v>
+      </c>
+      <c r="H275" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="31.2">
+      <c r="A276">
+        <v>2</v>
+      </c>
+      <c r="B276">
+        <v>10</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G276" t="s">
+        <v>13</v>
+      </c>
+      <c r="H276" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="31.2">
+      <c r="A277">
+        <v>3</v>
+      </c>
+      <c r="B277">
+        <v>10</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G277" t="s">
+        <v>13</v>
+      </c>
+      <c r="H277" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="31.2">
+      <c r="A278">
+        <v>4</v>
+      </c>
+      <c r="B278">
+        <v>10</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G278" t="s">
+        <v>13</v>
+      </c>
+      <c r="H278" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" ht="31.2">
+      <c r="A279">
+        <v>5</v>
+      </c>
+      <c r="B279">
+        <v>10</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G279" t="s">
+        <v>13</v>
+      </c>
+      <c r="H279" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" ht="31.2">
+      <c r="A280">
+        <v>6</v>
+      </c>
+      <c r="B280">
+        <v>10</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G280" t="s">
+        <v>13</v>
+      </c>
+      <c r="H280" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" ht="31.2">
+      <c r="A281">
+        <v>7</v>
+      </c>
+      <c r="B281">
+        <v>10</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G281" t="s">
+        <v>13</v>
+      </c>
+      <c r="H281" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="31.2">
+      <c r="A282">
+        <v>8</v>
+      </c>
+      <c r="B282">
+        <v>10</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G282" t="s">
+        <v>13</v>
+      </c>
+      <c r="H282" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" ht="31.2">
+      <c r="A283">
+        <v>9</v>
+      </c>
+      <c r="B283">
+        <v>10</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G283" t="s">
+        <v>13</v>
+      </c>
+      <c r="H283" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" ht="31.2">
+      <c r="A284">
+        <v>10</v>
+      </c>
+      <c r="B284">
+        <v>10</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G284" t="s">
+        <v>13</v>
+      </c>
+      <c r="H284" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" ht="31.2">
+      <c r="A285">
+        <v>11</v>
+      </c>
+      <c r="B285">
+        <v>10</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G285" t="s">
+        <v>13</v>
+      </c>
+      <c r="H285" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="31.2">
+      <c r="A286">
+        <v>12</v>
+      </c>
+      <c r="B286">
+        <v>10</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G286" t="s">
+        <v>13</v>
+      </c>
+      <c r="H286" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="31.2">
+      <c r="A287">
+        <v>13</v>
+      </c>
+      <c r="B287">
+        <v>10</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G287" t="s">
+        <v>13</v>
+      </c>
+      <c r="H287" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="31.2">
+      <c r="A288">
+        <v>14</v>
+      </c>
+      <c r="B288">
+        <v>10</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G288" t="s">
+        <v>13</v>
+      </c>
+      <c r="H288" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" ht="31.2">
+      <c r="A289">
+        <v>15</v>
+      </c>
+      <c r="B289">
+        <v>10</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G289" t="s">
+        <v>13</v>
+      </c>
+      <c r="H289" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" ht="31.2">
+      <c r="A290">
+        <v>16</v>
+      </c>
+      <c r="B290">
+        <v>10</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G290" t="s">
+        <v>13</v>
+      </c>
+      <c r="H290" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" ht="31.2">
+      <c r="A291">
+        <v>17</v>
+      </c>
+      <c r="B291">
+        <v>10</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G291" t="s">
+        <v>13</v>
+      </c>
+      <c r="H291" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" ht="31.2">
+      <c r="A292">
+        <v>18</v>
+      </c>
+      <c r="B292">
+        <v>10</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G292" t="s">
+        <v>13</v>
+      </c>
+      <c r="H292" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" ht="31.2">
+      <c r="A293">
+        <v>19</v>
+      </c>
+      <c r="B293">
+        <v>10</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G293" t="s">
+        <v>13</v>
+      </c>
+      <c r="H293" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" ht="31.2">
+      <c r="A294">
+        <v>20</v>
+      </c>
+      <c r="B294">
+        <v>10</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G294" t="s">
+        <v>13</v>
+      </c>
+      <c r="H294" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" ht="31.2">
+      <c r="A295">
+        <v>21</v>
+      </c>
+      <c r="B295">
+        <v>10</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G295" t="s">
+        <v>13</v>
+      </c>
+      <c r="H295" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296">
+        <v>22</v>
+      </c>
+      <c r="B296">
+        <v>10</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G296" t="s">
+        <v>80</v>
+      </c>
+      <c r="H296" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297">
+        <v>23</v>
+      </c>
+      <c r="B297">
+        <v>10</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G297" t="s">
+        <v>80</v>
+      </c>
+      <c r="H297" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298">
+        <v>24</v>
+      </c>
+      <c r="B298">
+        <v>10</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G298" t="s">
+        <v>80</v>
+      </c>
+      <c r="H298" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299">
+        <v>25</v>
+      </c>
+      <c r="B299">
+        <v>10</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G299" t="s">
+        <v>80</v>
+      </c>
+      <c r="H299" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300">
+        <v>26</v>
+      </c>
+      <c r="B300">
+        <v>10</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G300" t="s">
+        <v>80</v>
+      </c>
+      <c r="H300" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" ht="46.8">
+      <c r="A301">
+        <v>27</v>
+      </c>
+      <c r="B301">
+        <v>10</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G301" t="s">
+        <v>83</v>
+      </c>
+      <c r="H301" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" ht="46.8">
+      <c r="A302">
+        <v>28</v>
+      </c>
+      <c r="B302">
+        <v>10</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G302" t="s">
+        <v>83</v>
+      </c>
+      <c r="H302" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" ht="46.8">
+      <c r="A303">
+        <v>29</v>
+      </c>
+      <c r="B303">
+        <v>10</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G303" t="s">
+        <v>83</v>
+      </c>
+      <c r="H303" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304">
+        <v>30</v>
+      </c>
+      <c r="B304">
+        <v>10</v>
+      </c>
+      <c r="H304" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305">
+        <v>31</v>
+      </c>
+      <c r="B305">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" ht="31.2">
+      <c r="A306">
+        <v>1</v>
+      </c>
+      <c r="B306">
+        <v>11</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G306" t="s">
+        <v>13</v>
+      </c>
+      <c r="H306" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" ht="31.2">
+      <c r="A307">
+        <v>2</v>
+      </c>
+      <c r="B307">
+        <v>11</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G307" t="s">
+        <v>13</v>
+      </c>
+      <c r="H307" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" ht="31.2">
+      <c r="A308">
+        <v>3</v>
+      </c>
+      <c r="B308">
+        <v>11</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G308" t="s">
+        <v>13</v>
+      </c>
+      <c r="H308" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" ht="31.2">
+      <c r="A309">
+        <v>4</v>
+      </c>
+      <c r="B309">
+        <v>11</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G309" t="s">
+        <v>13</v>
+      </c>
+      <c r="H309" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" ht="31.2">
+      <c r="A310">
+        <v>5</v>
+      </c>
+      <c r="B310">
+        <v>11</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G310" t="s">
+        <v>13</v>
+      </c>
+      <c r="H310" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" ht="31.2">
+      <c r="A311">
+        <v>6</v>
+      </c>
+      <c r="B311">
+        <v>11</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G311" t="s">
+        <v>13</v>
+      </c>
+      <c r="H311" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" ht="31.2">
+      <c r="A312">
+        <v>7</v>
+      </c>
+      <c r="B312">
+        <v>11</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G312" t="s">
+        <v>13</v>
+      </c>
+      <c r="H312" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" ht="31.2">
+      <c r="A313">
+        <v>8</v>
+      </c>
+      <c r="B313">
+        <v>11</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G313" t="s">
+        <v>13</v>
+      </c>
+      <c r="H313" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" ht="31.2">
+      <c r="A314">
+        <v>9</v>
+      </c>
+      <c r="B314">
+        <v>11</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G314" t="s">
+        <v>13</v>
+      </c>
+      <c r="H314" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" ht="31.2">
+      <c r="A315">
+        <v>10</v>
+      </c>
+      <c r="B315">
+        <v>11</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G315" t="s">
+        <v>13</v>
+      </c>
+      <c r="H315" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" ht="31.2">
+      <c r="A316">
+        <v>11</v>
+      </c>
+      <c r="B316">
+        <v>11</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G316" t="s">
+        <v>13</v>
+      </c>
+      <c r="H316" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" ht="31.2">
+      <c r="A317">
+        <v>12</v>
+      </c>
+      <c r="B317">
+        <v>11</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G317" t="s">
+        <v>13</v>
+      </c>
+      <c r="H317" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" ht="31.2">
+      <c r="A318">
+        <v>13</v>
+      </c>
+      <c r="B318">
+        <v>11</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G318" t="s">
+        <v>13</v>
+      </c>
+      <c r="H318" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" ht="31.2">
+      <c r="A319">
+        <v>14</v>
+      </c>
+      <c r="B319">
+        <v>11</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G319" t="s">
+        <v>13</v>
+      </c>
+      <c r="H319" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" ht="31.2">
+      <c r="A320">
+        <v>15</v>
+      </c>
+      <c r="B320">
+        <v>11</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G320" t="s">
+        <v>13</v>
+      </c>
+      <c r="H320" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" ht="31.2">
+      <c r="A321">
+        <v>16</v>
+      </c>
+      <c r="B321">
+        <v>11</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G321" t="s">
+        <v>13</v>
+      </c>
+      <c r="H321" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" ht="31.2">
+      <c r="A322">
+        <v>17</v>
+      </c>
+      <c r="B322">
+        <v>11</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G322" t="s">
+        <v>13</v>
+      </c>
+      <c r="H322" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" ht="31.2">
+      <c r="A323">
+        <v>18</v>
+      </c>
+      <c r="B323">
+        <v>11</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G323" t="s">
+        <v>13</v>
+      </c>
+      <c r="H323" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" ht="31.2">
+      <c r="A324">
+        <v>19</v>
+      </c>
+      <c r="B324">
+        <v>11</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G324" t="s">
+        <v>13</v>
+      </c>
+      <c r="H324" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" ht="31.2">
+      <c r="A325">
+        <v>20</v>
+      </c>
+      <c r="B325">
+        <v>11</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G325" t="s">
+        <v>13</v>
+      </c>
+      <c r="H325" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" ht="31.2">
+      <c r="A326">
+        <v>21</v>
+      </c>
+      <c r="B326">
+        <v>11</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G326" t="s">
+        <v>13</v>
+      </c>
+      <c r="H326" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" ht="31.2">
+      <c r="A327">
+        <v>22</v>
+      </c>
+      <c r="B327">
+        <v>11</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G327" t="s">
+        <v>80</v>
+      </c>
+      <c r="H327" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" ht="31.2">
+      <c r="A328">
+        <v>23</v>
+      </c>
+      <c r="B328">
+        <v>11</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G328" t="s">
+        <v>80</v>
+      </c>
+      <c r="H328" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" ht="31.2">
+      <c r="A329">
+        <v>24</v>
+      </c>
+      <c r="B329">
+        <v>11</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G329" t="s">
+        <v>80</v>
+      </c>
+      <c r="H329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" ht="31.2">
+      <c r="A330">
+        <v>25</v>
+      </c>
+      <c r="B330">
+        <v>11</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G330" t="s">
+        <v>80</v>
+      </c>
+      <c r="H330" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" ht="31.2">
+      <c r="A331">
+        <v>26</v>
+      </c>
+      <c r="B331">
+        <v>11</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G331" t="s">
+        <v>80</v>
+      </c>
+      <c r="H331" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" ht="31.2">
+      <c r="A332">
+        <v>27</v>
+      </c>
+      <c r="B332">
+        <v>11</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G332" t="s">
+        <v>83</v>
+      </c>
+      <c r="H332" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" ht="31.2">
+      <c r="A333">
+        <v>28</v>
+      </c>
+      <c r="B333">
+        <v>11</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G333" t="s">
+        <v>83</v>
+      </c>
+      <c r="H333" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" ht="31.2">
+      <c r="A334">
+        <v>29</v>
+      </c>
+      <c r="B334">
+        <v>11</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G334" t="s">
+        <v>83</v>
+      </c>
+      <c r="H334" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335">
+        <v>30</v>
+      </c>
+      <c r="B335">
+        <v>11</v>
+      </c>
+      <c r="D335" s="1"/>
+      <c r="H335" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336">
+        <v>1</v>
+      </c>
+      <c r="B336">
+        <v>12</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G336" t="s">
+        <v>13</v>
+      </c>
+      <c r="H336" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337">
+        <v>2</v>
+      </c>
+      <c r="B337">
+        <v>12</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G337" t="s">
+        <v>13</v>
+      </c>
+      <c r="H337" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
+      <c r="A338">
+        <v>3</v>
+      </c>
+      <c r="B338">
+        <v>12</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G338" t="s">
+        <v>13</v>
+      </c>
+      <c r="H338" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8">
+      <c r="A339">
+        <v>4</v>
+      </c>
+      <c r="B339">
+        <v>12</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G339" t="s">
+        <v>13</v>
+      </c>
+      <c r="H339" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8">
+      <c r="A340">
+        <v>5</v>
+      </c>
+      <c r="B340">
+        <v>12</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G340" t="s">
+        <v>13</v>
+      </c>
+      <c r="H340" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8">
+      <c r="A341">
+        <v>6</v>
+      </c>
+      <c r="B341">
+        <v>12</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G341" t="s">
+        <v>13</v>
+      </c>
+      <c r="H341" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8">
+      <c r="A342">
+        <v>7</v>
+      </c>
+      <c r="B342">
+        <v>12</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G342" t="s">
+        <v>13</v>
+      </c>
+      <c r="H342" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8">
+      <c r="A343">
+        <v>8</v>
+      </c>
+      <c r="B343">
+        <v>12</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G343" t="s">
+        <v>13</v>
+      </c>
+      <c r="H343" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344">
+        <v>9</v>
+      </c>
+      <c r="B344">
+        <v>12</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G344" t="s">
+        <v>13</v>
+      </c>
+      <c r="H344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345">
+        <v>10</v>
+      </c>
+      <c r="B345">
+        <v>12</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G345" t="s">
+        <v>13</v>
+      </c>
+      <c r="H345" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346">
+        <v>11</v>
+      </c>
+      <c r="B346">
+        <v>12</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G346" t="s">
+        <v>13</v>
+      </c>
+      <c r="H346" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347">
+        <v>12</v>
+      </c>
+      <c r="B347">
+        <v>12</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G347" t="s">
+        <v>13</v>
+      </c>
+      <c r="H347" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348">
+        <v>13</v>
+      </c>
+      <c r="B348">
+        <v>12</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G348" t="s">
+        <v>13</v>
+      </c>
+      <c r="H348" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349">
+        <v>14</v>
+      </c>
+      <c r="B349">
+        <v>12</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G349" t="s">
+        <v>13</v>
+      </c>
+      <c r="H349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350">
+        <v>15</v>
+      </c>
+      <c r="B350">
+        <v>12</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G350" t="s">
+        <v>13</v>
+      </c>
+      <c r="H350" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351">
+        <v>16</v>
+      </c>
+      <c r="B351">
+        <v>12</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G351" t="s">
+        <v>13</v>
+      </c>
+      <c r="H351" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8">
+      <c r="A352">
+        <v>17</v>
+      </c>
+      <c r="B352">
+        <v>12</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G352" t="s">
+        <v>13</v>
+      </c>
+      <c r="H352" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353">
+        <v>18</v>
+      </c>
+      <c r="B353">
+        <v>12</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G353" t="s">
+        <v>13</v>
+      </c>
+      <c r="H353" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354">
+        <v>19</v>
+      </c>
+      <c r="B354">
+        <v>12</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G354" t="s">
+        <v>13</v>
+      </c>
+      <c r="H354" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355">
+        <v>20</v>
+      </c>
+      <c r="B355">
+        <v>12</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G355" t="s">
+        <v>13</v>
+      </c>
+      <c r="H355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356">
+        <v>21</v>
+      </c>
+      <c r="B356">
+        <v>12</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G356" t="s">
+        <v>13</v>
+      </c>
+      <c r="H356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" ht="31.2">
+      <c r="A357">
+        <v>22</v>
+      </c>
+      <c r="B357">
+        <v>12</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G357" t="s">
+        <v>80</v>
+      </c>
+      <c r="H357" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" ht="31.2">
+      <c r="A358">
+        <v>23</v>
+      </c>
+      <c r="B358">
+        <v>12</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G358" t="s">
+        <v>80</v>
+      </c>
+      <c r="H358" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" ht="31.2">
+      <c r="A359">
+        <v>24</v>
+      </c>
+      <c r="B359">
+        <v>12</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G359" t="s">
+        <v>80</v>
+      </c>
+      <c r="H359" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" ht="31.2">
+      <c r="A360">
+        <v>25</v>
+      </c>
+      <c r="B360">
+        <v>12</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D360" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G360" t="s">
+        <v>80</v>
+      </c>
+      <c r="H360" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" ht="31.2">
+      <c r="A361">
+        <v>26</v>
+      </c>
+      <c r="B361">
+        <v>12</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G361" t="s">
+        <v>80</v>
+      </c>
+      <c r="H361" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" ht="31.2">
+      <c r="A362">
+        <v>27</v>
+      </c>
+      <c r="B362">
+        <v>12</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G362" t="s">
+        <v>83</v>
+      </c>
+      <c r="H362" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" ht="31.2">
+      <c r="A363">
+        <v>28</v>
+      </c>
+      <c r="B363">
+        <v>12</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G363" t="s">
+        <v>83</v>
+      </c>
+      <c r="H363" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" ht="31.2">
+      <c r="A364">
+        <v>29</v>
+      </c>
+      <c r="B364">
+        <v>12</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G364" t="s">
+        <v>83</v>
+      </c>
+      <c r="H364" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365">
+        <v>30</v>
+      </c>
+      <c r="B365">
+        <v>12</v>
+      </c>
+      <c r="D365" s="1"/>
+      <c r="H365" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366">
+        <v>31</v>
+      </c>
+      <c r="B366">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="I3:J3 D2:E3 A3 G2:J2 A2:B2 A1:J1" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="216">
   <si>
     <t xml:space="preserve">Day</t>
   </si>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">FALSE</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day1.jpeg</t>
+    <t xml:space="preserve">/images/lessons/month1-day1.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Responsibility of parents</t>
@@ -82,120 +82,180 @@
     <t xml:space="preserve">/example.pdf</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day2.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Health and medical services</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Article 24-26 in simple words (10-15mins), then let the child draw, repeat, or share it with the family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day3.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Standard of living</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 27 and 31  in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day4.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Non-discrimination</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 2 and 11 in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day5.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protection from abuse</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 19 and 20 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day6.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Refugee children</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 22 and 25 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day7.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Child labour</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 32 and 33 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day8.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protection from sexual exploitation</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 34 and 35 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day9.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protection from all other forms of exploitation</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 36 and 37 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day10.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">War and armed conflict</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 38 and 39 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day11.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Juvenile justice</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Article 40 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day12.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Respect for parental rights</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 5 and 7 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day13.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protection of identity</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 8 and 10 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day14.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adoption</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 21 and 23 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day15.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Disabled children</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 28 and 29 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day16.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Educational aims</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Article 30 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day17.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">The well-being of the child is paramount</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Article 3 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day18.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Freedom of opinion</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 12 and 13 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day19.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Freedom of thought, conscience, and religion</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 14 and 15 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day20.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Protection of privacy</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 16 and 17 in simple words (10–15 mins), then let the child draw, repeat, or share it with family</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month1-day21.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">REWARD DAY - Gauntlets of Safety</t>
   </si>
   <si>
@@ -220,16 +280,26 @@
     <t xml:space="preserve"> Rich in essential nutrients</t>
   </si>
   <si>
+    <t xml:space="preserve">Ginisang munggo with malunggay and kalabasa is a nutritious Filipino dish rich in essential vitamins and minerals. Mung bean provides a good source of plant-based protein, dietary fiber, iron, and folate, which help support muscle growth, improve digestion, and prevent anemia. The addition of Moringa oleifera (malunggay) boosts the dish’s nutritional value because it is packed with Vitamin A, Vitamin C, calcium, iron, and antioxidants that strengthen immunity, promote healthy vision, and support strong bones. Meanwhile, Cucurbita moschata (kalabasa) supplies beta-carotene, fiber, and potassium, which help maintain good eyesight, heart health, and proper digestion. Together, these ingredients create a balanced, affordable, and nutrient-dense meal that supports overall health and well-being.</t>
+  </si>
+  <si>
     <t xml:space="preserve">test</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month2-day1.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Add malunggay leaves to tinola, munggo,or instant noodles.</t>
   </si>
   <si>
     <t xml:space="preserve">Rich in antioxidants</t>
   </si>
   <si>
-    <t xml:space="preserve">Wardi gwapo</t>
+    <t xml:space="preserve">Adding malunggay leaves to tinola, munggo, or even instant noodles is a simple way to make everyday meals more nutritious and rich in antioxidants. Moringa oleifera, commonly known as malunggay, contains powerful antioxidants such as vitamin C, beta-carotene, quercetin, and chlorogenic acid. These compounds help protect the body’s cells from damage caused by free radicals, which are linked to aging and various diseases. When added to dishes like Tinola, munggo, or instant noodles, malunggay enhances not only the flavor and color but also the nutritional value of the meal. Its high antioxidant content supports a stronger immune system, reduces inflammation, and promotes overall health, making it an easy and affordable way to boost daily nutrient intake.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/month2-day2.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Add boiled egg (split in half if budget is tight)</t>
@@ -238,22 +308,34 @@
     <t xml:space="preserve">Contains protein</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month2-day3.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Add banana (saging na saba or lakatan) for dessert or merienda</t>
   </si>
   <si>
     <t xml:space="preserve">Rich in fiber and potassium</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month2-day4.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Add dilis (small dried fish) with egg fried rice.</t>
   </si>
   <si>
     <t xml:space="preserve">Rich in calcium</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month2-day5.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Add kamote (sweet potato) boiled or fried. </t>
   </si>
   <si>
     <t xml:space="preserve">Contains carbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/month2-day6.jpg</t>
   </si>
   <si>
     <t xml:space="preserve"> Add gabi/taro or squash to a simple sabaw </t>
@@ -263,7 +345,13 @@
  and E</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/month2-day7.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Add malunggay leaves to tinola, munggo,or intant noodles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/month2-day1.jpeg</t>
   </si>
   <si>
     <t xml:space="preserve"> Contains Vitamin C and E</t>
@@ -863,7 +951,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -887,6 +975,26 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFCC0000"/>
       <name val="Arial"/>
@@ -900,13 +1008,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -958,7 +1059,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -975,23 +1076,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1344,7 +1453,7 @@
         <v>15</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1355,10 +1464,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>19</v>
@@ -1370,7 +1479,7 @@
         <v>15</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1381,10 +1490,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -1393,7 +1502,7 @@
         <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1404,10 +1513,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>14</v>
@@ -1415,8 +1524,8 @@
       <c r="H6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>16</v>
+      <c r="K6" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1427,10 +1536,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -1438,8 +1547,8 @@
       <c r="H7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>16</v>
+      <c r="K7" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1450,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>14</v>
@@ -1461,8 +1570,8 @@
       <c r="H8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>16</v>
+      <c r="K8" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1473,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
@@ -1484,8 +1593,8 @@
       <c r="H9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>16</v>
+      <c r="K9" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1496,16 +1605,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1516,16 +1628,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1536,16 +1651,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1556,16 +1674,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1576,10 +1697,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>14</v>
@@ -1587,6 +1708,9 @@
       <c r="H14" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="K14" s="4" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -1596,16 +1720,19 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1616,16 +1743,19 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1636,16 +1766,19 @@
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1656,16 +1789,19 @@
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1676,16 +1812,19 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1696,16 +1835,19 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1716,16 +1858,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1736,16 +1881,19 @@
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1833,25 +1981,25 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1862,26 +2010,29 @@
         <v>2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>66</v>
+        <v>85</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="4" t="b">
+      <c r="H32" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>2</v>
       </c>
@@ -1889,20 +2040,23 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>69</v>
+        <v>90</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="4" t="b">
+      <c r="H33" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1913,17 +2067,20 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="4" t="b">
+      <c r="H34" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1934,17 +2091,20 @@
         <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="4" t="b">
+      <c r="H35" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1955,17 +2115,20 @@
         <v>2</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="4" t="b">
+      <c r="H36" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1976,17 +2139,20 @@
         <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="4" t="b">
+      <c r="H37" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1997,17 +2163,20 @@
         <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="4" t="b">
+      <c r="H38" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2018,17 +2187,20 @@
         <v>2</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="4" t="b">
+      <c r="H39" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2039,17 +2211,20 @@
         <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="4" t="b">
+      <c r="H40" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2060,17 +2235,20 @@
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="4" t="b">
+      <c r="H41" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2081,17 +2259,20 @@
         <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H42" s="4" t="b">
+      <c r="H42" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2102,17 +2283,20 @@
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="4" t="b">
+      <c r="H43" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2123,18 +2307,21 @@
         <v>2</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="4" t="b">
+      <c r="H44" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K44" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
@@ -2144,17 +2331,20 @@
         <v>2</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="4" t="b">
+      <c r="H45" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2165,17 +2355,20 @@
         <v>2</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="4" t="b">
+      <c r="H46" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2186,17 +2379,20 @@
         <v>2</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H47" s="4" t="b">
+      <c r="H47" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2207,17 +2403,20 @@
         <v>2</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H48" s="4" t="b">
+      <c r="H48" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2228,17 +2427,20 @@
         <v>2</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="4" t="b">
+      <c r="H49" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2249,17 +2451,20 @@
         <v>2</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H50" s="4" t="b">
+      <c r="H50" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2270,17 +2475,20 @@
         <v>2</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="4" t="b">
+      <c r="H51" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2291,20 +2499,23 @@
         <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="4" t="b">
+      <c r="H52" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K52" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
         <v>22</v>
       </c>
@@ -2312,12 +2523,12 @@
         <v>2</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H53" s="4" t="b">
+        <v>112</v>
+      </c>
+      <c r="H53" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2330,12 +2541,12 @@
         <v>2</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H54" s="4" t="b">
+        <v>112</v>
+      </c>
+      <c r="H54" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2348,12 +2559,12 @@
         <v>2</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H55" s="4" t="b">
+        <v>112</v>
+      </c>
+      <c r="H55" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2366,12 +2577,12 @@
         <v>2</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H56" s="4" t="b">
+        <v>115</v>
+      </c>
+      <c r="H56" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2384,12 +2595,12 @@
         <v>2</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H57" s="4" t="b">
+        <v>115</v>
+      </c>
+      <c r="H57" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2402,12 +2613,12 @@
         <v>2</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H58" s="4" t="b">
+        <v>115</v>
+      </c>
+      <c r="H58" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2419,7 +2630,7 @@
       <c r="B59" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="4" t="b">
+      <c r="H59" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2434,7 +2645,7 @@
       <c r="G60" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H60" s="4" t="b">
+      <c r="H60" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2447,23 +2658,23 @@
         <v>2</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H61" s="4" t="b">
+      <c r="H61" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2474,15 +2685,15 @@
         <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H62" s="4" t="b">
+      <c r="H62" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2495,15 +2706,15 @@
         <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H63" s="4" t="b">
+      <c r="H63" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2516,15 +2727,15 @@
         <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H64" s="4" t="b">
+      <c r="H64" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2537,15 +2748,15 @@
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H65" s="4" t="b">
+      <c r="H65" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2558,15 +2769,15 @@
         <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H66" s="4" t="b">
+      <c r="H66" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2579,15 +2790,15 @@
         <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H67" s="4" t="b">
+      <c r="H67" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2600,15 +2811,15 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H68" s="4" t="b">
+      <c r="H68" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2621,15 +2832,15 @@
         <v>3</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H69" s="4" t="b">
+      <c r="H69" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2642,15 +2853,15 @@
         <v>3</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H70" s="4" t="b">
+      <c r="H70" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2663,15 +2874,15 @@
         <v>3</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H71" s="4" t="b">
+      <c r="H71" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2684,15 +2895,15 @@
         <v>3</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H72" s="4" t="b">
+      <c r="H72" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2705,15 +2916,15 @@
         <v>3</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H73" s="4" t="b">
+      <c r="H73" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2726,15 +2937,15 @@
         <v>3</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H74" s="4" t="b">
+      <c r="H74" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2747,15 +2958,15 @@
         <v>3</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H75" s="4" t="b">
+      <c r="H75" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2768,15 +2979,15 @@
         <v>3</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H76" s="4" t="b">
+      <c r="H76" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2789,15 +3000,15 @@
         <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H77" s="4" t="b">
+      <c r="H77" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2810,15 +3021,15 @@
         <v>3</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H78" s="4" t="b">
+      <c r="H78" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2831,15 +3042,15 @@
         <v>3</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H79" s="4" t="b">
+      <c r="H79" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2852,15 +3063,15 @@
         <v>3</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H80" s="4" t="b">
+      <c r="H80" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2873,15 +3084,15 @@
         <v>3</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="4" t="b">
+      <c r="H81" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2894,15 +3105,15 @@
         <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H82" s="4" t="b">
+      <c r="H82" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2915,12 +3126,12 @@
         <v>3</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H83" s="4" t="b">
+        <v>112</v>
+      </c>
+      <c r="H83" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2933,12 +3144,12 @@
         <v>3</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H84" s="4" t="b">
+        <v>112</v>
+      </c>
+      <c r="H84" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2951,12 +3162,12 @@
         <v>3</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H85" s="4" t="b">
+        <v>112</v>
+      </c>
+      <c r="H85" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2969,12 +3180,12 @@
         <v>3</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H86" s="4" t="b">
+        <v>112</v>
+      </c>
+      <c r="H86" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2987,12 +3198,12 @@
         <v>3</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H87" s="4" t="b">
+        <v>112</v>
+      </c>
+      <c r="H87" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3005,12 +3216,12 @@
         <v>3</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H88" s="4" t="b">
+        <v>115</v>
+      </c>
+      <c r="H88" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3023,12 +3234,12 @@
         <v>3</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H89" s="4" t="b">
+        <v>115</v>
+      </c>
+      <c r="H89" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3041,12 +3252,12 @@
         <v>3</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H90" s="4" t="b">
+        <v>115</v>
+      </c>
+      <c r="H90" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3059,26 +3270,26 @@
         <v>3</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H91" s="4" t="b">
+      <c r="H91" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3089,10 +3300,10 @@
         <v>4</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3103,10 +3314,10 @@
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3117,10 +3328,10 @@
         <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3131,10 +3342,10 @@
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3145,10 +3356,10 @@
         <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3159,10 +3370,10 @@
         <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3173,10 +3384,10 @@
         <v>4</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3187,10 +3398,10 @@
         <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3201,10 +3412,10 @@
         <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3215,10 +3426,10 @@
         <v>4</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3229,10 +3440,10 @@
         <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3243,10 +3454,10 @@
         <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3257,10 +3468,10 @@
         <v>4</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3271,10 +3482,10 @@
         <v>4</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3285,10 +3496,10 @@
         <v>4</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3299,10 +3510,10 @@
         <v>4</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3313,10 +3524,10 @@
         <v>4</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3327,10 +3538,10 @@
         <v>4</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3341,10 +3552,10 @@
         <v>4</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3355,10 +3566,10 @@
         <v>4</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3369,10 +3580,10 @@
         <v>4</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3383,10 +3594,10 @@
         <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3397,10 +3608,10 @@
         <v>4</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>132</v>
+        <v>159</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3411,10 +3622,10 @@
         <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>133</v>
+        <v>159</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3425,10 +3636,10 @@
         <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>134</v>
+        <v>159</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,10 +3650,10 @@
         <v>4</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>135</v>
+        <v>159</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3453,10 +3664,10 @@
         <v>4</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3467,10 +3678,10 @@
         <v>4</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3481,10 +3692,10 @@
         <v>4</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3503,10 +3714,10 @@
         <v>5</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>14</v>
@@ -3520,10 +3731,10 @@
         <v>5</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>14</v>
@@ -3537,10 +3748,10 @@
         <v>5</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>14</v>
@@ -3554,10 +3765,10 @@
         <v>5</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>14</v>
@@ -3571,10 +3782,10 @@
         <v>5</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>14</v>
@@ -3588,10 +3799,10 @@
         <v>5</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>14</v>
@@ -3605,10 +3816,10 @@
         <v>5</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>14</v>
@@ -3622,10 +3833,10 @@
         <v>5</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>14</v>
@@ -3639,10 +3850,10 @@
         <v>5</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>14</v>
@@ -3656,10 +3867,10 @@
         <v>5</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>14</v>
@@ -3673,10 +3884,10 @@
         <v>5</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>14</v>
@@ -3690,10 +3901,10 @@
         <v>5</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>14</v>
@@ -3707,10 +3918,10 @@
         <v>5</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>14</v>
@@ -3724,10 +3935,10 @@
         <v>5</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>14</v>
@@ -3741,10 +3952,10 @@
         <v>5</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>14</v>
@@ -3758,10 +3969,10 @@
         <v>5</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>14</v>
@@ -3775,10 +3986,10 @@
         <v>5</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>14</v>
@@ -3792,10 +4003,10 @@
         <v>5</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>14</v>
@@ -3809,10 +4020,10 @@
         <v>5</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>14</v>
@@ -3826,10 +4037,10 @@
         <v>5</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>14</v>
@@ -3843,10 +4054,10 @@
         <v>5</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>14</v>
@@ -3860,13 +4071,13 @@
         <v>5</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3877,13 +4088,13 @@
         <v>5</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3894,13 +4105,13 @@
         <v>5</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3911,13 +4122,13 @@
         <v>5</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3928,13 +4139,13 @@
         <v>5</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3945,13 +4156,13 @@
         <v>5</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3962,13 +4173,13 @@
         <v>5</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3979,13 +4190,13 @@
         <v>5</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4013,10 +4224,10 @@
         <v>6</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>14</v>
@@ -4030,10 +4241,10 @@
         <v>6</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>14</v>
@@ -4047,10 +4258,10 @@
         <v>6</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>14</v>
@@ -4064,10 +4275,10 @@
         <v>6</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>14</v>
@@ -4081,10 +4292,10 @@
         <v>6</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>14</v>
@@ -4098,10 +4309,10 @@
         <v>6</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>14</v>
@@ -4115,10 +4326,10 @@
         <v>6</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>14</v>
@@ -4132,10 +4343,10 @@
         <v>6</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>14</v>
@@ -4149,10 +4360,10 @@
         <v>6</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>14</v>
@@ -4166,10 +4377,10 @@
         <v>6</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>14</v>
@@ -4183,10 +4394,10 @@
         <v>6</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>14</v>
@@ -4200,10 +4411,10 @@
         <v>6</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>14</v>
@@ -4217,10 +4428,10 @@
         <v>6</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>14</v>
@@ -4234,10 +4445,10 @@
         <v>6</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>14</v>
@@ -4251,10 +4462,10 @@
         <v>6</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>14</v>
@@ -4268,10 +4479,10 @@
         <v>6</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>14</v>
@@ -4285,10 +4496,10 @@
         <v>6</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>14</v>
@@ -4302,10 +4513,10 @@
         <v>6</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>14</v>
@@ -4319,10 +4530,10 @@
         <v>6</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>14</v>
@@ -4336,10 +4547,10 @@
         <v>6</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>14</v>
@@ -4353,10 +4564,10 @@
         <v>6</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>14</v>
@@ -4370,13 +4581,13 @@
         <v>6</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4387,13 +4598,13 @@
         <v>6</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4404,13 +4615,13 @@
         <v>6</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4421,13 +4632,13 @@
         <v>6</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4438,13 +4649,13 @@
         <v>6</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4455,13 +4666,13 @@
         <v>6</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4472,13 +4683,13 @@
         <v>6</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D180" s="6" t="s">
-        <v>151</v>
+        <v>179</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4489,13 +4700,13 @@
         <v>6</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D181" s="7" t="s">
-        <v>151</v>
+        <v>179</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4513,11 +4724,11 @@
       <c r="B183" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C183" s="8" t="s">
-        <v>152</v>
+      <c r="C183" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>14</v>
@@ -4530,11 +4741,11 @@
       <c r="B184" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C184" s="8" t="s">
-        <v>152</v>
+      <c r="C184" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>14</v>
@@ -4547,11 +4758,11 @@
       <c r="B185" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C185" s="8" t="s">
-        <v>152</v>
+      <c r="C185" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>14</v>
@@ -4564,11 +4775,11 @@
       <c r="B186" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C186" s="8" t="s">
-        <v>152</v>
+      <c r="C186" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>14</v>
@@ -4581,11 +4792,11 @@
       <c r="B187" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C187" s="8" t="s">
-        <v>152</v>
+      <c r="C187" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>14</v>
@@ -4598,11 +4809,11 @@
       <c r="B188" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C188" s="8" t="s">
-        <v>152</v>
+      <c r="C188" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>14</v>
@@ -4615,11 +4826,11 @@
       <c r="B189" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C189" s="8" t="s">
-        <v>152</v>
+      <c r="C189" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>14</v>
@@ -4632,11 +4843,11 @@
       <c r="B190" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C190" s="8" t="s">
-        <v>152</v>
+      <c r="C190" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>14</v>
@@ -4649,11 +4860,11 @@
       <c r="B191" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C191" s="8" t="s">
-        <v>152</v>
+      <c r="C191" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>14</v>
@@ -4666,11 +4877,11 @@
       <c r="B192" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C192" s="8" t="s">
-        <v>152</v>
+      <c r="C192" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>14</v>
@@ -4683,11 +4894,11 @@
       <c r="B193" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C193" s="8" t="s">
-        <v>152</v>
+      <c r="C193" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>14</v>
@@ -4700,11 +4911,11 @@
       <c r="B194" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C194" s="8" t="s">
-        <v>152</v>
+      <c r="C194" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>14</v>
@@ -4717,11 +4928,11 @@
       <c r="B195" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C195" s="8" t="s">
-        <v>152</v>
+      <c r="C195" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>14</v>
@@ -4734,11 +4945,11 @@
       <c r="B196" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C196" s="8" t="s">
-        <v>152</v>
+      <c r="C196" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>14</v>
@@ -4751,11 +4962,11 @@
       <c r="B197" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C197" s="8" t="s">
-        <v>152</v>
+      <c r="C197" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>14</v>
@@ -4768,11 +4979,11 @@
       <c r="B198" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C198" s="8" t="s">
-        <v>152</v>
+      <c r="C198" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>14</v>
@@ -4785,11 +4996,11 @@
       <c r="B199" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C199" s="8" t="s">
-        <v>152</v>
+      <c r="C199" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>14</v>
@@ -4802,11 +5013,11 @@
       <c r="B200" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C200" s="8" t="s">
-        <v>152</v>
+      <c r="C200" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>14</v>
@@ -4819,11 +5030,11 @@
       <c r="B201" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C201" s="8" t="s">
-        <v>152</v>
+      <c r="C201" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>14</v>
@@ -4836,11 +5047,11 @@
       <c r="B202" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C202" s="8" t="s">
-        <v>152</v>
+      <c r="C202" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>14</v>
@@ -4853,11 +5064,11 @@
       <c r="B203" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C203" s="8" t="s">
-        <v>152</v>
+      <c r="C203" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>14</v>
@@ -4871,13 +5082,13 @@
         <v>7</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4888,13 +5099,13 @@
         <v>7</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4905,13 +5116,13 @@
         <v>7</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4922,13 +5133,13 @@
         <v>7</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4939,13 +5150,13 @@
         <v>7</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4956,13 +5167,13 @@
         <v>7</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4973,13 +5184,13 @@
         <v>7</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4990,13 +5201,13 @@
         <v>7</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5023,10 +5234,10 @@
         <v>8</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>14</v>
@@ -5040,10 +5251,10 @@
         <v>8</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>14</v>
@@ -5057,10 +5268,10 @@
         <v>8</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>14</v>
@@ -5074,10 +5285,10 @@
         <v>8</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>14</v>
@@ -5091,10 +5302,10 @@
         <v>8</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>14</v>
@@ -5108,10 +5319,10 @@
         <v>8</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>14</v>
@@ -5125,10 +5336,10 @@
         <v>8</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>14</v>
@@ -5142,10 +5353,10 @@
         <v>8</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>14</v>
@@ -5159,10 +5370,10 @@
         <v>8</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>14</v>
@@ -5176,10 +5387,10 @@
         <v>8</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>14</v>
@@ -5193,10 +5404,10 @@
         <v>8</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>14</v>
@@ -5210,10 +5421,10 @@
         <v>8</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>14</v>
@@ -5227,10 +5438,10 @@
         <v>8</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>14</v>
@@ -5244,10 +5455,10 @@
         <v>8</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>14</v>
@@ -5261,10 +5472,10 @@
         <v>8</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>14</v>
@@ -5278,10 +5489,10 @@
         <v>8</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>14</v>
@@ -5295,10 +5506,10 @@
         <v>8</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>14</v>
@@ -5312,10 +5523,10 @@
         <v>8</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>14</v>
@@ -5329,10 +5540,10 @@
         <v>8</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>14</v>
@@ -5346,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>14</v>
@@ -5363,10 +5574,10 @@
         <v>8</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>14</v>
@@ -5380,13 +5591,13 @@
         <v>8</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5397,13 +5608,13 @@
         <v>8</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5414,13 +5625,13 @@
         <v>8</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5431,13 +5642,13 @@
         <v>8</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5448,13 +5659,13 @@
         <v>8</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5465,13 +5676,13 @@
         <v>8</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5482,13 +5693,13 @@
         <v>8</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5499,13 +5710,13 @@
         <v>8</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5532,10 +5743,10 @@
         <v>9</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>14</v>
@@ -5549,10 +5760,10 @@
         <v>9</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>14</v>
@@ -5566,10 +5777,10 @@
         <v>9</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>14</v>
@@ -5583,10 +5794,10 @@
         <v>9</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>14</v>
@@ -5600,10 +5811,10 @@
         <v>9</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>14</v>
@@ -5617,10 +5828,10 @@
         <v>9</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>14</v>
@@ -5634,10 +5845,10 @@
         <v>9</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>14</v>
@@ -5651,10 +5862,10 @@
         <v>9</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>14</v>
@@ -5668,10 +5879,10 @@
         <v>9</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>14</v>
@@ -5685,10 +5896,10 @@
         <v>9</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>14</v>
@@ -5702,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>14</v>
@@ -5719,10 +5930,10 @@
         <v>9</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>14</v>
@@ -5736,10 +5947,10 @@
         <v>9</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>14</v>
@@ -5753,10 +5964,10 @@
         <v>9</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>14</v>
@@ -5770,10 +5981,10 @@
         <v>9</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>14</v>
@@ -5787,10 +5998,10 @@
         <v>9</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>14</v>
@@ -5804,10 +6015,10 @@
         <v>9</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>14</v>
@@ -5821,10 +6032,10 @@
         <v>9</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>14</v>
@@ -5838,10 +6049,10 @@
         <v>9</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>14</v>
@@ -5855,10 +6066,10 @@
         <v>9</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>14</v>
@@ -5872,10 +6083,10 @@
         <v>9</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>14</v>
@@ -5889,10 +6100,10 @@
         <v>9</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>14</v>
@@ -5906,10 +6117,10 @@
         <v>9</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>14</v>
@@ -5923,13 +6134,13 @@
         <v>9</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5940,13 +6151,13 @@
         <v>9</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5957,13 +6168,13 @@
         <v>9</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5974,13 +6185,13 @@
         <v>9</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5991,13 +6202,13 @@
         <v>9</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6008,13 +6219,13 @@
         <v>9</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6034,10 +6245,10 @@
         <v>10</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -6051,10 +6262,10 @@
         <v>10</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -6068,10 +6279,10 @@
         <v>10</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -6085,10 +6296,10 @@
         <v>10</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -6102,10 +6313,10 @@
         <v>10</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -6119,10 +6330,10 @@
         <v>10</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -6136,10 +6347,10 @@
         <v>10</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -6153,10 +6364,10 @@
         <v>10</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -6170,10 +6381,10 @@
         <v>10</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -6187,10 +6398,10 @@
         <v>10</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -6204,10 +6415,10 @@
         <v>10</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -6221,10 +6432,10 @@
         <v>10</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -6238,10 +6449,10 @@
         <v>10</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -6255,10 +6466,10 @@
         <v>10</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>14</v>
@@ -6272,10 +6483,10 @@
         <v>10</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>14</v>
@@ -6289,10 +6500,10 @@
         <v>10</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>14</v>
@@ -6306,10 +6517,10 @@
         <v>10</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>14</v>
@@ -6323,10 +6534,10 @@
         <v>10</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>14</v>
@@ -6340,10 +6551,10 @@
         <v>10</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>14</v>
@@ -6357,10 +6568,10 @@
         <v>10</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>14</v>
@@ -6374,10 +6585,10 @@
         <v>10</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>14</v>
@@ -6391,13 +6602,13 @@
         <v>10</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6408,13 +6619,13 @@
         <v>10</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6425,13 +6636,13 @@
         <v>10</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6442,13 +6653,13 @@
         <v>10</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6459,13 +6670,13 @@
         <v>10</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6476,13 +6687,13 @@
         <v>10</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6493,13 +6704,13 @@
         <v>10</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6510,13 +6721,13 @@
         <v>10</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6543,10 +6754,10 @@
         <v>11</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>14</v>
@@ -6560,10 +6771,10 @@
         <v>11</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>14</v>
@@ -6577,10 +6788,10 @@
         <v>11</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>14</v>
@@ -6594,10 +6805,10 @@
         <v>11</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>14</v>
@@ -6611,10 +6822,10 @@
         <v>11</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>14</v>
@@ -6628,10 +6839,10 @@
         <v>11</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -6645,10 +6856,10 @@
         <v>11</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>14</v>
@@ -6662,10 +6873,10 @@
         <v>11</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>14</v>
@@ -6679,10 +6890,10 @@
         <v>11</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>14</v>
@@ -6696,10 +6907,10 @@
         <v>11</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -6713,10 +6924,10 @@
         <v>11</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -6730,10 +6941,10 @@
         <v>11</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -6747,10 +6958,10 @@
         <v>11</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -6764,10 +6975,10 @@
         <v>11</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -6781,10 +6992,10 @@
         <v>11</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -6798,10 +7009,10 @@
         <v>11</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -6815,10 +7026,10 @@
         <v>11</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -6832,10 +7043,10 @@
         <v>11</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -6849,10 +7060,10 @@
         <v>11</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -6866,10 +7077,10 @@
         <v>11</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -6883,10 +7094,10 @@
         <v>11</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -6900,13 +7111,13 @@
         <v>11</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6917,13 +7128,13 @@
         <v>11</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6934,13 +7145,13 @@
         <v>11</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6951,13 +7162,13 @@
         <v>11</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6968,13 +7179,13 @@
         <v>11</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6985,13 +7196,13 @@
         <v>11</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7002,13 +7213,13 @@
         <v>11</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7019,13 +7230,13 @@
         <v>11</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7045,10 +7256,10 @@
         <v>12</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -7062,10 +7273,10 @@
         <v>12</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -7079,10 +7290,10 @@
         <v>12</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
@@ -7096,10 +7307,10 @@
         <v>12</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
@@ -7113,10 +7324,10 @@
         <v>12</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -7130,10 +7341,10 @@
         <v>12</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
@@ -7147,10 +7358,10 @@
         <v>12</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
@@ -7164,10 +7375,10 @@
         <v>12</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
@@ -7181,10 +7392,10 @@
         <v>12</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>14</v>
@@ -7198,10 +7409,10 @@
         <v>12</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>14</v>
@@ -7215,10 +7426,10 @@
         <v>12</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>14</v>
@@ -7232,10 +7443,10 @@
         <v>12</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>14</v>
@@ -7249,10 +7460,10 @@
         <v>12</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>14</v>
@@ -7266,10 +7477,10 @@
         <v>12</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -7283,10 +7494,10 @@
         <v>12</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -7300,10 +7511,10 @@
         <v>12</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -7317,10 +7528,10 @@
         <v>12</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
@@ -7334,10 +7545,10 @@
         <v>12</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>14</v>
@@ -7351,10 +7562,10 @@
         <v>12</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
@@ -7368,10 +7579,10 @@
         <v>12</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
@@ -7385,10 +7596,10 @@
         <v>12</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
@@ -7402,13 +7613,13 @@
         <v>12</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7419,13 +7630,13 @@
         <v>12</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7436,13 +7647,13 @@
         <v>12</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7453,13 +7664,13 @@
         <v>12</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7470,13 +7681,13 @@
         <v>12</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7487,13 +7698,13 @@
         <v>12</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7504,13 +7715,13 @@
         <v>12</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7521,13 +7732,13 @@
         <v>12</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="218">
   <si>
     <t xml:space="preserve">Day</t>
   </si>
@@ -79,18 +79,21 @@
     <t xml:space="preserve">Explore children's right to healthcare, nutrition, and a safe environment.</t>
   </si>
   <si>
+    <t xml:space="preserve">/excelPDF/WardiResume.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/month1-day2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health and medical services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explain Article 24-26 in simple words (10-15mins), then let the child draw, repeat, or share it with the family.</t>
+  </si>
+  <si>
     <t xml:space="preserve">/example.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day2.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health and medical services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Article 24-26 in simple words (10-15mins), then let the child draw, repeat, or share it with the family.</t>
-  </si>
-  <si>
     <t xml:space="preserve">/images/lessons/month1-day3.jpg</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t xml:space="preserve">Explain Articles 19 and 20 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <t xml:space="preserve">              }}</t>
+  </si>
+  <si>
     <t xml:space="preserve">/images/lessons/month1-day6.jpg</t>
   </si>
   <si>
@@ -283,7 +289,11 @@
     <t xml:space="preserve">Ginisang munggo with malunggay and kalabasa is a nutritious Filipino dish rich in essential vitamins and minerals. Mung bean provides a good source of plant-based protein, dietary fiber, iron, and folate, which help support muscle growth, improve digestion, and prevent anemia. The addition of Moringa oleifera (malunggay) boosts the dish’s nutritional value because it is packed with Vitamin A, Vitamin C, calcium, iron, and antioxidants that strengthen immunity, promote healthy vision, and support strong bones. Meanwhile, Cucurbita moschata (kalabasa) supplies beta-carotene, fiber, and potassium, which help maintain good eyesight, heart health, and proper digestion. Together, these ingredients create a balanced, affordable, and nutrient-dense meal that supports overall health and well-being.</t>
   </si>
   <si>
-    <t xml:space="preserve">test</t>
+    <t xml:space="preserve">Kalabasa (Squash), Monggos (Mung Beans), and Malunggay (Moringa) are three common ingredients in Filipino cuisine that are not only affordable and accessible, but also highly nutritious. Together, they provide a powerful combination of vitamins, minerals, fiber, and plant-based protein that support overall health. Regularly including these foods in meals can help improve immunity, digestion, heart health, and energy levels.
+Kalabasa (squash) is rich in vitamin A in the form of beta-carotene, which is essential for good vision, healthy skin, and a strong immune system. Its bright orange color is a sign of its high antioxidant content, which helps protect the body from harmful free radicals. Kalabasa is also a good source of fiber, which supports healthy digestion and helps prevent constipation. Because it is naturally low in calories but filling, it can also help with maintaining a healthy weight.
+Monggos (mung beans) are an excellent source of plant-based protein, making them especially important for muscle repair and growth. They are rich in iron, which helps prevent anemia and supports healthy blood circulation. Monggos also contain fiber, potassium, and antioxidants that promote heart health by helping regulate blood pressure and cholesterol levels. Additionally, their complex carbohydrates provide steady energy, making them a great food for sustained strength throughout the day.
+Malunggay (moringa leaves) is often called a “superfood” because of its impressive nutritional profile. It contains high amounts of vitamins A, C, and E, which strengthen the immune system and protect cells from damage. Malunggay is also rich in calcium for strong bones, iron for healthy blood, and protein for tissue repair. Its anti-inflammatory and antioxidant properties may help reduce the risk of chronic diseases. When combined in dishes like monggos with malunggay and kalabasa, these ingredients create a balanced, nutrient-dense meal that supports overall health and well-being.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/month2-day1.jpg</t>
@@ -951,7 +961,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -972,12 +982,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="0"/>
     </font>
     <font>
@@ -1059,7 +1063,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1080,27 +1084,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1470,7 +1470,7 @@
         <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>14</v>
@@ -1479,7 +1479,7 @@
         <v>15</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1490,10 +1490,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>14</v>
@@ -1502,7 +1502,7 @@
         <v>15</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1513,10 +1513,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>14</v>
@@ -1525,7 +1525,7 @@
         <v>15</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1536,10 +1536,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>14</v>
@@ -1547,8 +1547,11 @@
       <c r="H7" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="J7" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="K7" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1559,10 +1562,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>14</v>
@@ -1571,7 +1574,7 @@
         <v>15</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1582,10 +1585,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
@@ -1594,7 +1597,7 @@
         <v>15</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1605,10 +1608,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>14</v>
@@ -1617,7 +1620,7 @@
         <v>15</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1628,10 +1631,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>14</v>
@@ -1640,7 +1643,7 @@
         <v>15</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1651,10 +1654,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>14</v>
@@ -1663,7 +1666,7 @@
         <v>15</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1674,10 +1677,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
@@ -1686,7 +1689,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1697,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>14</v>
@@ -1709,7 +1712,7 @@
         <v>15</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1720,10 +1723,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>
@@ -1732,7 +1735,7 @@
         <v>15</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1743,10 +1746,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>14</v>
@@ -1755,7 +1758,7 @@
         <v>15</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1766,10 +1769,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>14</v>
@@ -1778,7 +1781,7 @@
         <v>15</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1789,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>14</v>
@@ -1801,7 +1804,7 @@
         <v>15</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1812,10 +1815,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>14</v>
@@ -1824,7 +1827,7 @@
         <v>15</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1835,10 +1838,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>14</v>
@@ -1847,7 +1850,7 @@
         <v>15</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1858,10 +1861,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>14</v>
@@ -1870,7 +1873,7 @@
         <v>15</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1881,10 +1884,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>14</v>
@@ -1893,7 +1896,7 @@
         <v>15</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1981,28 +1984,28 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="81.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>1</v>
       </c>
@@ -2010,26 +2013,26 @@
         <v>2</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="E32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="G32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="6" t="b">
+      <c r="H32" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2040,23 +2043,23 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H33" s="6" t="b">
+      <c r="H33" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2067,20 +2070,20 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H34" s="6" t="b">
+      <c r="H34" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2091,20 +2094,20 @@
         <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="6" t="b">
+      <c r="H35" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2115,20 +2118,20 @@
         <v>2</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H36" s="6" t="b">
+      <c r="H36" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2139,20 +2142,20 @@
         <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="6" t="b">
+      <c r="H37" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2163,20 +2166,20 @@
         <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="6" t="b">
+      <c r="H38" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2187,20 +2190,20 @@
         <v>2</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="6" t="b">
+      <c r="H39" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2211,20 +2214,20 @@
         <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="6" t="b">
+      <c r="H40" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2235,20 +2238,20 @@
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="6" t="b">
+      <c r="H41" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2259,20 +2262,20 @@
         <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H42" s="6" t="b">
+      <c r="H42" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2283,20 +2286,20 @@
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="6" t="b">
+      <c r="H43" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2307,20 +2310,20 @@
         <v>2</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H44" s="6" t="b">
+      <c r="H44" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2331,20 +2334,20 @@
         <v>2</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="6" t="b">
+      <c r="H45" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2355,20 +2358,20 @@
         <v>2</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="6" t="b">
+      <c r="H46" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2379,20 +2382,20 @@
         <v>2</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H47" s="6" t="b">
+      <c r="H47" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2403,20 +2406,20 @@
         <v>2</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H48" s="6" t="b">
+      <c r="H48" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2427,20 +2430,20 @@
         <v>2</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H49" s="6" t="b">
+      <c r="H49" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2451,20 +2454,20 @@
         <v>2</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H50" s="6" t="b">
+      <c r="H50" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2475,20 +2478,20 @@
         <v>2</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="6" t="b">
+      <c r="H51" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2499,20 +2502,20 @@
         <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H52" s="6" t="b">
+      <c r="H52" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2523,12 +2526,12 @@
         <v>2</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H53" s="6" t="b">
+        <v>114</v>
+      </c>
+      <c r="H53" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2541,12 +2544,12 @@
         <v>2</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H54" s="6" t="b">
+        <v>114</v>
+      </c>
+      <c r="H54" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2559,12 +2562,12 @@
         <v>2</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H55" s="6" t="b">
+        <v>114</v>
+      </c>
+      <c r="H55" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2577,12 +2580,12 @@
         <v>2</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H56" s="6" t="b">
+        <v>117</v>
+      </c>
+      <c r="H56" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2595,12 +2598,12 @@
         <v>2</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H57" s="6" t="b">
+        <v>117</v>
+      </c>
+      <c r="H57" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2613,12 +2616,12 @@
         <v>2</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H58" s="6" t="b">
+        <v>117</v>
+      </c>
+      <c r="H58" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2630,7 +2633,7 @@
       <c r="B59" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="6" t="b">
+      <c r="H59" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2645,7 +2648,7 @@
       <c r="G60" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H60" s="6" t="b">
+      <c r="H60" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2658,23 +2661,23 @@
         <v>2</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H61" s="6" t="b">
+      <c r="H61" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2685,15 +2688,15 @@
         <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H62" s="6" t="b">
+      <c r="H62" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2706,15 +2709,15 @@
         <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H63" s="6" t="b">
+      <c r="H63" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2727,15 +2730,15 @@
         <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H64" s="6" t="b">
+      <c r="H64" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2748,15 +2751,15 @@
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H65" s="6" t="b">
+      <c r="H65" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2769,15 +2772,15 @@
         <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H66" s="6" t="b">
+      <c r="H66" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2790,15 +2793,15 @@
         <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H67" s="6" t="b">
+      <c r="H67" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2811,15 +2814,15 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H68" s="6" t="b">
+      <c r="H68" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2832,15 +2835,15 @@
         <v>3</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H69" s="6" t="b">
+      <c r="H69" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2853,15 +2856,15 @@
         <v>3</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H70" s="6" t="b">
+      <c r="H70" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2874,15 +2877,15 @@
         <v>3</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H71" s="6" t="b">
+      <c r="H71" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2895,15 +2898,15 @@
         <v>3</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H72" s="6" t="b">
+      <c r="H72" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2916,15 +2919,15 @@
         <v>3</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H73" s="6" t="b">
+      <c r="H73" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2937,15 +2940,15 @@
         <v>3</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H74" s="6" t="b">
+      <c r="H74" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2958,15 +2961,15 @@
         <v>3</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H75" s="6" t="b">
+      <c r="H75" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2979,15 +2982,15 @@
         <v>3</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H76" s="6" t="b">
+      <c r="H76" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3000,15 +3003,15 @@
         <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H77" s="6" t="b">
+      <c r="H77" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3021,15 +3024,15 @@
         <v>3</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H78" s="6" t="b">
+      <c r="H78" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3042,15 +3045,15 @@
         <v>3</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H79" s="6" t="b">
+      <c r="H79" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3063,15 +3066,15 @@
         <v>3</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H80" s="6" t="b">
+      <c r="H80" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3084,15 +3087,15 @@
         <v>3</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H81" s="6" t="b">
+      <c r="H81" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3105,15 +3108,15 @@
         <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H82" s="6" t="b">
+      <c r="H82" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3126,12 +3129,12 @@
         <v>3</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H83" s="6" t="b">
+        <v>114</v>
+      </c>
+      <c r="H83" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3144,12 +3147,12 @@
         <v>3</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H84" s="6" t="b">
+        <v>114</v>
+      </c>
+      <c r="H84" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3162,12 +3165,12 @@
         <v>3</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H85" s="6" t="b">
+        <v>114</v>
+      </c>
+      <c r="H85" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3180,12 +3183,12 @@
         <v>3</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H86" s="6" t="b">
+        <v>114</v>
+      </c>
+      <c r="H86" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3198,12 +3201,12 @@
         <v>3</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H87" s="6" t="b">
+        <v>114</v>
+      </c>
+      <c r="H87" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3216,12 +3219,12 @@
         <v>3</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H88" s="6" t="b">
+        <v>117</v>
+      </c>
+      <c r="H88" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3234,12 +3237,12 @@
         <v>3</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H89" s="6" t="b">
+        <v>117</v>
+      </c>
+      <c r="H89" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3252,12 +3255,12 @@
         <v>3</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H90" s="6" t="b">
+        <v>117</v>
+      </c>
+      <c r="H90" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3270,26 +3273,26 @@
         <v>3</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H91" s="6" t="b">
+      <c r="H91" s="5" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3300,10 +3303,10 @@
         <v>4</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3314,10 +3317,10 @@
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3328,10 +3331,10 @@
         <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3342,10 +3345,10 @@
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3356,10 +3359,10 @@
         <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3370,10 +3373,10 @@
         <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3384,10 +3387,10 @@
         <v>4</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3398,10 +3401,10 @@
         <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3412,10 +3415,10 @@
         <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3426,10 +3429,10 @@
         <v>4</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3440,10 +3443,10 @@
         <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3454,10 +3457,10 @@
         <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3468,10 +3471,10 @@
         <v>4</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3482,10 +3485,10 @@
         <v>4</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3496,10 +3499,10 @@
         <v>4</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3510,10 +3513,10 @@
         <v>4</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3524,10 +3527,10 @@
         <v>4</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3538,10 +3541,10 @@
         <v>4</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3552,10 +3555,10 @@
         <v>4</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3566,10 +3569,10 @@
         <v>4</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3580,10 +3583,10 @@
         <v>4</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3594,10 +3597,10 @@
         <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3608,10 +3611,10 @@
         <v>4</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E114" s="8" t="s">
         <v>161</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3622,10 +3625,10 @@
         <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3636,10 +3639,10 @@
         <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3650,10 +3653,10 @@
         <v>4</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3664,10 +3667,10 @@
         <v>4</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3678,10 +3681,10 @@
         <v>4</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3692,10 +3695,10 @@
         <v>4</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3714,10 +3717,10 @@
         <v>5</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>14</v>
@@ -3731,10 +3734,10 @@
         <v>5</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>14</v>
@@ -3748,10 +3751,10 @@
         <v>5</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>14</v>
@@ -3765,10 +3768,10 @@
         <v>5</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>14</v>
@@ -3782,10 +3785,10 @@
         <v>5</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>14</v>
@@ -3799,10 +3802,10 @@
         <v>5</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>14</v>
@@ -3816,10 +3819,10 @@
         <v>5</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>14</v>
@@ -3833,10 +3836,10 @@
         <v>5</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>14</v>
@@ -3850,10 +3853,10 @@
         <v>5</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>14</v>
@@ -3867,10 +3870,10 @@
         <v>5</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>14</v>
@@ -3884,10 +3887,10 @@
         <v>5</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>14</v>
@@ -3901,10 +3904,10 @@
         <v>5</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>14</v>
@@ -3918,10 +3921,10 @@
         <v>5</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>14</v>
@@ -3935,10 +3938,10 @@
         <v>5</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>14</v>
@@ -3952,10 +3955,10 @@
         <v>5</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>14</v>
@@ -3969,10 +3972,10 @@
         <v>5</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>14</v>
@@ -3986,10 +3989,10 @@
         <v>5</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>14</v>
@@ -4003,10 +4006,10 @@
         <v>5</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>14</v>
@@ -4020,10 +4023,10 @@
         <v>5</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>14</v>
@@ -4037,10 +4040,10 @@
         <v>5</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>14</v>
@@ -4054,10 +4057,10 @@
         <v>5</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>14</v>
@@ -4071,13 +4074,13 @@
         <v>5</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4088,13 +4091,13 @@
         <v>5</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4105,13 +4108,13 @@
         <v>5</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4122,13 +4125,13 @@
         <v>5</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4139,13 +4142,13 @@
         <v>5</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4156,13 +4159,13 @@
         <v>5</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4173,13 +4176,13 @@
         <v>5</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4190,13 +4193,13 @@
         <v>5</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4224,10 +4227,10 @@
         <v>6</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>14</v>
@@ -4241,10 +4244,10 @@
         <v>6</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>14</v>
@@ -4258,10 +4261,10 @@
         <v>6</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>14</v>
@@ -4275,10 +4278,10 @@
         <v>6</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>14</v>
@@ -4292,10 +4295,10 @@
         <v>6</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>14</v>
@@ -4309,10 +4312,10 @@
         <v>6</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>14</v>
@@ -4326,10 +4329,10 @@
         <v>6</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>14</v>
@@ -4343,10 +4346,10 @@
         <v>6</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>14</v>
@@ -4360,10 +4363,10 @@
         <v>6</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>14</v>
@@ -4377,10 +4380,10 @@
         <v>6</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>14</v>
@@ -4394,10 +4397,10 @@
         <v>6</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>14</v>
@@ -4411,10 +4414,10 @@
         <v>6</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>14</v>
@@ -4428,10 +4431,10 @@
         <v>6</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>14</v>
@@ -4445,10 +4448,10 @@
         <v>6</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>14</v>
@@ -4462,10 +4465,10 @@
         <v>6</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>14</v>
@@ -4479,10 +4482,10 @@
         <v>6</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>14</v>
@@ -4496,10 +4499,10 @@
         <v>6</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>14</v>
@@ -4513,10 +4516,10 @@
         <v>6</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>14</v>
@@ -4530,10 +4533,10 @@
         <v>6</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>14</v>
@@ -4547,10 +4550,10 @@
         <v>6</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>14</v>
@@ -4564,10 +4567,10 @@
         <v>6</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>14</v>
@@ -4581,13 +4584,13 @@
         <v>6</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4598,13 +4601,13 @@
         <v>6</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4615,13 +4618,13 @@
         <v>6</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4632,13 +4635,13 @@
         <v>6</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4649,13 +4652,13 @@
         <v>6</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4666,13 +4669,13 @@
         <v>6</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4683,13 +4686,13 @@
         <v>6</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D180" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>182</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4700,13 +4703,13 @@
         <v>6</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4724,11 +4727,11 @@
       <c r="B183" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C183" s="10" t="s">
-        <v>181</v>
+      <c r="C183" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>14</v>
@@ -4741,11 +4744,11 @@
       <c r="B184" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C184" s="10" t="s">
-        <v>181</v>
+      <c r="C184" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>14</v>
@@ -4758,11 +4761,11 @@
       <c r="B185" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C185" s="10" t="s">
-        <v>181</v>
+      <c r="C185" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>14</v>
@@ -4775,11 +4778,11 @@
       <c r="B186" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C186" s="10" t="s">
-        <v>181</v>
+      <c r="C186" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>14</v>
@@ -4792,11 +4795,11 @@
       <c r="B187" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C187" s="10" t="s">
-        <v>181</v>
+      <c r="C187" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>14</v>
@@ -4809,11 +4812,11 @@
       <c r="B188" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C188" s="10" t="s">
-        <v>181</v>
+      <c r="C188" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>14</v>
@@ -4826,11 +4829,11 @@
       <c r="B189" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C189" s="10" t="s">
-        <v>181</v>
+      <c r="C189" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>14</v>
@@ -4843,11 +4846,11 @@
       <c r="B190" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C190" s="10" t="s">
-        <v>181</v>
+      <c r="C190" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>14</v>
@@ -4860,11 +4863,11 @@
       <c r="B191" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C191" s="10" t="s">
-        <v>181</v>
+      <c r="C191" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>14</v>
@@ -4877,11 +4880,11 @@
       <c r="B192" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C192" s="10" t="s">
-        <v>181</v>
+      <c r="C192" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>14</v>
@@ -4894,11 +4897,11 @@
       <c r="B193" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C193" s="10" t="s">
-        <v>181</v>
+      <c r="C193" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>14</v>
@@ -4911,11 +4914,11 @@
       <c r="B194" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C194" s="10" t="s">
-        <v>181</v>
+      <c r="C194" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>14</v>
@@ -4928,11 +4931,11 @@
       <c r="B195" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C195" s="10" t="s">
-        <v>181</v>
+      <c r="C195" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>14</v>
@@ -4945,11 +4948,11 @@
       <c r="B196" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C196" s="10" t="s">
-        <v>181</v>
+      <c r="C196" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>14</v>
@@ -4962,11 +4965,11 @@
       <c r="B197" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C197" s="10" t="s">
-        <v>181</v>
+      <c r="C197" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>14</v>
@@ -4979,11 +4982,11 @@
       <c r="B198" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C198" s="10" t="s">
-        <v>181</v>
+      <c r="C198" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>14</v>
@@ -4996,11 +4999,11 @@
       <c r="B199" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C199" s="10" t="s">
-        <v>181</v>
+      <c r="C199" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>14</v>
@@ -5013,11 +5016,11 @@
       <c r="B200" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C200" s="10" t="s">
-        <v>181</v>
+      <c r="C200" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>14</v>
@@ -5030,11 +5033,11 @@
       <c r="B201" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C201" s="10" t="s">
-        <v>181</v>
+      <c r="C201" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>14</v>
@@ -5047,11 +5050,11 @@
       <c r="B202" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C202" s="10" t="s">
-        <v>181</v>
+      <c r="C202" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>14</v>
@@ -5064,11 +5067,11 @@
       <c r="B203" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C203" s="10" t="s">
-        <v>181</v>
+      <c r="C203" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>14</v>
@@ -5082,13 +5085,13 @@
         <v>7</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5099,13 +5102,13 @@
         <v>7</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5116,13 +5119,13 @@
         <v>7</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5133,13 +5136,13 @@
         <v>7</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5150,13 +5153,13 @@
         <v>7</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5167,13 +5170,13 @@
         <v>7</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5184,13 +5187,13 @@
         <v>7</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5201,13 +5204,13 @@
         <v>7</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5234,10 +5237,10 @@
         <v>8</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>14</v>
@@ -5251,10 +5254,10 @@
         <v>8</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>14</v>
@@ -5268,10 +5271,10 @@
         <v>8</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>14</v>
@@ -5285,10 +5288,10 @@
         <v>8</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>14</v>
@@ -5302,10 +5305,10 @@
         <v>8</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>14</v>
@@ -5319,10 +5322,10 @@
         <v>8</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>14</v>
@@ -5336,10 +5339,10 @@
         <v>8</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>14</v>
@@ -5353,10 +5356,10 @@
         <v>8</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>14</v>
@@ -5370,10 +5373,10 @@
         <v>8</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>14</v>
@@ -5387,10 +5390,10 @@
         <v>8</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>14</v>
@@ -5404,10 +5407,10 @@
         <v>8</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>14</v>
@@ -5421,10 +5424,10 @@
         <v>8</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>14</v>
@@ -5438,10 +5441,10 @@
         <v>8</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>14</v>
@@ -5455,10 +5458,10 @@
         <v>8</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>14</v>
@@ -5472,10 +5475,10 @@
         <v>8</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>14</v>
@@ -5489,10 +5492,10 @@
         <v>8</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>14</v>
@@ -5506,10 +5509,10 @@
         <v>8</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>14</v>
@@ -5523,10 +5526,10 @@
         <v>8</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>14</v>
@@ -5540,10 +5543,10 @@
         <v>8</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>14</v>
@@ -5557,10 +5560,10 @@
         <v>8</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>14</v>
@@ -5574,10 +5577,10 @@
         <v>8</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>14</v>
@@ -5591,13 +5594,13 @@
         <v>8</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5608,13 +5611,13 @@
         <v>8</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5625,13 +5628,13 @@
         <v>8</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5642,13 +5645,13 @@
         <v>8</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5659,13 +5662,13 @@
         <v>8</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5676,13 +5679,13 @@
         <v>8</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5693,13 +5696,13 @@
         <v>8</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5710,13 +5713,13 @@
         <v>8</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5743,10 +5746,10 @@
         <v>9</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>14</v>
@@ -5760,10 +5763,10 @@
         <v>9</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>14</v>
@@ -5777,10 +5780,10 @@
         <v>9</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>14</v>
@@ -5794,10 +5797,10 @@
         <v>9</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>14</v>
@@ -5811,10 +5814,10 @@
         <v>9</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>14</v>
@@ -5828,10 +5831,10 @@
         <v>9</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>14</v>
@@ -5845,10 +5848,10 @@
         <v>9</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>14</v>
@@ -5862,10 +5865,10 @@
         <v>9</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>14</v>
@@ -5879,10 +5882,10 @@
         <v>9</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>14</v>
@@ -5896,10 +5899,10 @@
         <v>9</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>14</v>
@@ -5913,10 +5916,10 @@
         <v>9</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>14</v>
@@ -5930,10 +5933,10 @@
         <v>9</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>14</v>
@@ -5947,10 +5950,10 @@
         <v>9</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>14</v>
@@ -5964,10 +5967,10 @@
         <v>9</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>14</v>
@@ -5981,10 +5984,10 @@
         <v>9</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>14</v>
@@ -5998,10 +6001,10 @@
         <v>9</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>14</v>
@@ -6015,10 +6018,10 @@
         <v>9</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>14</v>
@@ -6032,10 +6035,10 @@
         <v>9</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>14</v>
@@ -6049,10 +6052,10 @@
         <v>9</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>14</v>
@@ -6066,10 +6069,10 @@
         <v>9</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>14</v>
@@ -6083,10 +6086,10 @@
         <v>9</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>14</v>
@@ -6100,10 +6103,10 @@
         <v>9</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>14</v>
@@ -6117,10 +6120,10 @@
         <v>9</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>14</v>
@@ -6134,13 +6137,13 @@
         <v>9</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6151,13 +6154,13 @@
         <v>9</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6168,13 +6171,13 @@
         <v>9</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6185,13 +6188,13 @@
         <v>9</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6202,13 +6205,13 @@
         <v>9</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6219,13 +6222,13 @@
         <v>9</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6245,10 +6248,10 @@
         <v>10</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -6262,10 +6265,10 @@
         <v>10</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -6279,10 +6282,10 @@
         <v>10</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -6296,10 +6299,10 @@
         <v>10</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -6313,10 +6316,10 @@
         <v>10</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -6330,10 +6333,10 @@
         <v>10</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -6347,10 +6350,10 @@
         <v>10</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -6364,10 +6367,10 @@
         <v>10</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -6381,10 +6384,10 @@
         <v>10</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -6398,10 +6401,10 @@
         <v>10</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -6415,10 +6418,10 @@
         <v>10</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -6432,10 +6435,10 @@
         <v>10</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -6449,10 +6452,10 @@
         <v>10</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -6466,10 +6469,10 @@
         <v>10</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>14</v>
@@ -6483,10 +6486,10 @@
         <v>10</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>14</v>
@@ -6500,10 +6503,10 @@
         <v>10</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>14</v>
@@ -6517,10 +6520,10 @@
         <v>10</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>14</v>
@@ -6534,10 +6537,10 @@
         <v>10</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>14</v>
@@ -6551,10 +6554,10 @@
         <v>10</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>14</v>
@@ -6568,10 +6571,10 @@
         <v>10</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>14</v>
@@ -6585,10 +6588,10 @@
         <v>10</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>14</v>
@@ -6602,13 +6605,13 @@
         <v>10</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6619,13 +6622,13 @@
         <v>10</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6636,13 +6639,13 @@
         <v>10</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6653,13 +6656,13 @@
         <v>10</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6670,13 +6673,13 @@
         <v>10</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6687,13 +6690,13 @@
         <v>10</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6704,13 +6707,13 @@
         <v>10</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6721,13 +6724,13 @@
         <v>10</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6754,10 +6757,10 @@
         <v>11</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>14</v>
@@ -6771,10 +6774,10 @@
         <v>11</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>14</v>
@@ -6788,10 +6791,10 @@
         <v>11</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>14</v>
@@ -6805,10 +6808,10 @@
         <v>11</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>14</v>
@@ -6822,10 +6825,10 @@
         <v>11</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>14</v>
@@ -6839,10 +6842,10 @@
         <v>11</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -6856,10 +6859,10 @@
         <v>11</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>14</v>
@@ -6873,10 +6876,10 @@
         <v>11</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>14</v>
@@ -6890,10 +6893,10 @@
         <v>11</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>14</v>
@@ -6907,10 +6910,10 @@
         <v>11</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -6924,10 +6927,10 @@
         <v>11</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -6941,10 +6944,10 @@
         <v>11</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -6958,10 +6961,10 @@
         <v>11</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -6975,10 +6978,10 @@
         <v>11</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -6992,10 +6995,10 @@
         <v>11</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -7009,10 +7012,10 @@
         <v>11</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -7026,10 +7029,10 @@
         <v>11</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -7043,10 +7046,10 @@
         <v>11</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -7060,10 +7063,10 @@
         <v>11</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -7077,10 +7080,10 @@
         <v>11</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -7094,10 +7097,10 @@
         <v>11</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -7111,13 +7114,13 @@
         <v>11</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7128,13 +7131,13 @@
         <v>11</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7145,13 +7148,13 @@
         <v>11</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7162,13 +7165,13 @@
         <v>11</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7179,13 +7182,13 @@
         <v>11</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7196,13 +7199,13 @@
         <v>11</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7213,13 +7216,13 @@
         <v>11</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7230,13 +7233,13 @@
         <v>11</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7256,10 +7259,10 @@
         <v>12</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -7273,10 +7276,10 @@
         <v>12</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -7290,10 +7293,10 @@
         <v>12</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
@@ -7307,10 +7310,10 @@
         <v>12</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
@@ -7324,10 +7327,10 @@
         <v>12</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -7341,10 +7344,10 @@
         <v>12</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
@@ -7358,10 +7361,10 @@
         <v>12</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
@@ -7375,10 +7378,10 @@
         <v>12</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
@@ -7392,10 +7395,10 @@
         <v>12</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>14</v>
@@ -7409,10 +7412,10 @@
         <v>12</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>14</v>
@@ -7426,10 +7429,10 @@
         <v>12</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>14</v>
@@ -7443,10 +7446,10 @@
         <v>12</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>14</v>
@@ -7460,10 +7463,10 @@
         <v>12</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>14</v>
@@ -7477,10 +7480,10 @@
         <v>12</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -7494,10 +7497,10 @@
         <v>12</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -7511,10 +7514,10 @@
         <v>12</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -7528,10 +7531,10 @@
         <v>12</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
@@ -7545,10 +7548,10 @@
         <v>12</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>14</v>
@@ -7562,10 +7565,10 @@
         <v>12</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
@@ -7579,10 +7582,10 @@
         <v>12</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
@@ -7596,10 +7599,10 @@
         <v>12</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
@@ -7613,13 +7616,13 @@
         <v>12</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7630,13 +7633,13 @@
         <v>12</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7647,13 +7650,13 @@
         <v>12</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7664,13 +7667,13 @@
         <v>12</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7681,13 +7684,13 @@
         <v>12</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7698,13 +7701,13 @@
         <v>12</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7715,13 +7718,13 @@
         <v>12</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7732,13 +7735,13 @@
         <v>12</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="250">
   <si>
     <t xml:space="preserve">Day</t>
   </si>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">FALSE</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day1.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day1.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Responsibility of parents</t>
@@ -82,7 +82,36 @@
     <t xml:space="preserve">/excelPDF/WardiResume.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day2.jpg</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">/images/lessons/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jan/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">month1-day2.jpg</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Health and medical services</t>
@@ -94,7 +123,36 @@
     <t xml:space="preserve">/example.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day3.jpg</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">/images/lessons/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jan/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">month1-day3.jpg</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Standard of living</t>
@@ -103,7 +161,36 @@
     <t xml:space="preserve">Explain Articles 27 and 31  in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day4.jpg</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">/images/lessons/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">jan/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">month1-day4.jpg</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Non-discrimination</t>
@@ -112,7 +199,7 @@
     <t xml:space="preserve">Explain Articles 2 and 11 in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day5.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day5.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Protection from abuse</t>
@@ -124,7 +211,7 @@
     <t xml:space="preserve">              }}</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day6.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day6.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Refugee children</t>
@@ -133,7 +220,7 @@
     <t xml:space="preserve">Explain Articles 22 and 25 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day7.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day7.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Child labour</t>
@@ -142,7 +229,7 @@
     <t xml:space="preserve">Explain Articles 32 and 33 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day8.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day8.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Protection from sexual exploitation</t>
@@ -151,7 +238,7 @@
     <t xml:space="preserve">Explain Articles 34 and 35 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day9.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day9.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Protection from all other forms of exploitation</t>
@@ -160,7 +247,7 @@
     <t xml:space="preserve">Explain Articles 36 and 37 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day10.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day10.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">War and armed conflict</t>
@@ -169,7 +256,7 @@
     <t xml:space="preserve">Explain Articles 38 and 39 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day11.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day11.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Juvenile justice</t>
@@ -178,7 +265,7 @@
     <t xml:space="preserve">Explain Article 40 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day12.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day12.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Respect for parental rights</t>
@@ -187,7 +274,7 @@
     <t xml:space="preserve">Explain Articles 5 and 7 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day13.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day13.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Protection of identity</t>
@@ -196,7 +283,7 @@
     <t xml:space="preserve">Explain Articles 8 and 10 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day14.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day14.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Adoption</t>
@@ -205,7 +292,7 @@
     <t xml:space="preserve">Explain Articles 21 and 23 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day15.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day15.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Disabled children</t>
@@ -214,7 +301,7 @@
     <t xml:space="preserve">Explain Articles 28 and 29 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day16.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day16.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Educational aims</t>
@@ -223,7 +310,7 @@
     <t xml:space="preserve">Explain Article 30 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day17.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day17.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">The well-being of the child is paramount</t>
@@ -232,7 +319,7 @@
     <t xml:space="preserve">Explain Article 3 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day18.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day18.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Freedom of opinion</t>
@@ -241,7 +328,7 @@
     <t xml:space="preserve">Explain Articles 12 and 13 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day19.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day19.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Freedom of thought, conscience, and religion</t>
@@ -250,7 +337,7 @@
     <t xml:space="preserve">Explain Articles 14 and 15 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day20.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day20.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Protection of privacy</t>
@@ -259,7 +346,7 @@
     <t xml:space="preserve">Explain Articles 16 and 17 in simple words (10–15 mins), then let the child draw, repeat, or share it with family</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month1-day21.jpg</t>
+    <t xml:space="preserve">/images/lessons/jan/month1-day21.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">REWARD DAY - Gauntlets of Safety</t>
@@ -296,7 +383,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month2-day1.jpg</t>
+    <t xml:space="preserve">/images/lessons/feb/day1.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Add malunggay leaves to tinola, munggo,or instant noodles.</t>
@@ -309,7 +396,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month2-day2.jpg</t>
+    <t xml:space="preserve">/images/lessons/feb/day2.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Add boiled egg (split in half if budget is tight)</t>
@@ -318,7 +405,7 @@
     <t xml:space="preserve">Contains protein</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month2-day3.jpg</t>
+    <t xml:space="preserve">/images/lessons/feb/day3.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Add banana (saging na saba or lakatan) for dessert or merienda</t>
@@ -327,7 +414,7 @@
     <t xml:space="preserve">Rich in fiber and potassium</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month2-day4.jpg</t>
+    <t xml:space="preserve">/images/lessons/feb/day4.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Add dilis (small dried fish) with egg fried rice.</t>
@@ -336,7 +423,7 @@
     <t xml:space="preserve">Rich in calcium</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month2-day5.jpg</t>
+    <t xml:space="preserve">/images/lessons/feb/day5.jpg</t>
   </si>
   <si>
     <t xml:space="preserve"> Add kamote (sweet potato) boiled or fried. </t>
@@ -345,7 +432,7 @@
     <t xml:space="preserve">Contains carbs</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month2-day6.jpg</t>
+    <t xml:space="preserve">/images/lessons/feb/day6.jpg</t>
   </si>
   <si>
     <t xml:space="preserve"> Add gabi/taro or squash to a simple sabaw </t>
@@ -355,16 +442,55 @@
  and E</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month2-day7.jpg</t>
+    <t xml:space="preserve">/images/lessons/feb/day7.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day8.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Add malunggay leaves to tinola, munggo,or intant noodles.</t>
   </si>
   <si>
-    <t xml:space="preserve">/images/lessons/month2-day1.jpeg</t>
+    <t xml:space="preserve">/images/lessons/feb/day9.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day10.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day11.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day12.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day13.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day14.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day15.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day16.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day17.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day18.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day19.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day20.jpg</t>
   </si>
   <si>
     <t xml:space="preserve"> Contains Vitamin C and E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day21.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Take a  Family Meal Photo
@@ -406,42 +532,63 @@
     <t xml:space="preserve">Family Praise</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/mar/day1.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Have your child show one coloring page from DICE. The parent will then say “Wow, you made it so colorful! Good job!”</t>
   </si>
   <si>
     <t xml:space="preserve">Coloring Pride</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/mar/day2.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Have your child read at least three words from a book. Repeat the words together with your child and give them a thumbs-up.</t>
   </si>
   <si>
     <t xml:space="preserve">Reading Together</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/mar/day3.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Let your child write a name or a letter on a paper. Trace it, and smile to show appreciation to your child’s work.</t>
   </si>
   <si>
     <t xml:space="preserve">Writing Practice</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/mar/day4.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Count 5 things at home (spoons, buttons, coins, or their fingers) with your child and clap when the child finishes.</t>
   </si>
   <si>
     <t xml:space="preserve">Counting Fun</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/mar/day5.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Let you child share one thing they learned or did at DICE today. Just listen and respons with, “Wow, I’m proud of you”</t>
   </si>
   <si>
     <t xml:space="preserve"> Story Telling</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/mar/day6.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Have your child draw one simple thing (house, sun, flower, or stick figure) Guess what it is, then say, “That’s a nice drawing!”</t>
   </si>
   <si>
     <t xml:space="preserve">Drawing Day</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/mar/day7.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Each child shares one thing they learned in DICE (e.g., coloring, reading, counting, writing). Family members then respond with claps or a thumbs up.</t>
   </si>
   <si>
@@ -463,6 +610,9 @@
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 2 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/apr/1.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 3 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
   </si>
   <si>
@@ -475,15 +625,24 @@
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 6 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/apr/5.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 7 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/apr/3.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 8 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
   </si>
   <si>
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 9 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/apr/2.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 10 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
   </si>
   <si>
@@ -503,6 +662,9 @@
   </si>
   <si>
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 16 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/apr/4.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">where each day, parents limit screen time on her family (e.g., only 17 hours for non-school use) and instead do one offline productive activity (drawing, reading, helping with chores, karaoke bonding etc.). They will record what they did in a Digital Journal on the app.</t>
@@ -639,6 +801,9 @@
     <t xml:space="preserve">Prepare a savings jar with the money tracker. Drop a money every day and mark check on the tracker.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/may/may.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">#NoGambling</t>
   </si>
   <si>
@@ -655,6 +820,24 @@
   </si>
   <si>
     <t xml:space="preserve">The parents and the kids will write one positive phrase about themselves. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/june/1.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/june/2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/june/5.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/june/3.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/june/6.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/june/4.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Family Advice Corner</t>
@@ -961,7 +1144,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1017,6 +1200,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1063,7 +1252,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1096,11 +1285,15 @@
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2005,7 +2198,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="81.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>1</v>
       </c>
@@ -2203,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2214,7 +2407,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>92</v>
@@ -2227,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2251,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2275,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2299,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2323,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2347,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2371,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2382,7 +2575,7 @@
         <v>2</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>92</v>
@@ -2395,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2419,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2443,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2467,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2491,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2505,7 +2698,7 @@
         <v>107</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>14</v>
@@ -2515,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2526,10 +2719,10 @@
         <v>2</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H53" s="5" t="b">
         <f aca="false">FALSE()</f>
@@ -2544,10 +2737,10 @@
         <v>2</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H54" s="5" t="b">
         <f aca="false">FALSE()</f>
@@ -2562,10 +2755,10 @@
         <v>2</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H55" s="5" t="b">
         <f aca="false">FALSE()</f>
@@ -2580,10 +2773,10 @@
         <v>2</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H56" s="5" t="b">
         <f aca="false">FALSE()</f>
@@ -2598,10 +2791,10 @@
         <v>2</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H57" s="5" t="b">
         <f aca="false">FALSE()</f>
@@ -2616,10 +2809,10 @@
         <v>2</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H58" s="5" t="b">
         <f aca="false">FALSE()</f>
@@ -2661,10 +2854,10 @@
         <v>2</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>14</v>
@@ -2688,10 +2881,10 @@
         <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>14</v>
@@ -2700,6 +2893,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K62" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
@@ -2709,10 +2905,10 @@
         <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>14</v>
@@ -2721,6 +2917,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K63" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
@@ -2730,10 +2929,10 @@
         <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>14</v>
@@ -2742,6 +2941,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K64" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="n">
@@ -2751,10 +2953,10 @@
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>14</v>
@@ -2763,6 +2965,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K65" s="1" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
@@ -2772,10 +2977,10 @@
         <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>14</v>
@@ -2784,6 +2989,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K66" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
@@ -2793,10 +3001,10 @@
         <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>14</v>
@@ -2805,6 +3013,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K67" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
@@ -2814,10 +3025,10 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>14</v>
@@ -2826,6 +3037,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K68" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
@@ -2835,10 +3049,10 @@
         <v>3</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>14</v>
@@ -2847,6 +3061,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K69" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
@@ -2856,10 +3073,10 @@
         <v>3</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>14</v>
@@ -2868,6 +3085,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K70" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
@@ -2877,10 +3097,10 @@
         <v>3</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>14</v>
@@ -2889,6 +3109,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K71" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="n">
@@ -2898,10 +3121,10 @@
         <v>3</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>14</v>
@@ -2910,6 +3133,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K72" s="1" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="n">
@@ -2919,10 +3145,10 @@
         <v>3</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>14</v>
@@ -2931,6 +3157,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K73" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
@@ -2940,10 +3169,10 @@
         <v>3</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>14</v>
@@ -2952,6 +3181,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K74" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
@@ -2961,10 +3193,10 @@
         <v>3</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>14</v>
@@ -2973,6 +3205,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K75" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
@@ -2982,10 +3217,10 @@
         <v>3</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>14</v>
@@ -2994,6 +3229,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K76" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
@@ -3003,10 +3241,10 @@
         <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>14</v>
@@ -3015,6 +3253,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K77" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
@@ -3024,10 +3265,10 @@
         <v>3</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>14</v>
@@ -3036,6 +3277,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K78" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="n">
@@ -3045,10 +3289,10 @@
         <v>3</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>14</v>
@@ -3057,6 +3301,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K79" s="1" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
@@ -3066,10 +3313,10 @@
         <v>3</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>14</v>
@@ -3078,6 +3325,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K80" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
@@ -3087,10 +3337,10 @@
         <v>3</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>14</v>
@@ -3099,6 +3349,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K81" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
@@ -3108,10 +3361,10 @@
         <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>14</v>
@@ -3120,6 +3373,9 @@
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K82" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="n">
@@ -3129,15 +3385,18 @@
         <v>3</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H83" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K83" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="n">
@@ -3147,15 +3406,18 @@
         <v>3</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H84" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K84" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
@@ -3165,15 +3427,18 @@
         <v>3</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H85" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K85" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
@@ -3183,15 +3448,18 @@
         <v>3</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H86" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K86" s="1" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
@@ -3201,15 +3469,18 @@
         <v>3</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H87" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K87" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="n">
@@ -3219,15 +3490,18 @@
         <v>3</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H88" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K88" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="n">
@@ -3237,15 +3511,18 @@
         <v>3</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H89" s="5" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="K89" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="n">
@@ -3255,10 +3532,10 @@
         <v>3</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H90" s="5" t="b">
         <f aca="false">FALSE()</f>
@@ -3273,13 +3550,13 @@
         <v>3</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>14</v>
@@ -3303,10 +3580,13 @@
         <v>4</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>140</v>
+        <v>160</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3317,10 +3597,13 @@
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>141</v>
+        <v>162</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3331,10 +3614,13 @@
         <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>142</v>
+        <v>163</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3345,10 +3631,13 @@
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>143</v>
+        <v>164</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3359,10 +3648,13 @@
         <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3373,10 +3665,13 @@
         <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>145</v>
+        <v>167</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3387,10 +3682,13 @@
         <v>4</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>146</v>
+        <v>169</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3401,10 +3699,13 @@
         <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>147</v>
+        <v>170</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3415,10 +3716,13 @@
         <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>148</v>
+        <v>172</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3429,10 +3733,13 @@
         <v>4</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>149</v>
+        <v>173</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3443,10 +3750,13 @@
         <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>150</v>
+        <v>174</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3457,10 +3767,13 @@
         <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>151</v>
+        <v>175</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3471,10 +3784,13 @@
         <v>4</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>152</v>
+        <v>176</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3485,10 +3801,13 @@
         <v>4</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>153</v>
+        <v>177</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3499,10 +3818,13 @@
         <v>4</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>154</v>
+        <v>178</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3513,10 +3835,13 @@
         <v>4</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>155</v>
+        <v>180</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3527,10 +3852,13 @@
         <v>4</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>156</v>
+        <v>181</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3541,10 +3869,13 @@
         <v>4</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>157</v>
+        <v>182</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3555,10 +3886,13 @@
         <v>4</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>158</v>
+        <v>183</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3569,10 +3903,13 @@
         <v>4</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>159</v>
+        <v>184</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3583,10 +3920,13 @@
         <v>4</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>160</v>
+        <v>185</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3597,10 +3937,10 @@
         <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3611,10 +3951,10 @@
         <v>4</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3625,10 +3965,10 @@
         <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3639,10 +3979,10 @@
         <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3653,10 +3993,10 @@
         <v>4</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3667,10 +4007,10 @@
         <v>4</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3681,10 +4021,10 @@
         <v>4</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3695,10 +4035,10 @@
         <v>4</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3717,13 +4057,16 @@
         <v>5</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3734,13 +4077,16 @@
         <v>5</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3751,13 +4097,16 @@
         <v>5</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3768,13 +4117,16 @@
         <v>5</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3785,13 +4137,16 @@
         <v>5</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3802,13 +4157,16 @@
         <v>5</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3819,13 +4177,16 @@
         <v>5</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3836,13 +4197,16 @@
         <v>5</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3853,13 +4217,16 @@
         <v>5</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3870,13 +4237,16 @@
         <v>5</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3887,13 +4257,16 @@
         <v>5</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3904,13 +4277,16 @@
         <v>5</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3921,13 +4297,16 @@
         <v>5</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3938,13 +4317,16 @@
         <v>5</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3955,13 +4337,16 @@
         <v>5</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3972,13 +4357,16 @@
         <v>5</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3989,13 +4377,16 @@
         <v>5</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4006,13 +4397,16 @@
         <v>5</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4023,13 +4417,16 @@
         <v>5</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4040,13 +4437,16 @@
         <v>5</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4057,10 +4457,10 @@
         <v>5</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>14</v>
@@ -4074,13 +4474,13 @@
         <v>5</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4091,13 +4491,13 @@
         <v>5</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4108,13 +4508,13 @@
         <v>5</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4125,13 +4525,13 @@
         <v>5</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4142,13 +4542,13 @@
         <v>5</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4159,13 +4559,13 @@
         <v>5</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4176,13 +4576,13 @@
         <v>5</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4193,13 +4593,13 @@
         <v>5</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4227,13 +4627,16 @@
         <v>6</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4244,13 +4647,16 @@
         <v>6</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K154" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4261,13 +4667,16 @@
         <v>6</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K155" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4278,13 +4687,16 @@
         <v>6</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K156" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4295,13 +4707,16 @@
         <v>6</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K157" s="8" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4312,13 +4727,16 @@
         <v>6</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K158" s="8" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4329,13 +4747,16 @@
         <v>6</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K159" s="8" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4346,13 +4767,16 @@
         <v>6</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K160" s="8" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4363,13 +4787,16 @@
         <v>6</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K161" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4380,13 +4807,16 @@
         <v>6</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K162" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4397,13 +4827,16 @@
         <v>6</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K163" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4414,13 +4847,16 @@
         <v>6</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K164" s="8" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4431,13 +4867,16 @@
         <v>6</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K165" s="8" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4448,13 +4887,16 @@
         <v>6</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K166" s="8" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4465,13 +4907,16 @@
         <v>6</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K167" s="8" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4482,13 +4927,16 @@
         <v>6</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K168" s="8" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4499,13 +4947,16 @@
         <v>6</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K169" s="8" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4516,13 +4967,16 @@
         <v>6</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K170" s="8" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4533,13 +4987,16 @@
         <v>6</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K171" s="8" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4550,13 +5007,16 @@
         <v>6</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K172" s="8" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4567,13 +5027,16 @@
         <v>6</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K173" s="8" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4584,13 +5047,13 @@
         <v>6</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4601,13 +5064,13 @@
         <v>6</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4618,13 +5081,13 @@
         <v>6</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4635,13 +5098,13 @@
         <v>6</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4652,13 +5115,13 @@
         <v>6</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4669,13 +5132,13 @@
         <v>6</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4686,13 +5149,13 @@
         <v>6</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>182</v>
+        <v>213</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4703,13 +5166,13 @@
         <v>6</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4727,11 +5190,11 @@
       <c r="B183" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C183" s="9" t="s">
-        <v>183</v>
+      <c r="C183" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>14</v>
@@ -4744,11 +5207,11 @@
       <c r="B184" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C184" s="9" t="s">
-        <v>183</v>
+      <c r="C184" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>14</v>
@@ -4761,11 +5224,11 @@
       <c r="B185" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C185" s="9" t="s">
-        <v>183</v>
+      <c r="C185" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>14</v>
@@ -4778,11 +5241,11 @@
       <c r="B186" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C186" s="9" t="s">
-        <v>183</v>
+      <c r="C186" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>14</v>
@@ -4795,11 +5258,11 @@
       <c r="B187" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C187" s="9" t="s">
-        <v>183</v>
+      <c r="C187" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>14</v>
@@ -4812,11 +5275,11 @@
       <c r="B188" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C188" s="9" t="s">
-        <v>183</v>
+      <c r="C188" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>14</v>
@@ -4829,11 +5292,11 @@
       <c r="B189" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C189" s="9" t="s">
-        <v>183</v>
+      <c r="C189" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>14</v>
@@ -4846,11 +5309,11 @@
       <c r="B190" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C190" s="9" t="s">
-        <v>183</v>
+      <c r="C190" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>14</v>
@@ -4863,11 +5326,11 @@
       <c r="B191" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C191" s="9" t="s">
-        <v>183</v>
+      <c r="C191" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>14</v>
@@ -4880,11 +5343,11 @@
       <c r="B192" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C192" s="9" t="s">
-        <v>183</v>
+      <c r="C192" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>14</v>
@@ -4897,11 +5360,11 @@
       <c r="B193" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C193" s="9" t="s">
-        <v>183</v>
+      <c r="C193" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>14</v>
@@ -4914,11 +5377,11 @@
       <c r="B194" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C194" s="9" t="s">
-        <v>183</v>
+      <c r="C194" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>14</v>
@@ -4931,11 +5394,11 @@
       <c r="B195" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C195" s="9" t="s">
-        <v>183</v>
+      <c r="C195" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>14</v>
@@ -4948,11 +5411,11 @@
       <c r="B196" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C196" s="9" t="s">
-        <v>183</v>
+      <c r="C196" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>14</v>
@@ -4965,11 +5428,11 @@
       <c r="B197" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C197" s="9" t="s">
-        <v>183</v>
+      <c r="C197" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>14</v>
@@ -4982,11 +5445,11 @@
       <c r="B198" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C198" s="9" t="s">
-        <v>183</v>
+      <c r="C198" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>14</v>
@@ -4999,11 +5462,11 @@
       <c r="B199" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C199" s="9" t="s">
-        <v>183</v>
+      <c r="C199" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>14</v>
@@ -5016,11 +5479,11 @@
       <c r="B200" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C200" s="9" t="s">
-        <v>183</v>
+      <c r="C200" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>14</v>
@@ -5033,11 +5496,11 @@
       <c r="B201" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C201" s="9" t="s">
-        <v>183</v>
+      <c r="C201" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>14</v>
@@ -5050,11 +5513,11 @@
       <c r="B202" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C202" s="9" t="s">
-        <v>183</v>
+      <c r="C202" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>14</v>
@@ -5067,11 +5530,11 @@
       <c r="B203" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C203" s="9" t="s">
-        <v>183</v>
+      <c r="C203" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>14</v>
@@ -5085,13 +5548,13 @@
         <v>7</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5102,13 +5565,13 @@
         <v>7</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5119,13 +5582,13 @@
         <v>7</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5136,13 +5599,13 @@
         <v>7</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5153,13 +5616,13 @@
         <v>7</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5170,13 +5633,13 @@
         <v>7</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5187,13 +5650,13 @@
         <v>7</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5204,13 +5667,13 @@
         <v>7</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5237,10 +5700,10 @@
         <v>8</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>14</v>
@@ -5254,10 +5717,10 @@
         <v>8</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>14</v>
@@ -5271,10 +5734,10 @@
         <v>8</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>14</v>
@@ -5288,10 +5751,10 @@
         <v>8</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>14</v>
@@ -5305,10 +5768,10 @@
         <v>8</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>14</v>
@@ -5322,10 +5785,10 @@
         <v>8</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>14</v>
@@ -5339,10 +5802,10 @@
         <v>8</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>14</v>
@@ -5356,10 +5819,10 @@
         <v>8</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>14</v>
@@ -5373,10 +5836,10 @@
         <v>8</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>14</v>
@@ -5390,10 +5853,10 @@
         <v>8</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>14</v>
@@ -5407,10 +5870,10 @@
         <v>8</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>14</v>
@@ -5424,10 +5887,10 @@
         <v>8</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>14</v>
@@ -5441,10 +5904,10 @@
         <v>8</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>14</v>
@@ -5458,10 +5921,10 @@
         <v>8</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>14</v>
@@ -5475,10 +5938,10 @@
         <v>8</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>14</v>
@@ -5492,10 +5955,10 @@
         <v>8</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>14</v>
@@ -5509,10 +5972,10 @@
         <v>8</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>14</v>
@@ -5526,10 +5989,10 @@
         <v>8</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>14</v>
@@ -5543,10 +6006,10 @@
         <v>8</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>14</v>
@@ -5560,10 +6023,10 @@
         <v>8</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>14</v>
@@ -5577,10 +6040,10 @@
         <v>8</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>14</v>
@@ -5594,13 +6057,13 @@
         <v>8</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5611,13 +6074,13 @@
         <v>8</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5628,13 +6091,13 @@
         <v>8</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5645,13 +6108,13 @@
         <v>8</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5662,13 +6125,13 @@
         <v>8</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5679,13 +6142,13 @@
         <v>8</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5696,13 +6159,13 @@
         <v>8</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5713,13 +6176,13 @@
         <v>8</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5746,10 +6209,10 @@
         <v>9</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>14</v>
@@ -5763,10 +6226,10 @@
         <v>9</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>14</v>
@@ -5780,10 +6243,10 @@
         <v>9</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>14</v>
@@ -5797,10 +6260,10 @@
         <v>9</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>14</v>
@@ -5814,10 +6277,10 @@
         <v>9</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>14</v>
@@ -5831,10 +6294,10 @@
         <v>9</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>14</v>
@@ -5848,10 +6311,10 @@
         <v>9</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>14</v>
@@ -5865,10 +6328,10 @@
         <v>9</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>14</v>
@@ -5882,10 +6345,10 @@
         <v>9</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>14</v>
@@ -5899,10 +6362,10 @@
         <v>9</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>14</v>
@@ -5916,10 +6379,10 @@
         <v>9</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>14</v>
@@ -5933,10 +6396,10 @@
         <v>9</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>14</v>
@@ -5950,10 +6413,10 @@
         <v>9</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>14</v>
@@ -5967,10 +6430,10 @@
         <v>9</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>14</v>
@@ -5984,10 +6447,10 @@
         <v>9</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>14</v>
@@ -6001,10 +6464,10 @@
         <v>9</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>14</v>
@@ -6018,10 +6481,10 @@
         <v>9</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>14</v>
@@ -6035,10 +6498,10 @@
         <v>9</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>14</v>
@@ -6052,10 +6515,10 @@
         <v>9</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>14</v>
@@ -6069,10 +6532,10 @@
         <v>9</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>14</v>
@@ -6086,10 +6549,10 @@
         <v>9</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>14</v>
@@ -6103,10 +6566,10 @@
         <v>9</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>14</v>
@@ -6120,10 +6583,10 @@
         <v>9</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>14</v>
@@ -6137,13 +6600,13 @@
         <v>9</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6154,13 +6617,13 @@
         <v>9</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6171,13 +6634,13 @@
         <v>9</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6188,13 +6651,13 @@
         <v>9</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6205,13 +6668,13 @@
         <v>9</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6222,13 +6685,13 @@
         <v>9</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,10 +6711,10 @@
         <v>10</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -6265,10 +6728,10 @@
         <v>10</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -6282,10 +6745,10 @@
         <v>10</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -6299,10 +6762,10 @@
         <v>10</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -6316,10 +6779,10 @@
         <v>10</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -6333,10 +6796,10 @@
         <v>10</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -6350,10 +6813,10 @@
         <v>10</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -6367,10 +6830,10 @@
         <v>10</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -6384,10 +6847,10 @@
         <v>10</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -6401,10 +6864,10 @@
         <v>10</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -6418,10 +6881,10 @@
         <v>10</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -6435,10 +6898,10 @@
         <v>10</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -6452,10 +6915,10 @@
         <v>10</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -6469,10 +6932,10 @@
         <v>10</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>14</v>
@@ -6486,10 +6949,10 @@
         <v>10</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>14</v>
@@ -6503,10 +6966,10 @@
         <v>10</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>14</v>
@@ -6520,10 +6983,10 @@
         <v>10</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>14</v>
@@ -6537,10 +7000,10 @@
         <v>10</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>14</v>
@@ -6554,10 +7017,10 @@
         <v>10</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>14</v>
@@ -6571,10 +7034,10 @@
         <v>10</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>14</v>
@@ -6588,10 +7051,10 @@
         <v>10</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>14</v>
@@ -6605,13 +7068,13 @@
         <v>10</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6622,13 +7085,13 @@
         <v>10</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6639,13 +7102,13 @@
         <v>10</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6656,13 +7119,13 @@
         <v>10</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6673,13 +7136,13 @@
         <v>10</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6690,13 +7153,13 @@
         <v>10</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6707,13 +7170,13 @@
         <v>10</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6724,13 +7187,13 @@
         <v>10</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6757,10 +7220,10 @@
         <v>11</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>14</v>
@@ -6774,10 +7237,10 @@
         <v>11</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>14</v>
@@ -6791,10 +7254,10 @@
         <v>11</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>14</v>
@@ -6808,10 +7271,10 @@
         <v>11</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>14</v>
@@ -6825,10 +7288,10 @@
         <v>11</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>14</v>
@@ -6842,10 +7305,10 @@
         <v>11</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -6859,10 +7322,10 @@
         <v>11</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>14</v>
@@ -6876,10 +7339,10 @@
         <v>11</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>14</v>
@@ -6893,10 +7356,10 @@
         <v>11</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>14</v>
@@ -6910,10 +7373,10 @@
         <v>11</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -6927,10 +7390,10 @@
         <v>11</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -6944,10 +7407,10 @@
         <v>11</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -6961,10 +7424,10 @@
         <v>11</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -6978,10 +7441,10 @@
         <v>11</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -6995,10 +7458,10 @@
         <v>11</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -7012,10 +7475,10 @@
         <v>11</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -7029,10 +7492,10 @@
         <v>11</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -7046,10 +7509,10 @@
         <v>11</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -7063,10 +7526,10 @@
         <v>11</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -7080,10 +7543,10 @@
         <v>11</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -7097,10 +7560,10 @@
         <v>11</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -7114,13 +7577,13 @@
         <v>11</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7131,13 +7594,13 @@
         <v>11</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7148,13 +7611,13 @@
         <v>11</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7165,13 +7628,13 @@
         <v>11</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7182,13 +7645,13 @@
         <v>11</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7199,13 +7662,13 @@
         <v>11</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7216,13 +7679,13 @@
         <v>11</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7233,13 +7696,13 @@
         <v>11</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7259,10 +7722,10 @@
         <v>12</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -7276,10 +7739,10 @@
         <v>12</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -7293,10 +7756,10 @@
         <v>12</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
@@ -7310,10 +7773,10 @@
         <v>12</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
@@ -7327,10 +7790,10 @@
         <v>12</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -7344,10 +7807,10 @@
         <v>12</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
@@ -7361,10 +7824,10 @@
         <v>12</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
@@ -7378,10 +7841,10 @@
         <v>12</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
@@ -7395,10 +7858,10 @@
         <v>12</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>14</v>
@@ -7412,10 +7875,10 @@
         <v>12</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>14</v>
@@ -7429,10 +7892,10 @@
         <v>12</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>14</v>
@@ -7446,10 +7909,10 @@
         <v>12</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>14</v>
@@ -7463,10 +7926,10 @@
         <v>12</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>14</v>
@@ -7480,10 +7943,10 @@
         <v>12</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -7497,10 +7960,10 @@
         <v>12</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -7514,10 +7977,10 @@
         <v>12</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -7531,10 +7994,10 @@
         <v>12</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
@@ -7548,10 +8011,10 @@
         <v>12</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>14</v>
@@ -7565,10 +8028,10 @@
         <v>12</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
@@ -7582,10 +8045,10 @@
         <v>12</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
@@ -7599,10 +8062,10 @@
         <v>12</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
@@ -7616,13 +8079,13 @@
         <v>12</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7633,13 +8096,13 @@
         <v>12</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7650,13 +8113,13 @@
         <v>12</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7667,13 +8130,13 @@
         <v>12</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7684,13 +8147,13 @@
         <v>12</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7701,13 +8164,13 @@
         <v>12</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7718,13 +8181,13 @@
         <v>12</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7735,13 +8198,13 @@
         <v>12</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="261">
   <si>
     <t xml:space="preserve">Day</t>
   </si>
@@ -858,6 +858,9 @@
     <t xml:space="preserve">Each day, parents and children take time to watch a YouTube video about children's rights.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/jul/july.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Good touch, Bad touch</t>
   </si>
   <si>
@@ -871,6 +874,9 @@
   </si>
   <si>
     <t xml:space="preserve">One Day, one question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/aug/aug.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Kind Words Only</t>
@@ -911,6 +917,30 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/sept/5.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/sept/2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/sept/4.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/sept/3.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/sept/6.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/sept/7.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/sept/8.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/sept/22.jpg</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -934,6 +964,9 @@
   </si>
   <si>
     <t xml:space="preserve">Family member each identify what they are feeling based on the feeling wheel and they share calmly what made them feel that way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/sept/he.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">#BlessingsNotBurden</t>
@@ -5199,6 +5232,9 @@
       <c r="G183" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K183" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="n">
@@ -5216,6 +5252,9 @@
       <c r="G184" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K184" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="n">
@@ -5233,6 +5272,9 @@
       <c r="G185" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K185" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="n">
@@ -5250,6 +5292,9 @@
       <c r="G186" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K186" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="n">
@@ -5267,6 +5312,9 @@
       <c r="G187" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K187" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="n">
@@ -5284,6 +5332,9 @@
       <c r="G188" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K188" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="n">
@@ -5301,6 +5352,9 @@
       <c r="G189" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K189" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="n">
@@ -5318,6 +5372,9 @@
       <c r="G190" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K190" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="n">
@@ -5335,6 +5392,9 @@
       <c r="G191" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K191" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="n">
@@ -5352,6 +5412,9 @@
       <c r="G192" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K192" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="n">
@@ -5369,6 +5432,9 @@
       <c r="G193" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K193" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="n">
@@ -5386,6 +5452,9 @@
       <c r="G194" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K194" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="195" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="n">
@@ -5403,6 +5472,9 @@
       <c r="G195" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K195" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="n">
@@ -5419,6 +5491,9 @@
       </c>
       <c r="G196" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K196" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5437,6 +5512,9 @@
       <c r="G197" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K197" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="198" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="n">
@@ -5454,6 +5532,9 @@
       <c r="G198" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K198" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="n">
@@ -5471,6 +5552,9 @@
       <c r="G199" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K199" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="n">
@@ -5488,6 +5572,9 @@
       <c r="G200" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K200" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="n">
@@ -5505,6 +5592,9 @@
       <c r="G201" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K201" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="n">
@@ -5522,6 +5612,9 @@
       <c r="G202" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K202" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="n">
@@ -5539,6 +5632,9 @@
       <c r="G203" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K203" s="1" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="n">
@@ -5548,10 +5644,10 @@
         <v>7</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>127</v>
@@ -5565,10 +5661,10 @@
         <v>7</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>127</v>
@@ -5582,10 +5678,10 @@
         <v>7</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>127</v>
@@ -5599,10 +5695,10 @@
         <v>7</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>127</v>
@@ -5616,10 +5712,10 @@
         <v>7</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>127</v>
@@ -5633,10 +5729,10 @@
         <v>7</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>130</v>
@@ -5650,10 +5746,10 @@
         <v>7</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>130</v>
@@ -5667,10 +5763,10 @@
         <v>7</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>130</v>
@@ -5700,13 +5796,16 @@
         <v>8</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D214" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K214" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5717,13 +5816,16 @@
         <v>8</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K215" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5734,13 +5836,16 @@
         <v>8</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K216" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5751,13 +5856,16 @@
         <v>8</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K217" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5768,13 +5876,16 @@
         <v>8</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K218" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5785,13 +5896,16 @@
         <v>8</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K219" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5802,13 +5916,16 @@
         <v>8</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K220" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5819,13 +5936,16 @@
         <v>8</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5836,13 +5956,16 @@
         <v>8</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D222" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K222" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5853,13 +5976,16 @@
         <v>8</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K223" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5870,13 +5996,16 @@
         <v>8</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K224" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5887,13 +6016,16 @@
         <v>8</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K225" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5904,7 +6036,7 @@
         <v>8</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>181</v>
@@ -5912,6 +6044,9 @@
       <c r="G226" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K226" s="1" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="227" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="n">
@@ -5921,13 +6056,16 @@
         <v>8</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5938,13 +6076,16 @@
         <v>8</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K228" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5955,13 +6096,16 @@
         <v>8</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K229" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5972,13 +6116,16 @@
         <v>8</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K230" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5989,13 +6136,16 @@
         <v>8</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K231" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6006,13 +6156,16 @@
         <v>8</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K232" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6023,13 +6176,16 @@
         <v>8</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K233" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6040,13 +6196,16 @@
         <v>8</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>181</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K234" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6057,10 +6216,10 @@
         <v>8</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>127</v>
@@ -6074,10 +6233,10 @@
         <v>8</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>127</v>
@@ -6091,10 +6250,10 @@
         <v>8</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>127</v>
@@ -6108,10 +6267,10 @@
         <v>8</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>127</v>
@@ -6125,10 +6284,10 @@
         <v>8</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>127</v>
@@ -6142,10 +6301,10 @@
         <v>8</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G240" s="2" t="s">
         <v>130</v>
@@ -6159,10 +6318,10 @@
         <v>8</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>130</v>
@@ -6176,10 +6335,10 @@
         <v>8</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>130</v>
@@ -6209,13 +6368,16 @@
         <v>9</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K245" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6226,13 +6388,16 @@
         <v>9</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K246" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6243,13 +6408,16 @@
         <v>9</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K247" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6260,13 +6428,16 @@
         <v>9</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K248" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6277,13 +6448,16 @@
         <v>9</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K249" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6294,13 +6468,16 @@
         <v>9</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K250" s="1" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6311,13 +6488,16 @@
         <v>9</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K251" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6328,13 +6508,16 @@
         <v>9</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K252" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6345,13 +6528,16 @@
         <v>9</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K253" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6362,13 +6548,16 @@
         <v>9</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K254" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6379,13 +6568,16 @@
         <v>9</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K255" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6396,13 +6588,16 @@
         <v>9</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K256" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6413,13 +6608,16 @@
         <v>9</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K257" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6430,13 +6628,16 @@
         <v>9</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K258" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6447,13 +6648,16 @@
         <v>9</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K259" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6464,13 +6668,16 @@
         <v>9</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K260" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6481,13 +6688,16 @@
         <v>9</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K261" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6498,13 +6708,16 @@
         <v>9</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K262" s="1" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6515,13 +6728,16 @@
         <v>9</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K263" s="8" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6532,13 +6748,16 @@
         <v>9</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K264" s="8" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6549,16 +6768,19 @@
         <v>9</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="266" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K265" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="33.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="n">
         <v>22</v>
       </c>
@@ -6566,16 +6788,19 @@
         <v>9</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="267" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K266" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="33.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="n">
         <v>23</v>
       </c>
@@ -6583,13 +6808,16 @@
         <v>9</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K267" s="8" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6600,13 +6828,16 @@
         <v>9</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K268" s="8" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6617,13 +6848,16 @@
         <v>9</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K269" s="8" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6634,10 +6868,10 @@
         <v>9</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>127</v>
@@ -6651,10 +6885,10 @@
         <v>9</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>127</v>
@@ -6668,10 +6902,10 @@
         <v>9</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>127</v>
@@ -6685,10 +6919,10 @@
         <v>9</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>130</v>
@@ -6711,10 +6945,10 @@
         <v>10</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -6728,10 +6962,10 @@
         <v>10</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -6745,10 +6979,10 @@
         <v>10</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -6762,10 +6996,10 @@
         <v>10</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -6779,10 +7013,10 @@
         <v>10</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -6796,10 +7030,10 @@
         <v>10</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -6813,10 +7047,10 @@
         <v>10</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -6830,10 +7064,10 @@
         <v>10</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -6847,10 +7081,10 @@
         <v>10</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -6864,10 +7098,10 @@
         <v>10</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -6881,10 +7115,10 @@
         <v>10</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -6898,10 +7132,10 @@
         <v>10</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -6915,10 +7149,10 @@
         <v>10</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -6932,10 +7166,10 @@
         <v>10</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>14</v>
@@ -6949,10 +7183,10 @@
         <v>10</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>14</v>
@@ -6966,10 +7200,10 @@
         <v>10</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>14</v>
@@ -6983,10 +7217,10 @@
         <v>10</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>14</v>
@@ -7000,10 +7234,10 @@
         <v>10</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>14</v>
@@ -7017,10 +7251,10 @@
         <v>10</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>14</v>
@@ -7034,10 +7268,10 @@
         <v>10</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>14</v>
@@ -7051,10 +7285,10 @@
         <v>10</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>14</v>
@@ -7068,10 +7302,10 @@
         <v>10</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>127</v>
@@ -7085,10 +7319,10 @@
         <v>10</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>127</v>
@@ -7102,10 +7336,10 @@
         <v>10</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>127</v>
@@ -7119,10 +7353,10 @@
         <v>10</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>127</v>
@@ -7136,10 +7370,10 @@
         <v>10</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>127</v>
@@ -7153,10 +7387,10 @@
         <v>10</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>130</v>
@@ -7170,10 +7404,10 @@
         <v>10</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>130</v>
@@ -7187,10 +7421,10 @@
         <v>10</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>130</v>
@@ -7220,10 +7454,10 @@
         <v>11</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>14</v>
@@ -7237,10 +7471,10 @@
         <v>11</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>14</v>
@@ -7254,10 +7488,10 @@
         <v>11</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>14</v>
@@ -7271,10 +7505,10 @@
         <v>11</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>14</v>
@@ -7288,10 +7522,10 @@
         <v>11</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>14</v>
@@ -7305,10 +7539,10 @@
         <v>11</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -7322,10 +7556,10 @@
         <v>11</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>14</v>
@@ -7339,10 +7573,10 @@
         <v>11</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>14</v>
@@ -7356,10 +7590,10 @@
         <v>11</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>14</v>
@@ -7373,10 +7607,10 @@
         <v>11</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -7390,10 +7624,10 @@
         <v>11</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -7407,10 +7641,10 @@
         <v>11</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -7424,10 +7658,10 @@
         <v>11</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -7441,10 +7675,10 @@
         <v>11</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -7458,10 +7692,10 @@
         <v>11</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -7475,10 +7709,10 @@
         <v>11</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -7492,10 +7726,10 @@
         <v>11</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -7509,10 +7743,10 @@
         <v>11</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -7526,10 +7760,10 @@
         <v>11</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -7543,10 +7777,10 @@
         <v>11</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -7560,10 +7794,10 @@
         <v>11</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -7577,10 +7811,10 @@
         <v>11</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>127</v>
@@ -7594,10 +7828,10 @@
         <v>11</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>127</v>
@@ -7611,10 +7845,10 @@
         <v>11</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>127</v>
@@ -7628,10 +7862,10 @@
         <v>11</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>127</v>
@@ -7645,10 +7879,10 @@
         <v>11</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>127</v>
@@ -7662,10 +7896,10 @@
         <v>11</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>130</v>
@@ -7679,10 +7913,10 @@
         <v>11</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>130</v>
@@ -7696,10 +7930,10 @@
         <v>11</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>130</v>
@@ -7722,10 +7956,10 @@
         <v>12</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -7739,10 +7973,10 @@
         <v>12</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -7756,10 +7990,10 @@
         <v>12</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
@@ -7773,10 +8007,10 @@
         <v>12</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
@@ -7790,10 +8024,10 @@
         <v>12</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -7807,10 +8041,10 @@
         <v>12</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
@@ -7824,10 +8058,10 @@
         <v>12</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
@@ -7841,10 +8075,10 @@
         <v>12</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
@@ -7858,10 +8092,10 @@
         <v>12</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>14</v>
@@ -7875,10 +8109,10 @@
         <v>12</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>14</v>
@@ -7892,10 +8126,10 @@
         <v>12</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>14</v>
@@ -7909,10 +8143,10 @@
         <v>12</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>14</v>
@@ -7926,10 +8160,10 @@
         <v>12</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>14</v>
@@ -7943,10 +8177,10 @@
         <v>12</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -7960,10 +8194,10 @@
         <v>12</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -7977,10 +8211,10 @@
         <v>12</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -7994,10 +8228,10 @@
         <v>12</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
@@ -8011,10 +8245,10 @@
         <v>12</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>14</v>
@@ -8028,10 +8262,10 @@
         <v>12</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
@@ -8045,10 +8279,10 @@
         <v>12</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
@@ -8062,10 +8296,10 @@
         <v>12</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
@@ -8079,10 +8313,10 @@
         <v>12</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>127</v>
@@ -8096,10 +8330,10 @@
         <v>12</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>127</v>
@@ -8113,10 +8347,10 @@
         <v>12</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>127</v>
@@ -8130,10 +8364,10 @@
         <v>12</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>127</v>
@@ -8147,10 +8381,10 @@
         <v>12</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>127</v>
@@ -8164,10 +8398,10 @@
         <v>12</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>130</v>
@@ -8181,10 +8415,10 @@
         <v>12</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>130</v>
@@ -8198,10 +8432,10 @@
         <v>12</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>130</v>

--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="271">
   <si>
     <t xml:space="preserve">Day</t>
   </si>
@@ -1021,6 +1021,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/oct/1.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Declutter=Destress</t>
   </si>
   <si>
@@ -1099,6 +1102,30 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/nov/nov.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/nov/2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/nov/3.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/nov/4.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/nov/5.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/nov/6.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/nov/7.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/nov/1.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Their Next Chapter</t>
   </si>
   <si>
@@ -1137,6 +1164,9 @@
     <t xml:space="preserve">Two hours before bedtime is tech-free time. Let children share what their favorite online activity is.</t>
   </si>
   <si>
+    <t xml:space="preserve">/images/lessons/dec/1.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Make Your Move</t>
   </si>
   <si>
@@ -1177,7 +1207,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1233,12 +1263,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1285,7 +1309,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1318,15 +1342,11 @@
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4688,7 +4708,7 @@
       <c r="G154" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K154" s="8" t="s">
+      <c r="K154" s="4" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4708,7 +4728,7 @@
       <c r="G155" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K155" s="8" t="s">
+      <c r="K155" s="4" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4728,7 +4748,7 @@
       <c r="G156" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K156" s="8" t="s">
+      <c r="K156" s="4" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4748,7 +4768,7 @@
       <c r="G157" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K157" s="8" t="s">
+      <c r="K157" s="4" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4768,7 +4788,7 @@
       <c r="G158" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K158" s="8" t="s">
+      <c r="K158" s="4" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4788,7 +4808,7 @@
       <c r="G159" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K159" s="8" t="s">
+      <c r="K159" s="4" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4808,7 +4828,7 @@
       <c r="G160" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K160" s="8" t="s">
+      <c r="K160" s="4" t="s">
         <v>207</v>
       </c>
     </row>
@@ -4828,7 +4848,7 @@
       <c r="G161" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K161" s="8" t="s">
+      <c r="K161" s="4" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4848,7 +4868,7 @@
       <c r="G162" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K162" s="8" t="s">
+      <c r="K162" s="4" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4868,7 +4888,7 @@
       <c r="G163" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K163" s="8" t="s">
+      <c r="K163" s="4" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4888,7 +4908,7 @@
       <c r="G164" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K164" s="8" t="s">
+      <c r="K164" s="4" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4908,7 +4928,7 @@
       <c r="G165" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K165" s="8" t="s">
+      <c r="K165" s="4" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4928,7 +4948,7 @@
       <c r="G166" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K166" s="8" t="s">
+      <c r="K166" s="4" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4948,7 +4968,7 @@
       <c r="G167" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K167" s="8" t="s">
+      <c r="K167" s="4" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4968,7 +4988,7 @@
       <c r="G168" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K168" s="8" t="s">
+      <c r="K168" s="4" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4988,7 +5008,7 @@
       <c r="G169" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K169" s="8" t="s">
+      <c r="K169" s="4" t="s">
         <v>210</v>
       </c>
     </row>
@@ -5008,7 +5028,7 @@
       <c r="G170" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K170" s="8" t="s">
+      <c r="K170" s="4" t="s">
         <v>210</v>
       </c>
     </row>
@@ -5028,7 +5048,7 @@
       <c r="G171" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K171" s="8" t="s">
+      <c r="K171" s="4" t="s">
         <v>210</v>
       </c>
     </row>
@@ -5048,7 +5068,7 @@
       <c r="G172" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K172" s="8" t="s">
+      <c r="K172" s="4" t="s">
         <v>210</v>
       </c>
     </row>
@@ -5068,7 +5088,7 @@
       <c r="G173" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K173" s="8" t="s">
+      <c r="K173" s="4" t="s">
         <v>210</v>
       </c>
     </row>
@@ -5184,7 +5204,7 @@
       <c r="C180" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D180" s="9" t="s">
+      <c r="D180" s="8" t="s">
         <v>214</v>
       </c>
       <c r="G180" s="2" t="s">
@@ -5223,7 +5243,7 @@
       <c r="B183" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C183" s="10" t="s">
+      <c r="C183" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D183" s="3" t="s">
@@ -5243,7 +5263,7 @@
       <c r="B184" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C184" s="10" t="s">
+      <c r="C184" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D184" s="3" t="s">
@@ -5263,7 +5283,7 @@
       <c r="B185" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C185" s="10" t="s">
+      <c r="C185" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D185" s="3" t="s">
@@ -5283,7 +5303,7 @@
       <c r="B186" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C186" s="10" t="s">
+      <c r="C186" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D186" s="3" t="s">
@@ -5303,7 +5323,7 @@
       <c r="B187" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C187" s="10" t="s">
+      <c r="C187" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D187" s="3" t="s">
@@ -5323,7 +5343,7 @@
       <c r="B188" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C188" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D188" s="3" t="s">
@@ -5343,7 +5363,7 @@
       <c r="B189" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C189" s="10" t="s">
+      <c r="C189" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D189" s="3" t="s">
@@ -5363,7 +5383,7 @@
       <c r="B190" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="C190" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D190" s="3" t="s">
@@ -5383,7 +5403,7 @@
       <c r="B191" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C191" s="10" t="s">
+      <c r="C191" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D191" s="3" t="s">
@@ -5403,7 +5423,7 @@
       <c r="B192" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C192" s="10" t="s">
+      <c r="C192" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D192" s="3" t="s">
@@ -5423,7 +5443,7 @@
       <c r="B193" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C193" s="10" t="s">
+      <c r="C193" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D193" s="3" t="s">
@@ -5443,7 +5463,7 @@
       <c r="B194" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C194" s="10" t="s">
+      <c r="C194" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D194" s="3" t="s">
@@ -5463,7 +5483,7 @@
       <c r="B195" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C195" s="10" t="s">
+      <c r="C195" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D195" s="3" t="s">
@@ -5483,7 +5503,7 @@
       <c r="B196" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C196" s="10" t="s">
+      <c r="C196" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D196" s="3" t="s">
@@ -5503,7 +5523,7 @@
       <c r="B197" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C197" s="10" t="s">
+      <c r="C197" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D197" s="3" t="s">
@@ -5523,7 +5543,7 @@
       <c r="B198" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C198" s="10" t="s">
+      <c r="C198" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D198" s="3" t="s">
@@ -5543,7 +5563,7 @@
       <c r="B199" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C199" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D199" s="3" t="s">
@@ -5563,7 +5583,7 @@
       <c r="B200" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C200" s="10" t="s">
+      <c r="C200" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D200" s="3" t="s">
@@ -5583,7 +5603,7 @@
       <c r="B201" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C201" s="10" t="s">
+      <c r="C201" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D201" s="3" t="s">
@@ -5603,7 +5623,7 @@
       <c r="B202" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C202" s="10" t="s">
+      <c r="C202" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D202" s="3" t="s">
@@ -5623,7 +5643,7 @@
       <c r="B203" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C203" s="10" t="s">
+      <c r="C203" s="9" t="s">
         <v>215</v>
       </c>
       <c r="D203" s="3" t="s">
@@ -6736,7 +6756,7 @@
       <c r="G263" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K263" s="8" t="s">
+      <c r="K263" s="4" t="s">
         <v>236</v>
       </c>
     </row>
@@ -6756,7 +6776,7 @@
       <c r="G264" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K264" s="8" t="s">
+      <c r="K264" s="4" t="s">
         <v>236</v>
       </c>
     </row>
@@ -6776,11 +6796,11 @@
       <c r="G265" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K265" s="8" t="s">
+      <c r="K265" s="4" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="33.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="n">
         <v>22</v>
       </c>
@@ -6796,11 +6816,11 @@
       <c r="G266" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K266" s="8" t="s">
+      <c r="K266" s="4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="33.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="n">
         <v>23</v>
       </c>
@@ -6816,7 +6836,7 @@
       <c r="G267" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K267" s="8" t="s">
+      <c r="K267" s="4" t="s">
         <v>237</v>
       </c>
     </row>
@@ -6836,7 +6856,7 @@
       <c r="G268" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K268" s="8" t="s">
+      <c r="K268" s="4" t="s">
         <v>240</v>
       </c>
     </row>
@@ -6856,7 +6876,7 @@
       <c r="G269" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K269" s="8" t="s">
+      <c r="K269" s="4" t="s">
         <v>240</v>
       </c>
     </row>
@@ -6953,6 +6973,9 @@
       <c r="G275" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K275" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="276" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="n">
@@ -6970,6 +6993,9 @@
       <c r="G276" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K276" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="277" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="n">
@@ -6987,6 +7013,9 @@
       <c r="G277" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K277" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="278" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="n">
@@ -7004,6 +7033,9 @@
       <c r="G278" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K278" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="279" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="n">
@@ -7021,6 +7053,9 @@
       <c r="G279" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K279" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="280" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="n">
@@ -7038,6 +7073,9 @@
       <c r="G280" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K280" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="281" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="n">
@@ -7055,6 +7093,9 @@
       <c r="G281" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K281" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="282" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="n">
@@ -7072,6 +7113,9 @@
       <c r="G282" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K282" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="283" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="n">
@@ -7089,6 +7133,9 @@
       <c r="G283" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K283" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="284" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="n">
@@ -7106,6 +7153,9 @@
       <c r="G284" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K284" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="285" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="n">
@@ -7123,6 +7173,9 @@
       <c r="G285" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K285" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="286" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="n">
@@ -7140,6 +7193,9 @@
       <c r="G286" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K286" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="287" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="n">
@@ -7157,6 +7213,9 @@
       <c r="G287" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K287" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="288" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="n">
@@ -7173,6 +7232,9 @@
       </c>
       <c r="G288" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K288" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7191,6 +7253,9 @@
       <c r="G289" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K289" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="290" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="n">
@@ -7208,6 +7273,9 @@
       <c r="G290" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K290" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="291" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="n">
@@ -7225,6 +7293,9 @@
       <c r="G291" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K291" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="292" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="n">
@@ -7242,6 +7313,9 @@
       <c r="G292" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K292" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="293" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="n">
@@ -7259,6 +7333,9 @@
       <c r="G293" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K293" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="294" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="n">
@@ -7276,6 +7353,9 @@
       <c r="G294" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K294" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="295" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="n">
@@ -7293,6 +7373,9 @@
       <c r="G295" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K295" s="1" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="296" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="n">
@@ -7302,13 +7385,16 @@
         <v>10</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K296" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7319,13 +7405,16 @@
         <v>10</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K297" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7336,13 +7425,16 @@
         <v>10</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K298" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7353,13 +7445,16 @@
         <v>10</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K299" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7370,13 +7465,16 @@
         <v>10</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K300" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7387,13 +7485,16 @@
         <v>10</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>130</v>
+      </c>
+      <c r="K301" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7404,10 +7505,10 @@
         <v>10</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>130</v>
@@ -7421,10 +7522,10 @@
         <v>10</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>130</v>
@@ -7454,13 +7555,16 @@
         <v>11</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K306" s="1" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7471,13 +7575,16 @@
         <v>11</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K307" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7488,13 +7595,16 @@
         <v>11</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K308" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7505,13 +7615,16 @@
         <v>11</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K309" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7522,13 +7635,16 @@
         <v>11</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K310" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7539,13 +7655,16 @@
         <v>11</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K311" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7556,13 +7675,16 @@
         <v>11</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K312" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7573,13 +7695,16 @@
         <v>11</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K313" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7590,13 +7715,16 @@
         <v>11</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K314" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7607,13 +7735,16 @@
         <v>11</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K315" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7624,13 +7755,16 @@
         <v>11</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K316" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7641,13 +7775,16 @@
         <v>11</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K317" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7658,13 +7795,16 @@
         <v>11</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K318" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7675,13 +7815,16 @@
         <v>11</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K319" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7692,13 +7835,16 @@
         <v>11</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K320" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7709,13 +7855,16 @@
         <v>11</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K321" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7726,13 +7875,16 @@
         <v>11</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K322" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7743,13 +7895,16 @@
         <v>11</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K323" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7760,13 +7915,16 @@
         <v>11</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K324" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7777,13 +7935,16 @@
         <v>11</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K325" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7794,13 +7955,16 @@
         <v>11</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K326" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7811,13 +7975,16 @@
         <v>11</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K327" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7828,13 +7995,16 @@
         <v>11</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K328" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7845,13 +8015,16 @@
         <v>11</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K329" s="1" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7862,13 +8035,16 @@
         <v>11</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K330" s="1" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7879,13 +8055,16 @@
         <v>11</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>127</v>
+      </c>
+      <c r="K331" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7896,13 +8075,16 @@
         <v>11</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>130</v>
+      </c>
+      <c r="K332" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7913,13 +8095,16 @@
         <v>11</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>130</v>
+      </c>
+      <c r="K333" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7930,10 +8115,10 @@
         <v>11</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>130</v>
@@ -7947,6 +8132,9 @@
         <v>11</v>
       </c>
       <c r="D335" s="3"/>
+      <c r="K335" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="336" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="n">
@@ -7956,13 +8144,16 @@
         <v>12</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K336" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7973,13 +8164,16 @@
         <v>12</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K337" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7990,13 +8184,16 @@
         <v>12</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K338" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8007,13 +8204,16 @@
         <v>12</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K339" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8024,13 +8224,16 @@
         <v>12</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K340" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8041,13 +8244,16 @@
         <v>12</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K341" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8058,13 +8264,16 @@
         <v>12</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K342" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8075,13 +8284,16 @@
         <v>12</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K343" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8092,13 +8304,16 @@
         <v>12</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K344" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8109,13 +8324,16 @@
         <v>12</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K345" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8126,13 +8344,16 @@
         <v>12</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K346" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8143,13 +8364,16 @@
         <v>12</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K347" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8160,13 +8384,16 @@
         <v>12</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K348" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8177,13 +8404,16 @@
         <v>12</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K349" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8194,13 +8424,16 @@
         <v>12</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K350" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8211,13 +8444,16 @@
         <v>12</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K351" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8228,13 +8464,16 @@
         <v>12</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K352" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8245,13 +8484,16 @@
         <v>12</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K353" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8262,13 +8504,16 @@
         <v>12</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K354" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8279,13 +8524,16 @@
         <v>12</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K355" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8296,13 +8544,16 @@
         <v>12</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="K356" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8313,10 +8564,10 @@
         <v>12</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>127</v>
@@ -8330,10 +8581,10 @@
         <v>12</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>127</v>
@@ -8347,10 +8598,10 @@
         <v>12</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>127</v>
@@ -8364,10 +8615,10 @@
         <v>12</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>127</v>
@@ -8381,10 +8632,10 @@
         <v>12</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>127</v>
@@ -8398,10 +8649,10 @@
         <v>12</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>130</v>
@@ -8415,10 +8666,10 @@
         <v>12</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>130</v>
@@ -8432,10 +8683,10 @@
         <v>12</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>130</v>

--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="276">
   <si>
     <t xml:space="preserve">Day</t>
   </si>
@@ -1165,6 +1165,21 @@
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/dec/1.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/dec/2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/dec/3.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/dec/4.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/dec/11.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/dec/12.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Make Your Move</t>
@@ -8170,7 +8185,7 @@
         <v>14</v>
       </c>
       <c r="K337" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8190,7 +8205,7 @@
         <v>14</v>
       </c>
       <c r="K338" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8210,7 +8225,7 @@
         <v>14</v>
       </c>
       <c r="K339" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8230,7 +8245,7 @@
         <v>14</v>
       </c>
       <c r="K340" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8250,7 +8265,7 @@
         <v>14</v>
       </c>
       <c r="K341" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8270,7 +8285,7 @@
         <v>14</v>
       </c>
       <c r="K342" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8290,7 +8305,7 @@
         <v>14</v>
       </c>
       <c r="K343" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8310,7 +8325,7 @@
         <v>14</v>
       </c>
       <c r="K344" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8330,7 +8345,7 @@
         <v>14</v>
       </c>
       <c r="K345" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8350,7 +8365,7 @@
         <v>14</v>
       </c>
       <c r="K346" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8370,7 +8385,7 @@
         <v>14</v>
       </c>
       <c r="K347" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8390,7 +8405,7 @@
         <v>14</v>
       </c>
       <c r="K348" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8410,7 +8425,7 @@
         <v>14</v>
       </c>
       <c r="K349" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8430,7 +8445,7 @@
         <v>14</v>
       </c>
       <c r="K350" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8450,7 +8465,7 @@
         <v>14</v>
       </c>
       <c r="K351" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8470,7 +8485,7 @@
         <v>14</v>
       </c>
       <c r="K352" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8490,7 +8505,7 @@
         <v>14</v>
       </c>
       <c r="K353" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8510,7 +8525,7 @@
         <v>14</v>
       </c>
       <c r="K354" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8529,9 +8544,6 @@
       <c r="G355" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K355" s="1" t="s">
-        <v>266</v>
-      </c>
     </row>
     <row r="356" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="n">
@@ -8549,9 +8561,6 @@
       <c r="G356" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K356" s="1" t="s">
-        <v>266</v>
-      </c>
     </row>
     <row r="357" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="n">
@@ -8561,10 +8570,10 @@
         <v>12</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>127</v>
@@ -8578,10 +8587,10 @@
         <v>12</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>127</v>
@@ -8595,10 +8604,10 @@
         <v>12</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>127</v>
@@ -8612,10 +8621,10 @@
         <v>12</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>127</v>
@@ -8629,10 +8638,10 @@
         <v>12</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>127</v>
@@ -8646,10 +8655,10 @@
         <v>12</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>130</v>
@@ -8663,10 +8672,10 @@
         <v>12</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>130</v>
@@ -8680,10 +8689,10 @@
         <v>12</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>130</v>

--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="278">
   <si>
     <t xml:space="preserve">Day</t>
   </si>
@@ -55,13 +55,88 @@
     <t xml:space="preserve">ImagePath</t>
   </si>
   <si>
-    <t xml:space="preserve">Survival and development of the child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learn about Article 6 (Right to life) - every child's fundamental right to survive and develop.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/excelPDF/example.pdf</t>
+    <t xml:space="preserve">Day 1: The "Safe &amp; Strong" High-Five</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spend a few meaningful minutes with your child today—be present and explore their rights through a quick, hands-on activity!
+Time: 3–5 Minutes
+Materials: None (just your hands) | Use your child’s hand to help them understand their rights. 
+Feel free to use your own words to make it simple and clear for them!
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. The Thumb: Survival (Article 6)
+Action: Have the child hold up their thumb.
+The Talk: "See your thumb? It’s your 'thumbs up' for health! This means you have the right to grow up strong with good food, water, and a doctor when you're sick. We work together to keep your 'thumbs up' strong.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. The Fingers: Staying Connected (Article 9)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Action: Have them wiggle their other four fingers.
+The Talk: "These fingers are the people who love you..”
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3. The Palm: The Safety Net
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Action: Press your palm against theirs in a high-five.
+The Talk: “This high-five is like a shield. It means you have a whole team of grown-ups—me, your teachers, and even the people who make the laws—standing right behind you. 
+The Takeaway:
+"It is your duty to guide your child toward a healthy life and keep them close to those who care.”
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 6: Survival and Development of the Child
+Every child has the right to be alive. Governments must make sure that children survive and develop in the best possible way.
+Link: https://www.youtube.com/watch?v=KN-R_X7J-yI 
+Article 9: Separation of Parents
+Children should not be separated from their parents unless they are not being properly looked after – for example, if a parent hurts or does not take care of a child. Children whose parents don’t live together should stay in contact with both parents unless this might harm the child.
+Link: https://www.youtube.com/watch?v=bayHCraJLPc 
+</t>
   </si>
   <si>
     <t xml:space="preserve">individual</t>
@@ -73,13 +148,33 @@
     <t xml:space="preserve">/images/lessons/jan/month1-day1.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Responsibility of parents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explore children's right to healthcare, nutrition, and a safe environment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/excelPDF/WardiResume.pdf</t>
+    <t xml:space="preserve">Day 2: The "Shield of Care" Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let's explore more child rights together with a quick, hands-on activity! 
+Time: 5 Minutes
+Materials: None (just you and your child's imagination)
+Feel free to use your own words to make it simple and clear for them!
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The Small Circle (The Child)
+Action: Have the child cup their hands like they are holding a tiny ball.
+The Talk: "This little circle is you. You are the most important part of this story!"
+2. The Shield (Parents &amp; Guardians â€” Article 18)
+Action: Wrap your hands over theirs.
+The Talk: "My hands are your shield. Us parents have the most important job: doing what is best for you."
+3. The Big Hug (The Government - Main Duty Bearers)
+Action: Give them a quick hug or wrap your arms around the "shield."
+The Talk: "The Government is like a giant hug around our family. Their job is to help me take care of you by providing things like your school and your doctor."
+The Takeaway
+“You have the most important job of doing what’s best for the child, and the government is here to help you.”
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 18: Responsibility of Parents
+Parents are the main people responsible for bringing up a child. When the child does not have any parents, another adult will have this responsibility and they are called a “guardian”. Parents and guardians should always consider what is best for that child. Governments should help them. Where a child has both parents, both of them should be responsible for bringing up the child.
+Link: https://www.youtube.com/watch?v=zZZKL-H-MXs</t>
   </si>
   <si>
     <r>
@@ -1222,7 +1317,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1244,6 +1339,34 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1324,7 +1447,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1337,11 +1460,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1349,19 +1484,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1665,56 +1800,62 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="105.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="161.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1725,22 +1866,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1751,19 +1892,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1774,19 +1915,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1797,22 +1938,22 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1823,19 +1964,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>37</v>
+        <v>16</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1846,19 +1987,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>40</v>
+        <v>16</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1869,19 +2010,19 @@
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>43</v>
+        <v>16</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1892,19 +2033,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>46</v>
+        <v>16</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1915,19 +2056,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>49</v>
+        <v>16</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1938,19 +2079,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>52</v>
+        <v>16</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1961,19 +2102,19 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>55</v>
+        <v>16</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1984,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>58</v>
+        <v>16</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2007,19 +2148,19 @@
         <v>1</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>61</v>
+        <v>16</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2030,19 +2171,19 @@
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>64</v>
+        <v>16</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2053,19 +2194,19 @@
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>67</v>
+        <v>16</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2076,19 +2217,19 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>70</v>
+        <v>16</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2099,19 +2240,19 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>73</v>
+        <v>16</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2122,19 +2263,19 @@
         <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>76</v>
+        <v>16</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2145,19 +2286,19 @@
         <v>1</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>79</v>
+        <v>16</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2169,10 +2310,10 @@
       </c>
       <c r="C23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2183,10 +2324,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2245,25 +2386,25 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2273,27 +2414,27 @@
       <c r="B32" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>86</v>
+      <c r="C32" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F32" s="3" t="s">
         <v>89</v>
       </c>
+      <c r="E32" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="G32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H32" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2303,24 +2444,24 @@
       <c r="B33" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>91</v>
+      <c r="C33" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H33" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2331,20 +2472,20 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H34" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2355,20 +2496,20 @@
         <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H35" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2379,20 +2520,20 @@
         <v>2</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H36" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2403,20 +2544,20 @@
         <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H37" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2427,20 +2568,20 @@
         <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H38" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2451,20 +2592,20 @@
         <v>2</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H39" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2475,20 +2616,20 @@
         <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H40" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2499,20 +2640,20 @@
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H41" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H41" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2523,20 +2664,20 @@
         <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H42" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2547,20 +2688,20 @@
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H43" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2571,20 +2712,20 @@
         <v>2</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H44" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2595,20 +2736,20 @@
         <v>2</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H45" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2619,20 +2760,20 @@
         <v>2</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H46" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2643,20 +2784,20 @@
         <v>2</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H47" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2667,20 +2808,20 @@
         <v>2</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H48" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2691,20 +2832,20 @@
         <v>2</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H49" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H49" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2715,20 +2856,20 @@
         <v>2</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H50" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2739,20 +2880,20 @@
         <v>2</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H51" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H51" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2763,20 +2904,20 @@
         <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H52" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2786,13 +2927,13 @@
       <c r="B53" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>126</v>
+      <c r="C53" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H53" s="5" t="b">
+        <v>129</v>
+      </c>
+      <c r="H53" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2804,13 +2945,13 @@
       <c r="B54" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>126</v>
+      <c r="C54" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H54" s="5" t="b">
+        <v>129</v>
+      </c>
+      <c r="H54" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2822,13 +2963,13 @@
       <c r="B55" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>128</v>
+      <c r="C55" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H55" s="5" t="b">
+        <v>129</v>
+      </c>
+      <c r="H55" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2840,13 +2981,13 @@
       <c r="B56" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>129</v>
+      <c r="C56" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H56" s="5" t="b">
+        <v>132</v>
+      </c>
+      <c r="H56" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2858,13 +2999,13 @@
       <c r="B57" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>129</v>
+      <c r="C57" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H57" s="5" t="b">
+        <v>132</v>
+      </c>
+      <c r="H57" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2876,13 +3017,13 @@
       <c r="B58" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>129</v>
+      <c r="C58" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H58" s="5" t="b">
+        <v>132</v>
+      </c>
+      <c r="H58" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2894,7 +3035,7 @@
       <c r="B59" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="5" t="b">
+      <c r="H59" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2907,9 +3048,9 @@
         <v>2</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H60" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2921,24 +3062,24 @@
       <c r="B61" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>131</v>
+      <c r="C61" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H61" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H61" s="8" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2949,20 +3090,20 @@
         <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H62" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2973,20 +3114,20 @@
         <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H63" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H63" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2997,20 +3138,20 @@
         <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H64" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3021,20 +3162,20 @@
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H65" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H65" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3045,20 +3186,20 @@
         <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H66" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3069,20 +3210,20 @@
         <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H67" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H67" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3093,20 +3234,20 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H68" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3117,20 +3258,20 @@
         <v>3</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H69" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H69" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3141,20 +3282,20 @@
         <v>3</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H70" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3165,20 +3306,20 @@
         <v>3</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H71" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H71" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3189,20 +3330,20 @@
         <v>3</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H72" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3213,20 +3354,20 @@
         <v>3</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H73" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H73" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3237,20 +3378,20 @@
         <v>3</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H74" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3261,20 +3402,20 @@
         <v>3</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H75" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H75" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3285,20 +3426,20 @@
         <v>3</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H76" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3309,20 +3450,20 @@
         <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H77" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H77" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3333,20 +3474,20 @@
         <v>3</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H78" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H78" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3357,20 +3498,20 @@
         <v>3</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H79" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H79" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3381,20 +3522,20 @@
         <v>3</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H80" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H80" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3405,20 +3546,20 @@
         <v>3</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H81" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H81" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3429,20 +3570,20 @@
         <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H82" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H82" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3453,17 +3594,17 @@
         <v>3</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H83" s="5" t="b">
+        <v>129</v>
+      </c>
+      <c r="H83" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3474,17 +3615,17 @@
         <v>3</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H84" s="5" t="b">
+        <v>129</v>
+      </c>
+      <c r="H84" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3495,17 +3636,17 @@
         <v>3</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H85" s="5" t="b">
+        <v>129</v>
+      </c>
+      <c r="H85" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3516,17 +3657,17 @@
         <v>3</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H86" s="5" t="b">
+        <v>129</v>
+      </c>
+      <c r="H86" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3537,17 +3678,17 @@
         <v>3</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H87" s="5" t="b">
+        <v>129</v>
+      </c>
+      <c r="H87" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3558,17 +3699,17 @@
         <v>3</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H88" s="5" t="b">
+        <v>132</v>
+      </c>
+      <c r="H88" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3579,17 +3720,17 @@
         <v>3</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H89" s="5" t="b">
+        <v>132</v>
+      </c>
+      <c r="H89" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3600,12 +3741,12 @@
         <v>3</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H90" s="5" t="b">
+        <v>132</v>
+      </c>
+      <c r="H90" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3618,26 +3759,26 @@
         <v>3</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H91" s="5" t="b">
+        <v>15</v>
+      </c>
+      <c r="H91" s="8" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3648,13 +3789,13 @@
         <v>4</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3665,13 +3806,13 @@
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3682,13 +3823,13 @@
         <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D94" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3699,13 +3840,13 @@
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3716,13 +3857,13 @@
         <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3733,13 +3874,13 @@
         <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3750,13 +3891,13 @@
         <v>4</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3767,13 +3908,13 @@
         <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3784,13 +3925,13 @@
         <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3801,13 +3942,13 @@
         <v>4</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3818,13 +3959,13 @@
         <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3835,13 +3976,13 @@
         <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3852,13 +3993,13 @@
         <v>4</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3869,13 +4010,13 @@
         <v>4</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3886,13 +4027,13 @@
         <v>4</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3903,13 +4044,13 @@
         <v>4</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3920,13 +4061,13 @@
         <v>4</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D108" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K108" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3937,13 +4078,13 @@
         <v>4</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3954,13 +4095,13 @@
         <v>4</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3971,13 +4112,13 @@
         <v>4</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3988,13 +4129,13 @@
         <v>4</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4005,10 +4146,10 @@
         <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4019,10 +4160,10 @@
         <v>4</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E114" s="7" t="s">
         <v>188</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4033,10 +4174,10 @@
         <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4047,10 +4188,10 @@
         <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4061,10 +4202,10 @@
         <v>4</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4075,10 +4216,10 @@
         <v>4</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4089,10 +4230,10 @@
         <v>4</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4103,10 +4244,10 @@
         <v>4</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4124,17 +4265,17 @@
       <c r="B122" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C122" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>197</v>
+      <c r="C122" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4144,17 +4285,17 @@
       <c r="B123" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C123" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>197</v>
+      <c r="C123" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4164,17 +4305,17 @@
       <c r="B124" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C124" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>197</v>
+      <c r="C124" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4184,17 +4325,17 @@
       <c r="B125" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C125" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>197</v>
+      <c r="C125" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4204,17 +4345,17 @@
       <c r="B126" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>197</v>
+      <c r="C126" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4224,17 +4365,17 @@
       <c r="B127" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C127" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>197</v>
+      <c r="C127" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4244,17 +4385,17 @@
       <c r="B128" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C128" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>197</v>
+      <c r="C128" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4264,17 +4405,17 @@
       <c r="B129" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C129" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>197</v>
+      <c r="C129" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4284,17 +4425,17 @@
       <c r="B130" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C130" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>197</v>
+      <c r="C130" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4304,17 +4445,17 @@
       <c r="B131" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C131" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>197</v>
+      <c r="C131" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4324,17 +4465,17 @@
       <c r="B132" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C132" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>197</v>
+      <c r="C132" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4344,17 +4485,17 @@
       <c r="B133" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C133" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>197</v>
+      <c r="C133" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4364,17 +4505,17 @@
       <c r="B134" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>197</v>
+      <c r="C134" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4384,17 +4525,17 @@
       <c r="B135" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>197</v>
+      <c r="C135" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4404,17 +4545,17 @@
       <c r="B136" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C136" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>197</v>
+      <c r="C136" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4424,17 +4565,17 @@
       <c r="B137" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C137" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>197</v>
+      <c r="C137" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4444,17 +4585,17 @@
       <c r="B138" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C138" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>197</v>
+      <c r="C138" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4464,17 +4605,17 @@
       <c r="B139" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C139" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>197</v>
+      <c r="C139" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4484,17 +4625,17 @@
       <c r="B140" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C140" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>197</v>
+      <c r="C140" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4504,17 +4645,17 @@
       <c r="B141" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C141" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>197</v>
+      <c r="C141" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4524,14 +4665,14 @@
       <c r="B142" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C142" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>197</v>
+      <c r="C142" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4541,14 +4682,14 @@
       <c r="B143" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C143" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>200</v>
+      <c r="C143" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4558,14 +4699,14 @@
       <c r="B144" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C144" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>200</v>
+      <c r="C144" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4575,14 +4716,14 @@
       <c r="B145" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C145" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>200</v>
+      <c r="C145" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4592,14 +4733,14 @@
       <c r="B146" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C146" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>200</v>
+      <c r="C146" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4609,14 +4750,14 @@
       <c r="B147" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>200</v>
+      <c r="C147" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4626,14 +4767,14 @@
       <c r="B148" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C148" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>202</v>
+      <c r="C148" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>204</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4643,14 +4784,14 @@
       <c r="B149" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C149" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>202</v>
+      <c r="C149" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>204</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4660,14 +4801,14 @@
       <c r="B150" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C150" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>202</v>
+      <c r="C150" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>204</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4677,7 +4818,7 @@
       <c r="B151" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D151" s="3"/>
+      <c r="D151" s="6"/>
     </row>
     <row r="152" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="n">
@@ -4694,17 +4835,17 @@
       <c r="B153" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C153" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>204</v>
+      <c r="C153" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4714,17 +4855,17 @@
       <c r="B154" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C154" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>204</v>
+      <c r="C154" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K154" s="4" t="s">
-        <v>206</v>
+        <v>15</v>
+      </c>
+      <c r="K154" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4734,17 +4875,17 @@
       <c r="B155" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C155" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>204</v>
+      <c r="C155" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K155" s="4" t="s">
-        <v>206</v>
+        <v>15</v>
+      </c>
+      <c r="K155" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4754,17 +4895,17 @@
       <c r="B156" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C156" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>204</v>
+      <c r="C156" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K156" s="4" t="s">
-        <v>206</v>
+        <v>15</v>
+      </c>
+      <c r="K156" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4774,17 +4915,17 @@
       <c r="B157" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C157" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>204</v>
+      <c r="C157" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K157" s="4" t="s">
-        <v>207</v>
+        <v>15</v>
+      </c>
+      <c r="K157" s="7" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4794,17 +4935,17 @@
       <c r="B158" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C158" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>204</v>
+      <c r="C158" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K158" s="4" t="s">
-        <v>207</v>
+        <v>15</v>
+      </c>
+      <c r="K158" s="7" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4814,17 +4955,17 @@
       <c r="B159" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C159" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>204</v>
+      <c r="C159" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K159" s="4" t="s">
-        <v>207</v>
+        <v>15</v>
+      </c>
+      <c r="K159" s="7" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4834,17 +4975,17 @@
       <c r="B160" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C160" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>204</v>
+      <c r="C160" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K160" s="4" t="s">
-        <v>207</v>
+        <v>15</v>
+      </c>
+      <c r="K160" s="7" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4854,17 +4995,17 @@
       <c r="B161" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C161" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>204</v>
+      <c r="C161" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K161" s="4" t="s">
-        <v>208</v>
+        <v>15</v>
+      </c>
+      <c r="K161" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4874,17 +5015,17 @@
       <c r="B162" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C162" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>204</v>
+      <c r="C162" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K162" s="4" t="s">
-        <v>208</v>
+        <v>15</v>
+      </c>
+      <c r="K162" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4894,17 +5035,17 @@
       <c r="B163" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C163" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>204</v>
+      <c r="C163" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K163" s="4" t="s">
-        <v>208</v>
+        <v>15</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4914,17 +5055,17 @@
       <c r="B164" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C164" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>204</v>
+      <c r="C164" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K164" s="4" t="s">
-        <v>208</v>
+        <v>15</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4934,17 +5075,17 @@
       <c r="B165" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C165" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>204</v>
+      <c r="C165" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K165" s="4" t="s">
-        <v>209</v>
+        <v>15</v>
+      </c>
+      <c r="K165" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4954,17 +5095,17 @@
       <c r="B166" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C166" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D166" s="3" t="s">
-        <v>204</v>
+      <c r="C166" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K166" s="4" t="s">
-        <v>209</v>
+        <v>15</v>
+      </c>
+      <c r="K166" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4974,17 +5115,17 @@
       <c r="B167" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C167" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>204</v>
+      <c r="C167" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K167" s="4" t="s">
-        <v>209</v>
+        <v>15</v>
+      </c>
+      <c r="K167" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4994,17 +5135,17 @@
       <c r="B168" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C168" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>204</v>
+      <c r="C168" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K168" s="4" t="s">
-        <v>209</v>
+        <v>15</v>
+      </c>
+      <c r="K168" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5014,17 +5155,17 @@
       <c r="B169" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C169" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>204</v>
+      <c r="C169" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K169" s="4" t="s">
-        <v>210</v>
+        <v>15</v>
+      </c>
+      <c r="K169" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5034,17 +5175,17 @@
       <c r="B170" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C170" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>204</v>
+      <c r="C170" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K170" s="4" t="s">
-        <v>210</v>
+        <v>15</v>
+      </c>
+      <c r="K170" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5054,17 +5195,17 @@
       <c r="B171" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C171" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>204</v>
+      <c r="C171" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K171" s="4" t="s">
-        <v>210</v>
+        <v>15</v>
+      </c>
+      <c r="K171" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5074,17 +5215,17 @@
       <c r="B172" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>204</v>
+      <c r="C172" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K172" s="4" t="s">
-        <v>210</v>
+        <v>15</v>
+      </c>
+      <c r="K172" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5094,17 +5235,17 @@
       <c r="B173" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C173" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>204</v>
+      <c r="C173" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K173" s="4" t="s">
-        <v>210</v>
+        <v>15</v>
+      </c>
+      <c r="K173" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5114,14 +5255,14 @@
       <c r="B174" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C174" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D174" s="3" t="s">
-        <v>212</v>
+      <c r="C174" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5131,14 +5272,14 @@
       <c r="B175" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C175" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>212</v>
+      <c r="C175" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5148,14 +5289,14 @@
       <c r="B176" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C176" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>212</v>
+      <c r="C176" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5165,14 +5306,14 @@
       <c r="B177" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C177" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>212</v>
+      <c r="C177" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5182,14 +5323,14 @@
       <c r="B178" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C178" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>212</v>
+      <c r="C178" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5199,14 +5340,14 @@
       <c r="B179" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C179" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>214</v>
+      <c r="C179" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5216,14 +5357,14 @@
       <c r="B180" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C180" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>214</v>
+      <c r="C180" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D180" s="11" t="s">
+        <v>216</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5233,14 +5374,14 @@
       <c r="B181" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C181" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D181" s="4" t="s">
-        <v>214</v>
+      <c r="C181" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5258,17 +5399,17 @@
       <c r="B183" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C183" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>216</v>
+      <c r="C183" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5278,17 +5419,17 @@
       <c r="B184" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C184" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>216</v>
+      <c r="C184" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K184" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5298,17 +5439,17 @@
       <c r="B185" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C185" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>216</v>
+      <c r="C185" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K185" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5318,17 +5459,17 @@
       <c r="B186" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C186" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>216</v>
+      <c r="C186" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K186" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5338,17 +5479,17 @@
       <c r="B187" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C187" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>216</v>
+      <c r="C187" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K187" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5358,17 +5499,17 @@
       <c r="B188" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C188" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>216</v>
+      <c r="C188" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K188" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5378,17 +5519,17 @@
       <c r="B189" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C189" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>216</v>
+      <c r="C189" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K189" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5398,17 +5539,17 @@
       <c r="B190" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C190" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>216</v>
+      <c r="C190" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5418,17 +5559,17 @@
       <c r="B191" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C191" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>216</v>
+      <c r="C191" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5438,17 +5579,17 @@
       <c r="B192" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C192" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D192" s="3" t="s">
-        <v>216</v>
+      <c r="C192" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5458,17 +5599,17 @@
       <c r="B193" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C193" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>216</v>
+      <c r="C193" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5478,17 +5619,17 @@
       <c r="B194" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C194" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>216</v>
+      <c r="C194" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5498,17 +5639,17 @@
       <c r="B195" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C195" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>216</v>
+      <c r="C195" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K195" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5518,17 +5659,17 @@
       <c r="B196" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C196" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>216</v>
+      <c r="C196" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5538,17 +5679,17 @@
       <c r="B197" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C197" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>216</v>
+      <c r="C197" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5558,17 +5699,17 @@
       <c r="B198" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C198" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D198" s="3" t="s">
-        <v>216</v>
+      <c r="C198" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5578,17 +5719,17 @@
       <c r="B199" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C199" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>216</v>
+      <c r="C199" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5598,17 +5739,17 @@
       <c r="B200" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C200" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>216</v>
+      <c r="C200" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5618,17 +5759,17 @@
       <c r="B201" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C201" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>216</v>
+      <c r="C201" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D201" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5638,17 +5779,17 @@
       <c r="B202" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C202" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>216</v>
+      <c r="C202" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5658,17 +5799,17 @@
       <c r="B203" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C203" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D203" s="3" t="s">
-        <v>216</v>
+      <c r="C203" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D203" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5678,14 +5819,14 @@
       <c r="B204" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C204" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>219</v>
+      <c r="C204" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D204" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5695,14 +5836,14 @@
       <c r="B205" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C205" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>219</v>
+      <c r="C205" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5712,14 +5853,14 @@
       <c r="B206" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C206" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>219</v>
+      <c r="C206" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5729,14 +5870,14 @@
       <c r="B207" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C207" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>219</v>
+      <c r="C207" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5746,14 +5887,14 @@
       <c r="B208" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C208" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>219</v>
+      <c r="C208" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5763,14 +5904,14 @@
       <c r="B209" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C209" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>221</v>
+      <c r="C209" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>223</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5780,14 +5921,14 @@
       <c r="B210" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C210" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>221</v>
+      <c r="C210" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>223</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5797,14 +5938,14 @@
       <c r="B211" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C211" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>221</v>
+      <c r="C211" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>223</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5830,17 +5971,17 @@
       <c r="B214" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C214" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>181</v>
+      <c r="C214" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5850,17 +5991,17 @@
       <c r="B215" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C215" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>181</v>
+      <c r="C215" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5870,17 +6011,17 @@
       <c r="B216" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C216" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>181</v>
+      <c r="C216" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5890,17 +6031,17 @@
       <c r="B217" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C217" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>181</v>
+      <c r="C217" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5910,17 +6051,17 @@
       <c r="B218" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C218" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>181</v>
+      <c r="C218" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K218" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5930,17 +6071,17 @@
       <c r="B219" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C219" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>181</v>
+      <c r="C219" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5950,17 +6091,17 @@
       <c r="B220" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C220" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>181</v>
+      <c r="C220" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K220" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5970,17 +6111,17 @@
       <c r="B221" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C221" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D221" s="3" t="s">
-        <v>181</v>
+      <c r="C221" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5990,17 +6131,17 @@
       <c r="B222" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C222" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>181</v>
+      <c r="C222" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K222" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6010,17 +6151,17 @@
       <c r="B223" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C223" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>181</v>
+      <c r="C223" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6030,17 +6171,17 @@
       <c r="B224" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C224" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>181</v>
+      <c r="C224" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6050,17 +6191,17 @@
       <c r="B225" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C225" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>181</v>
+      <c r="C225" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6070,17 +6211,17 @@
       <c r="B226" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C226" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>181</v>
+      <c r="C226" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K226" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6090,17 +6231,17 @@
       <c r="B227" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C227" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>181</v>
+      <c r="C227" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6110,17 +6251,17 @@
       <c r="B228" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C228" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>181</v>
+      <c r="C228" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6130,17 +6271,17 @@
       <c r="B229" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C229" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>181</v>
+      <c r="C229" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D229" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K229" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6150,17 +6291,17 @@
       <c r="B230" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C230" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>181</v>
+      <c r="C230" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D230" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K230" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6170,17 +6311,17 @@
       <c r="B231" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C231" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>181</v>
+      <c r="C231" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D231" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K231" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6190,17 +6331,17 @@
       <c r="B232" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C232" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>181</v>
+      <c r="C232" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K232" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6210,17 +6351,17 @@
       <c r="B233" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C233" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>181</v>
+      <c r="C233" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D233" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6230,17 +6371,17 @@
       <c r="B234" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C234" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>181</v>
+      <c r="C234" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D234" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6250,14 +6391,14 @@
       <c r="B235" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C235" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>225</v>
+      <c r="C235" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D235" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6267,14 +6408,14 @@
       <c r="B236" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C236" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>225</v>
+      <c r="C236" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D236" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6284,14 +6425,14 @@
       <c r="B237" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C237" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>225</v>
+      <c r="C237" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6301,14 +6442,14 @@
       <c r="B238" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C238" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D238" s="3" t="s">
-        <v>225</v>
+      <c r="C238" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D238" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6318,14 +6459,14 @@
       <c r="B239" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C239" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>225</v>
+      <c r="C239" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D239" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6335,14 +6476,14 @@
       <c r="B240" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C240" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>227</v>
+      <c r="C240" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6352,14 +6493,14 @@
       <c r="B241" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C241" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>227</v>
+      <c r="C241" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D241" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6369,14 +6510,14 @@
       <c r="B242" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C242" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>227</v>
+      <c r="C242" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6402,17 +6543,17 @@
       <c r="B245" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C245" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>229</v>
+      <c r="C245" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D245" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K245" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6422,17 +6563,17 @@
       <c r="B246" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C246" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D246" s="3" t="s">
-        <v>229</v>
+      <c r="C246" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D246" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K246" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6442,17 +6583,17 @@
       <c r="B247" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C247" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>229</v>
+      <c r="C247" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D247" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6462,17 +6603,17 @@
       <c r="B248" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C248" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D248" s="3" t="s">
-        <v>229</v>
+      <c r="C248" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D248" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6482,17 +6623,17 @@
       <c r="B249" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C249" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>229</v>
+      <c r="C249" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6502,17 +6643,17 @@
       <c r="B250" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C250" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>229</v>
+      <c r="C250" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D250" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K250" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6522,17 +6663,17 @@
       <c r="B251" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C251" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>229</v>
+      <c r="C251" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D251" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K251" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6542,17 +6683,17 @@
       <c r="B252" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C252" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>229</v>
+      <c r="C252" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D252" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6562,17 +6703,17 @@
       <c r="B253" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C253" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>229</v>
+      <c r="C253" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D253" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K253" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6582,17 +6723,17 @@
       <c r="B254" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C254" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D254" s="3" t="s">
-        <v>229</v>
+      <c r="C254" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D254" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K254" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6602,17 +6743,17 @@
       <c r="B255" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C255" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>229</v>
+      <c r="C255" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D255" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K255" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6622,17 +6763,17 @@
       <c r="B256" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C256" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>229</v>
+      <c r="C256" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D256" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K256" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6642,17 +6783,17 @@
       <c r="B257" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C257" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D257" s="3" t="s">
-        <v>229</v>
+      <c r="C257" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D257" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6662,17 +6803,17 @@
       <c r="B258" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C258" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>229</v>
+      <c r="C258" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D258" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6682,17 +6823,17 @@
       <c r="B259" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C259" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>229</v>
+      <c r="C259" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D259" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K259" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6702,17 +6843,17 @@
       <c r="B260" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C260" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>229</v>
+      <c r="C260" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D260" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K260" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6722,17 +6863,17 @@
       <c r="B261" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C261" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D261" s="3" t="s">
-        <v>229</v>
+      <c r="C261" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D261" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6742,17 +6883,17 @@
       <c r="B262" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C262" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D262" s="3" t="s">
-        <v>229</v>
+      <c r="C262" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K262" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6762,17 +6903,17 @@
       <c r="B263" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C263" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D263" s="3" t="s">
-        <v>229</v>
+      <c r="C263" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D263" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K263" s="4" t="s">
-        <v>236</v>
+        <v>15</v>
+      </c>
+      <c r="K263" s="7" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6782,17 +6923,17 @@
       <c r="B264" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C264" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D264" s="3" t="s">
-        <v>229</v>
+      <c r="C264" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D264" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K264" s="4" t="s">
-        <v>236</v>
+        <v>15</v>
+      </c>
+      <c r="K264" s="7" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6802,17 +6943,17 @@
       <c r="B265" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C265" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D265" s="3" t="s">
-        <v>229</v>
+      <c r="C265" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D265" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K265" s="4" t="s">
-        <v>236</v>
+        <v>15</v>
+      </c>
+      <c r="K265" s="7" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6822,17 +6963,17 @@
       <c r="B266" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C266" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>229</v>
+      <c r="C266" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K266" s="4" t="s">
-        <v>237</v>
+        <v>15</v>
+      </c>
+      <c r="K266" s="7" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6842,17 +6983,17 @@
       <c r="B267" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C267" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>229</v>
+      <c r="C267" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D267" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K267" s="4" t="s">
-        <v>237</v>
+        <v>15</v>
+      </c>
+      <c r="K267" s="7" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6862,17 +7003,17 @@
       <c r="B268" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C268" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>239</v>
+      <c r="C268" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D268" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K268" s="4" t="s">
-        <v>240</v>
+        <v>129</v>
+      </c>
+      <c r="K268" s="7" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6882,17 +7023,17 @@
       <c r="B269" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C269" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D269" s="3" t="s">
-        <v>239</v>
+      <c r="C269" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D269" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K269" s="4" t="s">
-        <v>240</v>
+        <v>129</v>
+      </c>
+      <c r="K269" s="7" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6902,14 +7043,14 @@
       <c r="B270" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C270" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D270" s="3" t="s">
-        <v>239</v>
+      <c r="C270" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D270" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6919,14 +7060,14 @@
       <c r="B271" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C271" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D271" s="3" t="s">
-        <v>239</v>
+      <c r="C271" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D271" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6936,14 +7077,14 @@
       <c r="B272" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C272" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D272" s="3" t="s">
-        <v>239</v>
+      <c r="C272" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D272" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6953,14 +7094,14 @@
       <c r="B273" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C273" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D273" s="3" t="s">
-        <v>242</v>
+      <c r="C273" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D273" s="6" t="s">
+        <v>244</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6970,7 +7111,7 @@
       <c r="B274" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D274" s="3"/>
+      <c r="D274" s="6"/>
     </row>
     <row r="275" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="n">
@@ -6979,17 +7120,17 @@
       <c r="B275" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C275" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>244</v>
+      <c r="C275" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D275" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K275" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6999,17 +7140,17 @@
       <c r="B276" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C276" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>244</v>
+      <c r="C276" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D276" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K276" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7019,17 +7160,17 @@
       <c r="B277" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C277" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>244</v>
+      <c r="C277" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D277" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K277" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7039,17 +7180,17 @@
       <c r="B278" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C278" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D278" s="3" t="s">
-        <v>244</v>
+      <c r="C278" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D278" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K278" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7059,17 +7200,17 @@
       <c r="B279" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C279" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>244</v>
+      <c r="C279" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D279" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K279" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7079,17 +7220,17 @@
       <c r="B280" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C280" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>244</v>
+      <c r="C280" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K280" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7099,17 +7240,17 @@
       <c r="B281" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C281" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>244</v>
+      <c r="C281" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K281" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7119,17 +7260,17 @@
       <c r="B282" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C282" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D282" s="3" t="s">
-        <v>244</v>
+      <c r="C282" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K282" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7139,17 +7280,17 @@
       <c r="B283" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C283" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>244</v>
+      <c r="C283" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K283" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7159,17 +7300,17 @@
       <c r="B284" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C284" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D284" s="3" t="s">
-        <v>244</v>
+      <c r="C284" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K284" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7179,17 +7320,17 @@
       <c r="B285" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C285" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>244</v>
+      <c r="C285" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K285" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7199,17 +7340,17 @@
       <c r="B286" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C286" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D286" s="3" t="s">
-        <v>244</v>
+      <c r="C286" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K286" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7219,17 +7360,17 @@
       <c r="B287" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C287" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D287" s="3" t="s">
-        <v>244</v>
+      <c r="C287" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K287" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7239,17 +7380,17 @@
       <c r="B288" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C288" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>244</v>
+      <c r="C288" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K288" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7259,17 +7400,17 @@
       <c r="B289" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C289" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>244</v>
+      <c r="C289" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K289" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7279,17 +7420,17 @@
       <c r="B290" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C290" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D290" s="3" t="s">
-        <v>244</v>
+      <c r="C290" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K290" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7299,17 +7440,17 @@
       <c r="B291" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C291" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D291" s="3" t="s">
-        <v>244</v>
+      <c r="C291" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7319,17 +7460,17 @@
       <c r="B292" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C292" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>244</v>
+      <c r="C292" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K292" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7339,17 +7480,17 @@
       <c r="B293" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C293" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D293" s="3" t="s">
-        <v>244</v>
+      <c r="C293" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K293" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7359,17 +7500,17 @@
       <c r="B294" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C294" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D294" s="3" t="s">
-        <v>244</v>
+      <c r="C294" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K294" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7379,17 +7520,17 @@
       <c r="B295" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C295" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>244</v>
+      <c r="C295" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7399,17 +7540,17 @@
       <c r="B296" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C296" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D296" s="3" t="s">
+      <c r="C296" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K296" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="G296" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K296" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7419,17 +7560,17 @@
       <c r="B297" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C297" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D297" s="3" t="s">
+      <c r="C297" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G297" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K297" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="G297" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K297" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7439,17 +7580,17 @@
       <c r="B298" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C298" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D298" s="3" t="s">
+      <c r="C298" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G298" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K298" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="G298" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K298" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7459,17 +7600,17 @@
       <c r="B299" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C299" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D299" s="3" t="s">
+      <c r="C299" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G299" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K299" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="G299" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K299" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7479,17 +7620,17 @@
       <c r="B300" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C300" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D300" s="3" t="s">
+      <c r="C300" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D300" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G300" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K300" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="G300" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K300" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7499,17 +7640,17 @@
       <c r="B301" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C301" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D301" s="3" t="s">
-        <v>249</v>
+      <c r="C301" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K301" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7519,14 +7660,14 @@
       <c r="B302" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C302" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>249</v>
+      <c r="C302" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D302" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7536,14 +7677,14 @@
       <c r="B303" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C303" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>249</v>
+      <c r="C303" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7569,17 +7710,17 @@
       <c r="B306" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C306" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>251</v>
+      <c r="C306" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K306" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7589,17 +7730,17 @@
       <c r="B307" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C307" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D307" s="3" t="s">
-        <v>251</v>
+      <c r="C307" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K307" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7609,17 +7750,17 @@
       <c r="B308" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C308" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D308" s="3" t="s">
-        <v>251</v>
+      <c r="C308" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K308" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7629,17 +7770,17 @@
       <c r="B309" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C309" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D309" s="3" t="s">
-        <v>251</v>
+      <c r="C309" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K309" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7649,17 +7790,17 @@
       <c r="B310" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C310" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D310" s="3" t="s">
-        <v>251</v>
+      <c r="C310" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K310" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7669,17 +7810,17 @@
       <c r="B311" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C311" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D311" s="3" t="s">
-        <v>251</v>
+      <c r="C311" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K311" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7689,17 +7830,17 @@
       <c r="B312" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C312" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D312" s="3" t="s">
-        <v>251</v>
+      <c r="C312" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D312" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7709,17 +7850,17 @@
       <c r="B313" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C313" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D313" s="3" t="s">
-        <v>251</v>
+      <c r="C313" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K313" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7729,17 +7870,17 @@
       <c r="B314" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C314" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D314" s="3" t="s">
-        <v>251</v>
+      <c r="C314" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K314" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7749,17 +7890,17 @@
       <c r="B315" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C315" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D315" s="3" t="s">
-        <v>251</v>
+      <c r="C315" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D315" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K315" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7769,17 +7910,17 @@
       <c r="B316" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C316" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D316" s="3" t="s">
-        <v>251</v>
+      <c r="C316" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D316" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K316" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7789,17 +7930,17 @@
       <c r="B317" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C317" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D317" s="3" t="s">
-        <v>251</v>
+      <c r="C317" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K317" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7809,17 +7950,17 @@
       <c r="B318" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C318" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D318" s="3" t="s">
-        <v>251</v>
+      <c r="C318" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D318" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K318" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7829,17 +7970,17 @@
       <c r="B319" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C319" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D319" s="3" t="s">
-        <v>251</v>
+      <c r="C319" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K319" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7849,17 +7990,17 @@
       <c r="B320" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C320" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D320" s="3" t="s">
-        <v>251</v>
+      <c r="C320" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D320" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K320" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7869,17 +8010,17 @@
       <c r="B321" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C321" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D321" s="3" t="s">
-        <v>251</v>
+      <c r="C321" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K321" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7889,17 +8030,17 @@
       <c r="B322" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C322" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D322" s="3" t="s">
-        <v>251</v>
+      <c r="C322" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D322" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K322" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7909,17 +8050,17 @@
       <c r="B323" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C323" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D323" s="3" t="s">
-        <v>251</v>
+      <c r="C323" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D323" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K323" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7929,17 +8070,17 @@
       <c r="B324" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C324" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D324" s="3" t="s">
-        <v>251</v>
+      <c r="C324" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D324" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K324" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7949,17 +8090,17 @@
       <c r="B325" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C325" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D325" s="3" t="s">
-        <v>251</v>
+      <c r="C325" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K325" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7969,17 +8110,17 @@
       <c r="B326" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C326" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D326" s="3" t="s">
-        <v>251</v>
+      <c r="C326" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D326" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K326" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7989,17 +8130,17 @@
       <c r="B327" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C327" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D327" s="3" t="s">
+      <c r="C327" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G327" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K327" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="G327" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K327" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8009,17 +8150,17 @@
       <c r="B328" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C328" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D328" s="3" t="s">
-        <v>261</v>
+      <c r="C328" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D328" s="6" t="s">
+        <v>263</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K328" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8029,17 +8170,17 @@
       <c r="B329" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C329" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D329" s="3" t="s">
-        <v>261</v>
+      <c r="C329" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D329" s="6" t="s">
+        <v>263</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K329" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8049,17 +8190,17 @@
       <c r="B330" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C330" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D330" s="3" t="s">
-        <v>261</v>
+      <c r="C330" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D330" s="6" t="s">
+        <v>263</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K330" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8069,17 +8210,17 @@
       <c r="B331" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C331" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D331" s="3" t="s">
-        <v>261</v>
+      <c r="C331" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D331" s="6" t="s">
+        <v>263</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K331" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8089,17 +8230,17 @@
       <c r="B332" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C332" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D332" s="3" t="s">
-        <v>263</v>
+      <c r="C332" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D332" s="6" t="s">
+        <v>265</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K332" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8109,17 +8250,17 @@
       <c r="B333" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C333" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D333" s="3" t="s">
-        <v>263</v>
+      <c r="C333" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D333" s="6" t="s">
+        <v>265</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K333" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8129,14 +8270,14 @@
       <c r="B334" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C334" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D334" s="3" t="s">
-        <v>263</v>
+      <c r="C334" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D334" s="6" t="s">
+        <v>265</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8146,7 +8287,7 @@
       <c r="B335" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D335" s="3"/>
+      <c r="D335" s="6"/>
     </row>
     <row r="336" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="n">
@@ -8155,17 +8296,17 @@
       <c r="B336" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C336" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D336" s="3" t="s">
-        <v>265</v>
+      <c r="C336" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D336" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K336" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8175,17 +8316,17 @@
       <c r="B337" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C337" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D337" s="3" t="s">
-        <v>265</v>
+      <c r="C337" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D337" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K337" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8195,17 +8336,17 @@
       <c r="B338" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C338" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D338" s="3" t="s">
-        <v>265</v>
+      <c r="C338" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D338" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K338" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8215,17 +8356,17 @@
       <c r="B339" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C339" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D339" s="3" t="s">
-        <v>265</v>
+      <c r="C339" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K339" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8235,17 +8376,17 @@
       <c r="B340" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C340" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D340" s="3" t="s">
-        <v>265</v>
+      <c r="C340" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K340" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8255,17 +8396,17 @@
       <c r="B341" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C341" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D341" s="3" t="s">
-        <v>265</v>
+      <c r="C341" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K341" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8275,17 +8416,17 @@
       <c r="B342" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C342" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D342" s="3" t="s">
-        <v>265</v>
+      <c r="C342" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K342" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8295,17 +8436,17 @@
       <c r="B343" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C343" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D343" s="3" t="s">
-        <v>265</v>
+      <c r="C343" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K343" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8315,17 +8456,17 @@
       <c r="B344" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C344" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D344" s="3" t="s">
-        <v>265</v>
+      <c r="C344" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D344" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K344" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8335,17 +8476,17 @@
       <c r="B345" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C345" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D345" s="3" t="s">
-        <v>265</v>
+      <c r="C345" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G345" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K345" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8355,17 +8496,17 @@
       <c r="B346" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C346" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D346" s="3" t="s">
-        <v>265</v>
+      <c r="C346" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D346" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K346" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8375,17 +8516,17 @@
       <c r="B347" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C347" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D347" s="3" t="s">
-        <v>265</v>
+      <c r="C347" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D347" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G347" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K347" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8395,17 +8536,17 @@
       <c r="B348" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C348" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D348" s="3" t="s">
-        <v>265</v>
+      <c r="C348" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D348" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K348" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8415,17 +8556,17 @@
       <c r="B349" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C349" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D349" s="3" t="s">
-        <v>265</v>
+      <c r="C349" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D349" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K349" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8435,17 +8576,17 @@
       <c r="B350" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C350" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D350" s="3" t="s">
-        <v>265</v>
+      <c r="C350" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D350" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K350" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8455,17 +8596,17 @@
       <c r="B351" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C351" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D351" s="3" t="s">
-        <v>265</v>
+      <c r="C351" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D351" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K351" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8475,17 +8616,17 @@
       <c r="B352" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C352" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D352" s="3" t="s">
-        <v>265</v>
+      <c r="C352" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D352" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K352" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8495,17 +8636,17 @@
       <c r="B353" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C353" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D353" s="3" t="s">
-        <v>265</v>
+      <c r="C353" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D353" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K353" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8515,17 +8656,17 @@
       <c r="B354" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C354" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D354" s="3" t="s">
-        <v>265</v>
+      <c r="C354" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D354" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K354" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8535,14 +8676,14 @@
       <c r="B355" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C355" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D355" s="3" t="s">
-        <v>265</v>
+      <c r="C355" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D355" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8552,14 +8693,14 @@
       <c r="B356" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C356" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="D356" s="3" t="s">
-        <v>265</v>
+      <c r="C356" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D356" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8569,14 +8710,14 @@
       <c r="B357" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C357" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D357" s="3" t="s">
-        <v>273</v>
+      <c r="C357" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D357" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8586,14 +8727,14 @@
       <c r="B358" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C358" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D358" s="3" t="s">
-        <v>273</v>
+      <c r="C358" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D358" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8603,14 +8744,14 @@
       <c r="B359" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C359" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D359" s="3" t="s">
-        <v>273</v>
+      <c r="C359" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D359" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8620,14 +8761,14 @@
       <c r="B360" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C360" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D360" s="3" t="s">
-        <v>273</v>
+      <c r="C360" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D360" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8637,14 +8778,14 @@
       <c r="B361" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C361" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D361" s="3" t="s">
-        <v>273</v>
+      <c r="C361" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D361" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8654,14 +8795,14 @@
       <c r="B362" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C362" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D362" s="3" t="s">
-        <v>275</v>
+      <c r="C362" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D362" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8671,14 +8812,14 @@
       <c r="B363" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C363" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D363" s="3" t="s">
-        <v>275</v>
+      <c r="C363" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D363" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8688,14 +8829,14 @@
       <c r="B364" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C364" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D364" s="3" t="s">
-        <v>275</v>
+      <c r="C364" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D364" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8705,7 +8846,7 @@
       <c r="B365" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D365" s="3"/>
+      <c r="D365" s="6"/>
     </row>
     <row r="366" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="n">
@@ -8716,6 +8857,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" display="https://www.youtube.com/watch?v=zZZKL-H-MXs"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/public/dailyArticles.xlsx
+++ b/public/dailyArticles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="349">
   <si>
     <t xml:space="preserve">Day</t>
   </si>
@@ -59,12 +59,22 @@
   </si>
   <si>
     <t xml:space="preserve">Spend a few meaningful minutes with your child today—be present and explore their rights through a quick, hands-on activity!
-Time: 3–5 Minutes
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Time: 3–5 Minutes
 Materials: None (just your hands) | Use your child’s hand to help them understand their rights. 
 Feel free to use your own words to make it simple and clear for them!
 </t>
-  </si>
-  <si>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -151,14 +161,32 @@
     <t xml:space="preserve">Day 2: The "Shield of Care" Activity</t>
   </si>
   <si>
-    <t xml:space="preserve">Let's explore more child rights together with a quick, hands-on activity! 
-Time: 5 Minutes
+    <t xml:space="preserve">Let's explore more child rights together with a quick, hands-on activity! </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Time: 5 Minutes
 Materials: None (just you and your child's imagination)
 Feel free to use your own words to make it simple and clear for them!
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The Small Circle (The Child)
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1. The Small Circle (The Child)
 Action: Have the child cup their hands like they are holding a tiny ball.
 The Talk: "This little circle is you. You are the most important part of this story!"
 2. The Shield (Parents &amp; Guardians â€” Article 18)
@@ -170,6 +198,7 @@
 The Takeaway
 “You have the most important job of doing what’s best for the child, and the government is here to help you.”
 </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Article 18: Responsibility of Parents
@@ -209,13 +238,72 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Health and medical services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Article 24-26 in simple words (10-15mins), then let the child draw, repeat, or share it with the family.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/example.pdf</t>
+    <t xml:space="preserve">Day 3: The "Healthy &amp; Checked" Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another day, another interactive activity for you and your child!</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Time: 5 Minutes 
+Materials: None (just your surroundings)
+Feel free to use your own words to make it simple and clear for them!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1. The "Fuel Up" Check (Article 24)
+Action: Have your child take a sip of water or a bite of a snack.
+The Talk: "Just like a car needs gas, your body needs 'fuel' to grow! You have the right to the very best health—this means clean water, good food, and a doctor/nurse to help you if you feel sick. We work together to keep your 'fuel tank' full and healthy."
+2. The "Safety Check-In" (Article 26)
+Action: Give your child a quick shoulder squeeze or a high-five.
+The Talk: "Sometimes, children have to stay away from home for a little while—maybe at a hospital or a special school to get extra help. No matter where a child is, grown-ups must check in on them regularly. This ensures they are happy, safe, and in the best place for them. You are never forgotten!"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">The Takeaway
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">“When your child is away, check in often to ensure their new environment is a safe space for their protection.”
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 24: Health and Medical Services
+Children have the right to the best healthcare possible, clean water to drink, healthy food and a clean and safe environment to live in. All adults and children should have information about how to stay safe and healthy.
+Article 26: Social Security
+Every child who has been placed somewhere away from home - for their care, protection or health – should have their situation checked regularly to see if everything is going well and if this is still the best place for the child to be.
+</t>
   </si>
   <si>
     <r>
@@ -250,10 +338,30 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Standard of living</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 27 and 31  in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 4: The "Hunt &amp; Dance" Activity
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To wrap up the Rights to Survival, let’s take this small step for them. It’s a great way to help them rest and stay balanced!
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time: 5 Minutes
+Materials: Just the things around you!
+Feel free to use your own words to make it simple and clear for them!
+Point to your child's clothes, food, bed, and if it’s okay to play and relax. 
+Ask if it’s their right to have that.
+If they hesitate, cheer them on with a "Yes!" 
+The Takeaway:
+“Your child has the right to a safe home, good food, and plenty of time to play and rest.”
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 27: Standard of Living
+Children have the right to food, clothing and a safe place to live so they can develop in the best possible way. The government should help families and children who cannot afford this.
+Article 31: Rest, play, and free time
+Every child has the right to rest, relax, play and to take part in cultural and creative activities.
+</t>
   </si>
   <si>
     <r>
@@ -288,19 +396,93 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Non-discrimination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 2 and 11 in simple words (10-15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 5: The "All-Access Armor" Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It’s time to learn more about their rights to protection.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time: 5–7 Minutes
+Materials: None (just your imagination)
+Feel free to use your own words to make it simple and clear for them!
+ Point to different colors around the room or on your clothes.
+Tell them that just like these colors, children look and speak differently. Their rights to be safe and loved are always the same!
+The Takeaway:
+"Your children are just as important as everyone else, and should have a safe place with the people who love them."
+The Takeaway:
+"Your children are just as important as everyone else, and should have a safe place with the people who love them."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learn More:
+Article 2: Non-discrimination
+All children have all these rights, no matter who they are, where they live, what language they speak, what their religion is, what they think, what they look like, if they are a boy or girl, if they have a disability, if they are rich or poor, and no matter who their parents or families are or what their parents or families believe or do. No child should be treated unfairly for any reason.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day5.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Protection from abuse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 19 and 20 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 6: The "Hand of Safety &amp; Belonging" Activity
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s practice some ways to help your child to be aware, so they can protect themselves.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Time: 5–7 Minutes
+Materials: Your hand (or a piece of paper and a pencil)
+Feel free to use your own words to make it simple and clear for them!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. The "Hand of Help" - Safety Network (Article 19)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Action: Have the child hold up their hand. Point to each finger one by one.
+The Talk: "You have the right to be safe. If someone ever hurts you or makes you feel scared, you have a 'Hand of Help.' Let’s name five trusted grown-ups—one for each finger—who you can tell. If the first person doesn't listen, you keep going to the next finger until you are safe."
+The Fingers:
+Thumb: Me (Mama/Papa/Guardian).
+Pointer: A teacher, guidance counselor, police, or barangay officials. (Duty Bearers)
+Middle: A trusted relative (Tito/Tita/Lolo/Lola).
+Ring: A kind neighbor or family friend.
+Pinky: A helper in the community (like a nurse or a guard).
+The Takeaway
+“Your child has the right to be protected from harm by people you trust.”
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 19: Protection from Abuse
+Governments must protect children from violence, abuse and being neglected by anyone who looks after them.
+Link: https://www.youtube.com/watch?v=qxmwXGruiWY
+</t>
   </si>
   <si>
     <t xml:space="preserve">              }}</t>
@@ -309,145 +491,506 @@
     <t xml:space="preserve">/images/lessons/jan/month1-day6.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Refugee children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 22 and 25 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 7:  Superpower Session: The Shield &amp; The Scout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Another activity to help your child understand that wherever they go, their rights stay with them.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Time: 5–7 Minutes
+Materials: None (only iImagination)
+Feel free to use your own words to make it simple and clear for them!
+Have your child pretend to put on a backpack.
+Explain that their rights are like what's inside the bag. They stay inside even if you move to new place
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> The Takeaway:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">"Whether your child will move across the world, their safety and rights stay with them. “
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 22: Refugee Children
+Children who move from their home country to another country as refugees (because it was not safe for them to stay there) should get help and protection and have the same rights as children born in that country.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day7.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Child labour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 32 and 33 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 8: The Safety Fact-Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal: Knowing the difference between "helping out" and "harmful work," and keeping the body strong.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The "15 &amp; Free" Rule - (Article 32) Child Labor
+The Fact: Children under 15 should not have a "job." Their main job is school. Helping at home with chores is okay, but work that is dangerous or stops school is a "No-Go."
+The Quick Game: Ask your child, "Which one is a 'Yes' and which one is a 'No'?"
+Folding the laundry? (YES!)
+Working in a factory or a mine? (NO!)
+Helping with the dishes? (YES!)
+Missing school to go work for money? (NO!)
+The Talk: "You have the right to be a student. No one can make you do heavy or scary work that hurts your body or stops you from learning. When you are over 15 and 18, work must still be safe and fair."
+The Takeaway:
+“If under 15, their only job is school and play, not dangerous work. “
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 32: Child Labour
+Children have the right to be protected from doing work that is dangerous or bad for their education, health or development. If children work, they have the right to be safe and paid fairly.
+Link: https://elibrary.judiciary.gov.ph/thebookshelf/showdocs/2/1388 </t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day8.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Protection from sexual exploitation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 34 and 35 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 9: The "Priceless" Safety Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have the child point to the areas a swimsuit covers (chest, bottom, and between the legs.
+No one is allowed to touch them, look at them, or ask them to show it.
+If anyone tries, they should say “STOP” and tell you right away.
+The Takeaway:
+The private parts are for you only, and they’re so valuable that they can never be bought or sold. They stay safe right here where you are loved.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 34: Protection from Sexual Exploitation
+The government should protect children from sexual exploitation (being taken advantage of) and sexual abuse, including by people forcing children to have sex for money, or making sexual pictures or films of them.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day9.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Protection from all other forms of exploitation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 36 and 37 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 10: The "Fairness &amp; Kindness" Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal: To know that you are not a "tool" for others and that everyone deserves to be treated humanely.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice them to say “NO,” “STOP,” or “AYAW” loudly and firmly with a "stop" hand gesture.
+If anyone makes them feel unsafe, tell them to use their loud voice and hand. 
+The Takeaway:
+“They have the right to say “No” if a situation feels unsafe to them.”
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 36- Protection from All other Forms of Exploitation
+Children have the right to be protected from all other kinds of exploitation (being taken advantage of), even if these are not specifically mentioned in this Convention.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day10.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">War and armed conflict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 38 and 39 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 11: The "Shield &amp; Band-Aid" Moment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal: To know that children are a "No-Fight Zone" and that they always get help to feel better.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tell your child who they should trust.
+Name trusted people like teachers, police, and nurses that will keep them safe and protected!
+The Takeaway:
+“Your child deserves to experience safety from those who are in the role of protecting them.”
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 38: War and Armed Conflict
+Children have the right to be protected during war. No child under 15 can join the army or take part in war.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day11.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Juvenile justice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Article 40 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 12: The "U-Turn" Mission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal: To know that if you make a mistake, the law helps you turn around and find the right way home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teach them who to ask for help if they commit a mistake or break a law,
+Such as parents, police, or teachers, to help them learn from the situation.
+The Takeaway
+“Lead children back from mistakes and make things right by seeking the help or treatment needed.”
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 40: Juvenile Justice
+Children accused of breaking the law have the right to legal help and fair treatment. There should be lots of solutions to help these children become good members of their communities. Prison should only be the last choice.
+That’s a wrap on our “Rights to Protection” series! We hope these reminders serve as a helpful guide in your journey as parents. Remember, you and the law are a team in keeping every child safe from harm.
+Stay tuned—we have more insightful topics coming your way soon that you won't want to miss!
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day12.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Respect for parental rights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 5 and 7 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 13: The Great Road Trip: Me and My Guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal: To understand that being "registered" with a name and nationality is what gives them the "ticket" to go to school, see a doctor, and be protected. To understand that parental guidance is like "Co-Driving"—it’s there to keep you on the road until you’re ready for the wheel.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1: The All-Access Pass(Article 7)
+Show them their birth certificate.
+Point the important information.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Full Name (Your official "User ID")
+Birthday &amp; Time (When your story began)
+Parents (Your official support team)
+Tell them the paper is essential for their future.
+The Takeaway:
+“Your child’s birth certificate is more than just paperâ€”it is their legal shield and their ticket to protection as a Filipino. By securing this document, you are giving them an official voice. As you guide them through life, you are teaching them how to use that voice to navigate the world safely.”
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 7: Name and State Membership
+Children must be registered when they are born and given a name which is officially recognized by the government. Children must have a nationality (belong to a country). Whenever possible, children should know their parents and be looked after by them.
+Link: https://psahelpline.ph/psa-birth-certificate#what-is-psa-birth-certificate </t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day13.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Protection of identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 8 and 10 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 14: The "Invisible String" Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal: To show that your name and your family connection are yours forever, and no one can cut that tie. (Article 8 &amp; 10)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Gentle “Hatak" (Tug), hold your child’s hand or wrist gently.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">They have an Invisible String. Their name,family and nationality are theirs forever.
+An Invisible String that connects them to you and to our country. 
+The Takeaway
+“Your child’s identity is rooted in your family relations. Knowing "who they belong to" gives them confidence.”
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 10: Family Reunification
+If a child lives in a different country than their parents, governments must let the child and parents travel so that they can stay in contact and be together.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day14.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Adoption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 21 and 23 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 15: The Safety Vest Assurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let’s teach them new things so they don’t have to be afraid of big ideas—and so they can share what they learn with others who might need it too! (Article 21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action: Have the child hold the child’s hands firmly or give a "Secure Hug" while talking.
+The Concept: Just like you wear a life vest on a boat—not because you will fall in, but so you are safe just in case—the law has a "Back-up Plan" called Adoption. It’s like a car having a spare tire; it’s there to make sure everyone keeps moving forward safely.
+The Talk: "Anak, did you know the law has a special 'Safety Vest' for all children? It’s called Adoption. 
+We are in our 'family boat' right now, and we are staying together. You aren't being adopted because you already have your home and your team with me. But this law is for children who don't have a 'boat' or a family of their own yet. It’s the government’s way of making sure every child in the world has a safe place to sleep and a family to love them. It promises that no child will ever have to be alone."
+The Takeaway
+“These rules are just the world’s way of promising to keep your child safe and loved.”
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 21: Adoption
+When children are adopted, the most important thing is to do what is best for them. If a child cannot be properly looked after in their own country – for example by living with another family – then they might be adopted in another country.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day15.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Disabled children</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 28 and 29 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 16: No One Left Behind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask these questions to your child:
+Can a blind person go to school? (Yes)
+Can a deaf person go to school? (Yes)
+Can an underprivileged go to school? (Yes)
+The Takeaway:
+“Education is for everyone, no matter who they are.”
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 23: Disabled Children
+Every child with a disability should enjoy the best possible life in society. Governments should remove all obstacles for children with disabilities to become independent and to participate actively in the community.
+Article 28: Education
+Every child has the right to an education. Primary education should be free. Secondary and higher education should be available to every child. Children should be encouraged to go to school to the highest level possible. Discipline in schools should respect children’s rights and never use violence.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day16.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Educational aims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Article 30 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 17: To Be Belong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask your child what events they like to join with their friends?
+Explain they can meet anyone, as long as everyone stays safe and kind.
+The Takeaway:
+You should let your child join different groups, as long as they’re safe.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 29: Educational Aims
+Children’s education should help them fully develop their personalities, talents and abilities. It should teach them to understand their own rights, and to respect other people’s rights, cultures and differences. It should help them to live peacefully and protect the environment.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day17.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">The well-being of the child is paramount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Article 3 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 18: Child’s Best Interest</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Time: 5 Minutes
+Materials: None (Just your hands!)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. The Lesson: "Is it Good for the Kid?"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">The Talk: "Imagine I’m deciding on a new job. I have to ask: 'Will this keep my child safe? Will they be looked after well?' If the answer is YES, I give the decision a High-Five! If the answer is NO, I put my hand down. Adults must always choose what is best for you."
+The Takeaway:
+“Always consider the child’s best interest in every decision you make.”
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 3: The well-being of the child is paramount
+When adults make decisions, they should think about how their decisions will affect children. All adults should do what is best for children. Governments should make sure children are protected and looked after by their parents, or by other people when this is needed. Governments should make sure that people and places responsible for looking after children are doing a good job. 
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day18.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Freedom of opinion</t>
+    <t xml:space="preserve">Day 19: Speaker and Audience</t>
   </si>
   <si>
     <t xml:space="preserve">Explain Articles 12 and 13 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Time: 5 Minutes
+Materials: None (or a spoon/TV remote to act as a "Microphone")
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Let your child finish these sentences:
+Malingaw ko kung;
+Hadlok ko sa;
+Masuko ko kung;
+Sapotong ko kung;
+I enjoy!
+The Takeaway:
+‘Let your child feel heard and be taken seriously.”
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 12: The Child’s Freedom of Opinion
+Children have the right to give their opinions freely on issues that affect them. Adults should listen and take children seriously.
+Article 13: Freedom of Expression
+Children have the right to share freely with others what they learn, think and feel, by talking, drawing, writing or in any other way unless it harms other people.
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day19.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Freedom of thought, conscience, and religion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 14 and 15 in simple words (10–15 mins), then let the child draw, repeat, or share it with family.</t>
+    <t xml:space="preserve">Day 20: The Glowing Lantern</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Time: 8 Minutes
+Materials: 1 Piece of Paper and 1 Pen or Crayon
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Let your child draw a lightbulb
+Say that this light is a secret light inside them.
+Say no one can reach inside and turn it off. It only belongs to them.
+The Takeaway
+“Their thoughts are their own light, and they are free to shine them however they choose.” 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 14: Freedom of Thought, Conscience, and Religion.
+Children can choose their own thoughts, opinions and religion, but this should not stop other people from enjoying their rights. Parents can guide children so that as they grow up, they learn to properly use this right.
+Article 15: Right to Peaceful Public Gathering
+Children can join or set up groups or organisations, and they can meet with others, as long as this does not harm other people.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day20.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Protection of privacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explain Articles 16 and 17 in simple words (10–15 mins), then let the child draw, repeat, or share it with family</t>
+    <t xml:space="preserve">Day 21: The “Lock and Filter”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show your or their gadget to them.
+Ask them about the purpose of the gadget.
+Encourage them that they can get nice things on it but ask for guidance from you.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article 17: Access to Appropriate Information
+Children have the right to get information from the Internet, radio, television, newspapers, books and other sources. Adults should make sure the information they are getting is not harmful. Governments should encourage the media to share information from lots of different sources, in languages that all children can understand. 
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/jan/month1-day21.jpg</t>
   </si>
   <si>
+    <t xml:space="preserve">Day 22-25: Family Challenge - Family Child Rights Poster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each member contributes (parent writes, child draws/colors) a big paper or cardboard that says or centers around: “Our Family Protects Children's Rights”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 26: Family Challenge - Family Child Rights Poster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Place it inside the home as a reminder. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 27- 29: Social Media Challenge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share the photo of the poster (with or without faces) with caption: “Among pamilya naga kat-on ug naga supporta sa balaud para sa mga bata”</t>
+  </si>
+  <si>
     <t xml:space="preserve">REWARD DAY - Gauntlets of Safety</t>
   </si>
   <si>
-    <t xml:space="preserve">Congratulations! You learned your rights for 30 days!</t>
+    <t xml:space="preserve">Armor part earned: Armor of Honor, Gauntlets/Gloves — Congratulations! You learned your rights for 21 days! You now unlock the Gauntlets of Safety. These gloves give you the power to protect yourself, because you know what is right and fair for you.
+</t>
   </si>
   <si>
     <t xml:space="preserve">🎉 Amazing achievement! You've completed 30 days of learning about your rights!</t>
@@ -462,124 +1005,307 @@
     <t xml:space="preserve">These gloves give you the power to protect yourself, because you know what is right and fair for you.</t>
   </si>
   <si>
-    <t xml:space="preserve"> Add munggo with malunggay or kalabasa. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Rich in essential nutrients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ginisang munggo with malunggay and kalabasa is a nutritious Filipino dish rich in essential vitamins and minerals. Mung bean provides a good source of plant-based protein, dietary fiber, iron, and folate, which help support muscle growth, improve digestion, and prevent anemia. The addition of Moringa oleifera (malunggay) boosts the dish’s nutritional value because it is packed with Vitamin A, Vitamin C, calcium, iron, and antioxidants that strengthen immunity, promote healthy vision, and support strong bones. Meanwhile, Cucurbita moschata (kalabasa) supplies beta-carotene, fiber, and potassium, which help maintain good eyesight, heart health, and proper digestion. Together, these ingredients create a balanced, affordable, and nutrient-dense meal that supports overall health and well-being.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalabasa (Squash), Monggos (Mung Beans), and Malunggay (Moringa) are three common ingredients in Filipino cuisine that are not only affordable and accessible, but also highly nutritious. Together, they provide a powerful combination of vitamins, minerals, fiber, and plant-based protein that support overall health. Regularly including these foods in meals can help improve immunity, digestion, heart health, and energy levels.
-Kalabasa (squash) is rich in vitamin A in the form of beta-carotene, which is essential for good vision, healthy skin, and a strong immune system. Its bright orange color is a sign of its high antioxidant content, which helps protect the body from harmful free radicals. Kalabasa is also a good source of fiber, which supports healthy digestion and helps prevent constipation. Because it is naturally low in calories but filling, it can also help with maintaining a healthy weight.
-Monggos (mung beans) are an excellent source of plant-based protein, making them especially important for muscle repair and growth. They are rich in iron, which helps prevent anemia and supports healthy blood circulation. Monggos also contain fiber, potassium, and antioxidants that promote heart health by helping regulate blood pressure and cholesterol levels. Additionally, their complex carbohydrates provide steady energy, making them a great food for sustained strength throughout the day.
-Malunggay (moringa leaves) is often called a “superfood” because of its impressive nutritional profile. It contains high amounts of vitamins A, C, and E, which strengthen the immune system and protect cells from damage. Malunggay is also rich in calcium for strong bones, iron for healthy blood, and protein for tissue repair. Its anti-inflammatory and antioxidant properties may help reduce the risk of chronic diseases. When combined in dishes like monggos with malunggay and kalabasa, these ingredients create a balanced, nutrient-dense meal that supports overall health and well-being.
+    <t xml:space="preserve">Day 1: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add one simple, affordable nutritious food to any main meal (breakfast, lunch, or dinner).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredients:
+Munggo with Kalabasa or Malunggay
+Munggo (Mung Beans)
+ Packed with protein. 
+If meat is too expensive, Munggo gives your body the strength it needs to build muscles and stay strong.
+To make it even healthier for children, always add others like:
+Malunggay: For extra calcium and vitamins.
+Kalabasa: Loaded with Vitamin A (keeping the skin glowing).
 </t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/feb/day1.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Add malunggay leaves to tinola, munggo,or instant noodles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich in antioxidants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adding malunggay leaves to tinola, munggo, or even instant noodles is a simple way to make everyday meals more nutritious and rich in antioxidants. Moringa oleifera, commonly known as malunggay, contains powerful antioxidants such as vitamin C, beta-carotene, quercetin, and chlorogenic acid. These compounds help protect the body’s cells from damage caused by free radicals, which are linked to aging and various diseases. When added to dishes like Tinola, munggo, or instant noodles, malunggay enhances not only the flavor and color but also the nutritional value of the meal. Its high antioxidant content supports a stronger immune system, reduces inflammation, and promotes overall health, making it an easy and affordable way to boost daily nutrient intake.
+    <t xml:space="preserve">Day 2: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Malunggay (Moringa)
+Can be used for food or medicine
+Overflowing with antioxidants (clean waste).
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Read: Health Benefits of Malunggay: The Miracle Tree</t>
+  </si>
+  <si>
     <t xml:space="preserve">/images/lessons/feb/day2.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Add boiled egg (split in half if budget is tight)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contains protein</t>
+    <t xml:space="preserve">Day 3: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Egg
+Contain almost every nutrient a human body needs in one small, affordable package. 
+Protein in eggs is the "gold standard." 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Why Eggs Are the Best Protein for Kids</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/feb/day3.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Add banana (saging na saba or lakatan) for dessert or merienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich in fiber and potassium</t>
+    <t xml:space="preserve">Day 4: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Banana
+Famous for Potassium (a tiny "electrician" for body, carry small electrical signals that keep your heart, muscles, and nerves working perfectly)
+They contain "pectin," a fiber that helps with both constipation and diarrhea.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Bananas 101: Nutrition Facts and Health Benefits</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/feb/day4.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Add dilis (small dried fish) with egg fried rice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rich in calcium</t>
+    <t xml:space="preserve">Day 5: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Dilis (Anchovies) 
+One of the best sources of calcium, they help strengthen a child’s skeleton and teeth. 
+They can be added to Pinakbet or ground up to be added to Lugaw.
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/feb/day5.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve"> Add kamote (sweet potato) boiled or fried. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contains carbs</t>
+    <t xml:space="preserve">Day 6: Add Ingredients Challenge
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add one simple, affordable nutritious food to any main meal (breakfast, lunch, or dinner).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Kamote
+Best sources of complex carbohydrates
+It releases energy slowly, so children stay active and focused in school all morning without feeling tired or "low-batt."
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Sweet Potatoes vs. White Potatoes: Which is Healthier?
+</t>
   </si>
   <si>
     <t xml:space="preserve">/images/lessons/feb/day6.jpg</t>
   </si>
   <si>
+    <t xml:space="preserve">Day 7: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Gabi (Taro)
+ most reliable "energy crops"
+ a nutritional powerhouse for growing children and hard-working parents
+contains a surprising "double-defense" of Vitamins C (fight off coughs and colds) and E (keeps a child's skin from getting too dry), especially when you eat both the root and the leaves.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Taro Root: Benefits and Nutritional Facts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day7.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 8: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Sayote (Chayote)
+Often called the "Hydration Vegetable,” it’s so easy on the tummy.
+Surprisingly high in Folate (make new cells and healthy blood).
+To make it even healthier for children, always add others like:
+Malunggay: For extra calcium and vitamins.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Chayote (Sayote) Nutrition: Fiber, Folate, and More</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day8.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 9: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day9.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 10: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Apple
+"Crunchy Medicine,” chewing them helps clean a child's teeth and gums.
+Rich in Fiber (essential because it cleans everything out as it passes through).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Fiber and Teeth: Why Apples are Good for Gums</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day10.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day11: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day11.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 12: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Kamoteng Kahoy (Cassava)
+One of the most powerful "Energy Anchors" 
+It is packed with complex carbohydrates that take a long time to digest.
+It prevents "energy dips" during long school days or after-school play. It keeps a child's "battery" on full for much longer.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day12.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 13: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Sapsap (Ponyfish)
+Very high in Zinc. Helps the body grow taller and ensures a child's immune system can fight off coughs and colds.
+Has very fine bones, some of the calcium seeps into the broth, making it a "bone-building" soup.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: The Role of Zinc in Child Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day13.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 14: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day14.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 15: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredients:
+Munggo with Sotanghon
+Munggo (Mung Beans)
+ Packed with protein. 
+If meat is too expensive, Munggo gives your body the strength it needs to build muscles and stay strong.
+To make it even healthier for children, always add others like:
+Malunggay: For extra calcium and vitamins.
+Kalabasa: Loaded with Vitamin A (keeping the skin glowing).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day15.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 16: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient: 
+Noodles with Malunggay
+Malunggay (Moringa)
+Can be used for food or medicine
+Overflowing with antioxidants (clean waste).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Fortifying Instant Noodles with Moringa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day16.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 17: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Kinamatisang Dilis
+Dilis (Anchovies) 
+One of the best sources of calcium, they help strengthen a child’s skeleton and teeth. 
+They can be added to Pinakbet or ground up to be added to Lugaw.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Lycopene in Cooked Tomatoes: Why it's Healthier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day17.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 18: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient:
+Orange
+A single medium orange provides about 70% to 90% of the daily recommended intake of Vitamin C. 
+This antioxidant helps protect cells from damage and supports the production of white blood cells.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: The Immune-Boosting Benefits of Citrus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day18.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 19: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Additional Ingredient: Add Ampalaya to your Eggs!
+Egg
+Contain almost every nutrient a human body needs in one small, affordable package. 
+Protein in eggs is the "gold standard." 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day19.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 20: Add Ingredients Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uggested Additional Ingredient:
+Taro Chips
+Gabi (Taro)
+ most reliable "energy crops"
+ a nutritional powerhouse for growing children and hard-working parents
+contains a surprising "double-defense" of Vitamins C (fight off coughs and colds) and E (keeps a child's skin from getting too dry), especially when you eat both the root and the leaves.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read: Homemade Vegetable Chips: Nutritional Tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/images/lessons/feb/day20.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Add gabi/taro or squash to a simple sabaw </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Contains Vitamin C
- and E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day7.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day8.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add malunggay leaves to tinola, munggo,or intant noodles.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day9.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day10.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day11.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day12.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day13.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day14.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day15.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day16.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day17.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day18.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day19.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/images/lessons/feb/day20.jpg</t>
   </si>
   <si>
     <t xml:space="preserve"> Contains Vitamin C and E</t>
@@ -1317,7 +2043,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1355,8 +2081,30 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
@@ -1367,20 +2115,6 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1447,57 +2181,73 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1763,6 +2513,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="50.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="41.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1813,7 +2564,7 @@
       <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -1829,20 +2580,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="161.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="243.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -1858,21 +2609,24 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="246.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>25</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
@@ -1881,21 +2635,27 @@
         <v>16</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>28</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -1904,21 +2664,27 @@
         <v>16</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>31</v>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -1927,21 +2693,27 @@
         <v>16</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="232.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>34</v>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -1950,24 +2722,30 @@
         <v>16</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="111.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>38</v>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -1976,21 +2754,27 @@
         <v>16</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>41</v>
+      <c r="C9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -1999,21 +2783,25 @@
         <v>16</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>44</v>
+      <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -2022,21 +2810,27 @@
         <v>16</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="68.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>47</v>
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -2045,21 +2839,27 @@
         <v>16</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="68.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>50</v>
+      <c r="C12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -2068,21 +2868,27 @@
         <v>16</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="176.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>53</v>
+      <c r="C13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -2091,21 +2897,27 @@
         <v>16</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="171.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>56</v>
+      <c r="C14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -2114,21 +2926,27 @@
         <v>16</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>59</v>
+      <c r="C15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -2137,21 +2955,27 @@
         <v>16</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="162.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>62</v>
+      <c r="C16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -2160,21 +2984,25 @@
         <v>16</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>65</v>
+      <c r="C17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -2183,21 +3011,25 @@
         <v>16</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>68</v>
+      <c r="C18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
@@ -2206,21 +3038,25 @@
         <v>16</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="140.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>71</v>
+      <c r="C19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
@@ -2229,21 +3065,27 @@
         <v>16</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="164.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>74</v>
+      <c r="C20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -2252,21 +3094,25 @@
         <v>16</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>77</v>
+      <c r="C21" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -2275,21 +3121,25 @@
         <v>16</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>80</v>
+      <c r="C22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -2298,7 +3148,7 @@
         <v>16</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2308,7 +3158,12 @@
       <c r="B23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
@@ -2323,6 +3178,12 @@
       <c r="B24" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="C24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="G24" s="1" t="s">
         <v>15</v>
       </c>
@@ -2337,6 +3198,12 @@
       <c r="B25" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="C25" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -2345,6 +3212,12 @@
       <c r="B26" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="C26" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -2353,6 +3226,12 @@
       <c r="B27" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="C27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -2361,6 +3240,12 @@
       <c r="B28" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="C28" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
@@ -2369,6 +3254,12 @@
       <c r="B29" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="C29" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
@@ -2377,8 +3268,14 @@
       <c r="B30" s="1" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
@@ -2386,25 +3283,25 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>83</v>
+        <v>119</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2414,486 +3311,574 @@
       <c r="B32" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>91</v>
-      </c>
+      <c r="C32" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="11"/>
       <c r="G32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="8" t="b">
+      <c r="H32" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>95</v>
+      <c r="C33" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="8" t="b">
+      <c r="H33" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>98</v>
+      <c r="C34" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="8" t="b">
+      <c r="H34" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>101</v>
+      <c r="C35" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="8" t="b">
+      <c r="H35" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>104</v>
+      <c r="C36" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="8" t="b">
+      <c r="H36" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>107</v>
+      <c r="C37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H37" s="8" t="b">
+      <c r="H37" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B38" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>110</v>
+      <c r="C38" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H38" s="8" t="b">
+      <c r="H38" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B39" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>89</v>
+      <c r="C39" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H39" s="8" t="b">
+      <c r="H39" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>94</v>
+      <c r="C40" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H40" s="8" t="b">
+      <c r="H40" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>98</v>
+      <c r="C41" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="8" t="b">
+      <c r="H41" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>101</v>
+      <c r="C42" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H42" s="8" t="b">
+      <c r="H42" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>104</v>
+      <c r="C43" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H43" s="8" t="b">
+      <c r="H43" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B44" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>107</v>
+      <c r="C44" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H44" s="8" t="b">
+      <c r="H44" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B45" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>110</v>
+      <c r="C45" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H45" s="8" t="b">
+      <c r="H45" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B46" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>89</v>
+      <c r="C46" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="8" t="b">
+      <c r="H46" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B47" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>94</v>
+      <c r="C47" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H47" s="8" t="b">
+      <c r="H47" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B48" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>98</v>
+      <c r="C48" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H48" s="8" t="b">
+      <c r="H48" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="68.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B49" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>101</v>
+      <c r="C49" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H49" s="8" t="b">
+      <c r="H49" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="68.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B50" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>104</v>
+      <c r="C50" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H50" s="8" t="b">
+      <c r="H50" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="95.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B51" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>107</v>
+      <c r="C51" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H51" s="8" t="b">
+      <c r="H51" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2904,36 +3889,36 @@
         <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H52" s="8" t="b">
+      <c r="H52" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="82.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="83.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B53" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>128</v>
+      <c r="C53" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H53" s="8" t="b">
+        <v>200</v>
+      </c>
+      <c r="H53" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2945,13 +3930,13 @@
       <c r="B54" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>128</v>
+      <c r="C54" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H54" s="8" t="b">
+        <v>200</v>
+      </c>
+      <c r="H54" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2963,13 +3948,13 @@
       <c r="B55" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>130</v>
+      <c r="C55" s="11" t="s">
+        <v>201</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H55" s="8" t="b">
+        <v>200</v>
+      </c>
+      <c r="H55" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2981,13 +3966,13 @@
       <c r="B56" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>131</v>
+      <c r="C56" s="11" t="s">
+        <v>202</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H56" s="8" t="b">
+        <v>203</v>
+      </c>
+      <c r="H56" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -2999,13 +3984,13 @@
       <c r="B57" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>131</v>
+      <c r="C57" s="11" t="s">
+        <v>202</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H57" s="8" t="b">
+        <v>203</v>
+      </c>
+      <c r="H57" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3017,13 +4002,13 @@
       <c r="B58" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>131</v>
+      <c r="C58" s="11" t="s">
+        <v>202</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H58" s="8" t="b">
+        <v>203</v>
+      </c>
+      <c r="H58" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3035,7 +4020,7 @@
       <c r="B59" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="8" t="b">
+      <c r="H59" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3050,36 +4035,36 @@
       <c r="G60" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H60" s="8" t="b">
+      <c r="H60" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B61" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>133</v>
+      <c r="C61" s="11" t="s">
+        <v>204</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H61" s="8" t="b">
+      <c r="H61" s="12" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3090,20 +4075,20 @@
         <v>3</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H62" s="8" t="b">
+      <c r="H62" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3114,20 +4099,20 @@
         <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H63" s="8" t="b">
+      <c r="H63" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>140</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3138,20 +4123,20 @@
         <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H64" s="8" t="b">
+      <c r="H64" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3162,20 +4147,20 @@
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H65" s="8" t="b">
+      <c r="H65" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3186,20 +4171,20 @@
         <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H66" s="8" t="b">
+      <c r="H66" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3210,20 +4195,20 @@
         <v>3</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H67" s="8" t="b">
+      <c r="H67" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>152</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3234,20 +4219,20 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H68" s="8" t="b">
+      <c r="H68" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3258,20 +4243,20 @@
         <v>3</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H69" s="8" t="b">
+      <c r="H69" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3282,20 +4267,20 @@
         <v>3</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H70" s="8" t="b">
+      <c r="H70" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>140</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3306,20 +4291,20 @@
         <v>3</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H71" s="8" t="b">
+      <c r="H71" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3330,20 +4315,20 @@
         <v>3</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H72" s="8" t="b">
+      <c r="H72" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3354,20 +4339,20 @@
         <v>3</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H73" s="8" t="b">
+      <c r="H73" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3378,20 +4363,20 @@
         <v>3</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H74" s="8" t="b">
+      <c r="H74" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>152</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3402,20 +4387,20 @@
         <v>3</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H75" s="8" t="b">
+      <c r="H75" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3426,20 +4411,20 @@
         <v>3</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>135</v>
+        <v>206</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>136</v>
+        <v>207</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H76" s="8" t="b">
+      <c r="H76" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3450,20 +4435,20 @@
         <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>138</v>
+        <v>209</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H77" s="8" t="b">
+      <c r="H77" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>140</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3474,20 +4459,20 @@
         <v>3</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>141</v>
+        <v>212</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H78" s="8" t="b">
+      <c r="H78" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3498,20 +4483,20 @@
         <v>3</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H79" s="8" t="b">
+      <c r="H79" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3522,20 +4507,20 @@
         <v>3</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H80" s="8" t="b">
+      <c r="H80" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3546,20 +4531,20 @@
         <v>3</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H81" s="8" t="b">
+      <c r="H81" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>152</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3570,20 +4555,20 @@
         <v>3</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H82" s="8" t="b">
+      <c r="H82" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3594,17 +4579,17 @@
         <v>3</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H83" s="8" t="b">
+        <v>200</v>
+      </c>
+      <c r="H83" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>137</v>
+        <v>208</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3615,17 +4600,17 @@
         <v>3</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H84" s="8" t="b">
+        <v>200</v>
+      </c>
+      <c r="H84" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>140</v>
+        <v>211</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3636,17 +4621,17 @@
         <v>3</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H85" s="8" t="b">
+        <v>200</v>
+      </c>
+      <c r="H85" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3657,17 +4642,17 @@
         <v>3</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H86" s="8" t="b">
+        <v>200</v>
+      </c>
+      <c r="H86" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3678,17 +4663,17 @@
         <v>3</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>156</v>
+        <v>227</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H87" s="8" t="b">
+        <v>200</v>
+      </c>
+      <c r="H87" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3699,17 +4684,17 @@
         <v>3</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H88" s="8" t="b">
+        <v>203</v>
+      </c>
+      <c r="H88" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>152</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3720,17 +4705,17 @@
         <v>3</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H89" s="8" t="b">
+        <v>203</v>
+      </c>
+      <c r="H89" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3741,12 +4726,12 @@
         <v>3</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H90" s="8" t="b">
+        <v>203</v>
+      </c>
+      <c r="H90" s="12" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3759,26 +4744,26 @@
         <v>3</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H91" s="8" t="b">
+      <c r="H91" s="12" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3789,13 +4774,13 @@
         <v>4</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3806,13 +4791,13 @@
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3823,13 +4808,13 @@
         <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>165</v>
+        <v>236</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3840,13 +4825,13 @@
         <v>4</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>166</v>
+        <v>237</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3857,13 +4842,13 @@
         <v>4</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3874,13 +4859,13 @@
         <v>4</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>169</v>
+        <v>240</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3891,13 +4876,13 @@
         <v>4</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3908,13 +4893,13 @@
         <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>172</v>
+        <v>243</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3925,13 +4910,13 @@
         <v>4</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3942,13 +4927,13 @@
         <v>4</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3959,13 +4944,13 @@
         <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>176</v>
+        <v>247</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>173</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3976,13 +4961,13 @@
         <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>177</v>
+        <v>248</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3993,13 +4978,13 @@
         <v>4</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4010,13 +4995,13 @@
         <v>4</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>179</v>
+        <v>250</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4027,13 +5012,13 @@
         <v>4</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4044,13 +5029,13 @@
         <v>4</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>182</v>
+        <v>253</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4061,13 +5046,13 @@
         <v>4</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>183</v>
+        <v>254</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4078,13 +5063,13 @@
         <v>4</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4095,13 +5080,13 @@
         <v>4</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4112,13 +5097,13 @@
         <v>4</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>186</v>
+        <v>257</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4129,13 +5114,13 @@
         <v>4</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4146,10 +5131,10 @@
         <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>188</v>
+        <v>259</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>189</v>
+        <v>260</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4160,10 +5145,10 @@
         <v>4</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>190</v>
+        <v>259</v>
+      </c>
+      <c r="E114" s="14" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4174,10 +5159,10 @@
         <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E115" s="10" t="s">
-        <v>191</v>
+        <v>259</v>
+      </c>
+      <c r="E115" s="14" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4188,10 +5173,10 @@
         <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>192</v>
+        <v>259</v>
+      </c>
+      <c r="E116" s="14" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4202,10 +5187,10 @@
         <v>4</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>193</v>
+        <v>259</v>
+      </c>
+      <c r="E117" s="14" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4216,10 +5201,10 @@
         <v>4</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>195</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4230,10 +5215,10 @@
         <v>4</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>196</v>
+        <v>267</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4244,10 +5229,10 @@
         <v>4</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>197</v>
+        <v>268</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4265,17 +5250,17 @@
       <c r="B122" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C122" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>199</v>
+      <c r="C122" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4285,17 +5270,17 @@
       <c r="B123" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C123" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>199</v>
+      <c r="C123" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4305,17 +5290,17 @@
       <c r="B124" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>199</v>
+      <c r="C124" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4325,17 +5310,17 @@
       <c r="B125" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C125" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>199</v>
+      <c r="C125" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D125" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4345,17 +5330,17 @@
       <c r="B126" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>199</v>
+      <c r="C126" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4365,17 +5350,17 @@
       <c r="B127" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C127" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>199</v>
+      <c r="C127" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4385,17 +5370,17 @@
       <c r="B128" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C128" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>199</v>
+      <c r="C128" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4405,17 +5390,17 @@
       <c r="B129" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C129" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>199</v>
+      <c r="C129" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4425,17 +5410,17 @@
       <c r="B130" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C130" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>199</v>
+      <c r="C130" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4445,17 +5430,17 @@
       <c r="B131" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C131" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>199</v>
+      <c r="C131" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4465,17 +5450,17 @@
       <c r="B132" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>199</v>
+      <c r="C132" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4485,17 +5470,17 @@
       <c r="B133" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C133" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>199</v>
+      <c r="C133" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4505,17 +5490,17 @@
       <c r="B134" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C134" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>199</v>
+      <c r="C134" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4525,17 +5510,17 @@
       <c r="B135" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C135" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>199</v>
+      <c r="C135" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D135" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4545,17 +5530,17 @@
       <c r="B136" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>199</v>
+      <c r="C136" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4565,17 +5550,17 @@
       <c r="B137" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C137" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D137" s="6" t="s">
-        <v>199</v>
+      <c r="C137" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D137" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4585,17 +5570,17 @@
       <c r="B138" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C138" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>199</v>
+      <c r="C138" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4605,17 +5590,17 @@
       <c r="B139" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C139" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>199</v>
+      <c r="C139" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4625,17 +5610,17 @@
       <c r="B140" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>199</v>
+      <c r="C140" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D140" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4645,17 +5630,17 @@
       <c r="B141" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>199</v>
+      <c r="C141" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D141" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4665,11 +5650,11 @@
       <c r="B142" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>199</v>
+      <c r="C142" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>270</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>15</v>
@@ -4682,14 +5667,14 @@
       <c r="B143" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>202</v>
+      <c r="C143" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D143" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4699,14 +5684,14 @@
       <c r="B144" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>202</v>
+      <c r="C144" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4716,14 +5701,14 @@
       <c r="B145" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C145" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>202</v>
+      <c r="C145" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4733,14 +5718,14 @@
       <c r="B146" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C146" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>202</v>
+      <c r="C146" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D146" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4750,14 +5735,14 @@
       <c r="B147" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C147" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>202</v>
+      <c r="C147" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D147" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4767,14 +5752,14 @@
       <c r="B148" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="C148" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="G148" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="G148" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4784,14 +5769,14 @@
       <c r="B149" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C149" s="6" t="s">
+      <c r="C149" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D149" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="G149" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4801,14 +5786,14 @@
       <c r="B150" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C150" s="6" t="s">
+      <c r="C150" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="G150" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4818,7 +5803,7 @@
       <c r="B151" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D151" s="6"/>
+      <c r="D151" s="11"/>
     </row>
     <row r="152" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="n">
@@ -4835,17 +5820,17 @@
       <c r="B153" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C153" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>206</v>
+      <c r="C153" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D153" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>207</v>
+        <v>278</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4855,17 +5840,17 @@
       <c r="B154" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C154" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>206</v>
+      <c r="C154" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K154" s="7" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4875,17 +5860,17 @@
       <c r="B155" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C155" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>206</v>
+      <c r="C155" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K155" s="7" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4895,17 +5880,17 @@
       <c r="B156" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C156" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>206</v>
+      <c r="C156" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K156" s="7" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4915,17 +5900,17 @@
       <c r="B157" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C157" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>206</v>
+      <c r="C157" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K157" s="7" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4935,17 +5920,17 @@
       <c r="B158" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C158" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>206</v>
+      <c r="C158" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K158" s="7" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4955,17 +5940,17 @@
       <c r="B159" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C159" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>206</v>
+      <c r="C159" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K159" s="7" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4975,17 +5960,17 @@
       <c r="B160" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C160" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>206</v>
+      <c r="C160" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K160" s="7" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4995,17 +5980,17 @@
       <c r="B161" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C161" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>206</v>
+      <c r="C161" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5015,17 +6000,17 @@
       <c r="B162" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C162" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>206</v>
+      <c r="C162" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K162" s="7" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5035,17 +6020,17 @@
       <c r="B163" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>206</v>
+      <c r="C163" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5055,17 +6040,17 @@
       <c r="B164" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C164" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>206</v>
+      <c r="C164" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K164" s="7" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5075,17 +6060,17 @@
       <c r="B165" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C165" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D165" s="6" t="s">
-        <v>206</v>
+      <c r="C165" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K165" s="7" t="s">
-        <v>211</v>
+        <v>282</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5095,17 +6080,17 @@
       <c r="B166" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C166" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D166" s="6" t="s">
-        <v>206</v>
+      <c r="C166" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K166" s="7" t="s">
-        <v>211</v>
+        <v>282</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5115,17 +6100,17 @@
       <c r="B167" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>206</v>
+      <c r="C167" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K167" s="7" t="s">
-        <v>211</v>
+        <v>282</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5135,17 +6120,17 @@
       <c r="B168" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C168" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D168" s="6" t="s">
-        <v>206</v>
+      <c r="C168" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K168" s="7" t="s">
-        <v>211</v>
+        <v>282</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5155,17 +6140,17 @@
       <c r="B169" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C169" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D169" s="6" t="s">
-        <v>206</v>
+      <c r="C169" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K169" s="7" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5175,17 +6160,17 @@
       <c r="B170" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C170" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D170" s="6" t="s">
-        <v>206</v>
+      <c r="C170" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K170" s="7" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5195,17 +6180,17 @@
       <c r="B171" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C171" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>206</v>
+      <c r="C171" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K171" s="7" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5215,17 +6200,17 @@
       <c r="B172" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C172" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D172" s="6" t="s">
-        <v>206</v>
+      <c r="C172" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K172" s="7" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5235,17 +6220,17 @@
       <c r="B173" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C173" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D173" s="6" t="s">
-        <v>206</v>
+      <c r="C173" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>277</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K173" s="7" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5255,14 +6240,14 @@
       <c r="B174" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C174" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D174" s="6" t="s">
-        <v>214</v>
+      <c r="C174" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D174" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5272,14 +6257,14 @@
       <c r="B175" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C175" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>214</v>
+      <c r="C175" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D175" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,14 +6274,14 @@
       <c r="B176" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C176" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D176" s="6" t="s">
-        <v>214</v>
+      <c r="C176" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D176" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5306,14 +6291,14 @@
       <c r="B177" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C177" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D177" s="6" t="s">
-        <v>214</v>
+      <c r="C177" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D177" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5323,14 +6308,14 @@
       <c r="B178" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C178" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>214</v>
+      <c r="C178" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D178" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5340,14 +6325,14 @@
       <c r="B179" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C179" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D179" s="6" t="s">
-        <v>216</v>
+      <c r="C179" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D179" s="11" t="s">
+        <v>287</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5357,14 +6342,14 @@
       <c r="B180" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C180" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D180" s="11" t="s">
-        <v>216</v>
+      <c r="C180" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D180" s="15" t="s">
+        <v>287</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5374,14 +6359,14 @@
       <c r="B181" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C181" s="6" t="s">
-        <v>215</v>
+      <c r="C181" s="11" t="s">
+        <v>286</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>216</v>
+        <v>287</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5399,17 +6384,17 @@
       <c r="B183" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C183" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D183" s="6" t="s">
-        <v>218</v>
+      <c r="C183" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D183" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5419,17 +6404,17 @@
       <c r="B184" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C184" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>218</v>
+      <c r="C184" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D184" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K184" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5439,17 +6424,17 @@
       <c r="B185" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C185" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D185" s="6" t="s">
-        <v>218</v>
+      <c r="C185" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D185" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K185" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5459,17 +6444,17 @@
       <c r="B186" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C186" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D186" s="6" t="s">
-        <v>218</v>
+      <c r="C186" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D186" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K186" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5479,17 +6464,17 @@
       <c r="B187" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C187" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D187" s="6" t="s">
-        <v>218</v>
+      <c r="C187" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D187" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K187" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5499,17 +6484,17 @@
       <c r="B188" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C188" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>218</v>
+      <c r="C188" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K188" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5519,17 +6504,17 @@
       <c r="B189" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C189" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D189" s="6" t="s">
-        <v>218</v>
+      <c r="C189" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D189" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K189" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5539,17 +6524,17 @@
       <c r="B190" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C190" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>218</v>
+      <c r="C190" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D190" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5559,17 +6544,17 @@
       <c r="B191" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C191" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D191" s="6" t="s">
-        <v>218</v>
+      <c r="C191" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D191" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5579,17 +6564,17 @@
       <c r="B192" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C192" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D192" s="6" t="s">
-        <v>218</v>
+      <c r="C192" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D192" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K192" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5599,17 +6584,17 @@
       <c r="B193" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C193" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D193" s="6" t="s">
-        <v>218</v>
+      <c r="C193" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D193" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5619,17 +6604,17 @@
       <c r="B194" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C194" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D194" s="6" t="s">
-        <v>218</v>
+      <c r="C194" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D194" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5639,17 +6624,17 @@
       <c r="B195" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C195" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D195" s="6" t="s">
-        <v>218</v>
+      <c r="C195" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D195" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K195" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5659,17 +6644,17 @@
       <c r="B196" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C196" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D196" s="6" t="s">
-        <v>218</v>
+      <c r="C196" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D196" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5679,17 +6664,17 @@
       <c r="B197" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C197" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>218</v>
+      <c r="C197" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D197" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5699,17 +6684,17 @@
       <c r="B198" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C198" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D198" s="6" t="s">
-        <v>218</v>
+      <c r="C198" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D198" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5719,17 +6704,17 @@
       <c r="B199" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C199" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D199" s="6" t="s">
-        <v>218</v>
+      <c r="C199" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D199" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5739,17 +6724,17 @@
       <c r="B200" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C200" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D200" s="6" t="s">
-        <v>218</v>
+      <c r="C200" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D200" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5759,17 +6744,17 @@
       <c r="B201" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C201" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>218</v>
+      <c r="C201" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D201" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5779,17 +6764,17 @@
       <c r="B202" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C202" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D202" s="6" t="s">
-        <v>218</v>
+      <c r="C202" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D202" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5799,17 +6784,17 @@
       <c r="B203" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C203" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="D203" s="6" t="s">
-        <v>218</v>
+      <c r="C203" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D203" s="11" t="s">
+        <v>289</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5819,14 +6804,14 @@
       <c r="B204" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C204" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D204" s="6" t="s">
-        <v>221</v>
+      <c r="C204" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D204" s="11" t="s">
+        <v>292</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5836,14 +6821,14 @@
       <c r="B205" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C205" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D205" s="6" t="s">
-        <v>221</v>
+      <c r="C205" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D205" s="11" t="s">
+        <v>292</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5853,14 +6838,14 @@
       <c r="B206" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C206" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D206" s="6" t="s">
-        <v>221</v>
+      <c r="C206" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D206" s="11" t="s">
+        <v>292</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5870,14 +6855,14 @@
       <c r="B207" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C207" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D207" s="6" t="s">
-        <v>221</v>
+      <c r="C207" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D207" s="11" t="s">
+        <v>292</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5887,14 +6872,14 @@
       <c r="B208" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C208" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>221</v>
+      <c r="C208" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D208" s="11" t="s">
+        <v>292</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5904,14 +6889,14 @@
       <c r="B209" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C209" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D209" s="6" t="s">
-        <v>223</v>
+      <c r="C209" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="D209" s="11" t="s">
+        <v>294</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5921,14 +6906,14 @@
       <c r="B210" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C210" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D210" s="6" t="s">
-        <v>223</v>
+      <c r="C210" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="D210" s="11" t="s">
+        <v>294</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5938,14 +6923,14 @@
       <c r="B211" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C211" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D211" s="6" t="s">
-        <v>223</v>
+      <c r="C211" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="D211" s="11" t="s">
+        <v>294</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5971,17 +6956,17 @@
       <c r="B214" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C214" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D214" s="6" t="s">
-        <v>183</v>
+      <c r="C214" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D214" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G214" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5991,17 +6976,17 @@
       <c r="B215" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C215" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D215" s="6" t="s">
-        <v>183</v>
+      <c r="C215" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D215" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6011,17 +6996,17 @@
       <c r="B216" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C216" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D216" s="6" t="s">
-        <v>183</v>
+      <c r="C216" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D216" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6031,17 +7016,17 @@
       <c r="B217" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C217" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D217" s="6" t="s">
-        <v>183</v>
+      <c r="C217" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D217" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6051,17 +7036,17 @@
       <c r="B218" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C218" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D218" s="6" t="s">
-        <v>183</v>
+      <c r="C218" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D218" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K218" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6071,17 +7056,17 @@
       <c r="B219" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C219" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D219" s="6" t="s">
-        <v>183</v>
+      <c r="C219" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D219" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6091,17 +7076,17 @@
       <c r="B220" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C220" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D220" s="6" t="s">
-        <v>183</v>
+      <c r="C220" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D220" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K220" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6111,17 +7096,17 @@
       <c r="B221" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C221" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D221" s="6" t="s">
-        <v>183</v>
+      <c r="C221" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D221" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6131,17 +7116,17 @@
       <c r="B222" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C222" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D222" s="6" t="s">
-        <v>183</v>
+      <c r="C222" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D222" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K222" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6151,17 +7136,17 @@
       <c r="B223" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C223" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D223" s="6" t="s">
-        <v>183</v>
+      <c r="C223" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D223" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6171,17 +7156,17 @@
       <c r="B224" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C224" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D224" s="6" t="s">
-        <v>183</v>
+      <c r="C224" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D224" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6191,17 +7176,17 @@
       <c r="B225" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C225" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D225" s="6" t="s">
-        <v>183</v>
+      <c r="C225" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D225" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6211,17 +7196,17 @@
       <c r="B226" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C226" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D226" s="6" t="s">
-        <v>183</v>
+      <c r="C226" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D226" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K226" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6231,17 +7216,17 @@
       <c r="B227" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C227" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D227" s="6" t="s">
-        <v>183</v>
+      <c r="C227" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D227" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6251,17 +7236,17 @@
       <c r="B228" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C228" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>183</v>
+      <c r="C228" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D228" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6271,17 +7256,17 @@
       <c r="B229" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C229" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D229" s="6" t="s">
-        <v>183</v>
+      <c r="C229" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D229" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K229" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6291,17 +7276,17 @@
       <c r="B230" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C230" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D230" s="6" t="s">
-        <v>183</v>
+      <c r="C230" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D230" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K230" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6311,17 +7296,17 @@
       <c r="B231" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C231" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D231" s="6" t="s">
-        <v>183</v>
+      <c r="C231" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D231" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K231" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6331,17 +7316,17 @@
       <c r="B232" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C232" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D232" s="6" t="s">
-        <v>183</v>
+      <c r="C232" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D232" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K232" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6351,17 +7336,17 @@
       <c r="B233" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C233" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D233" s="6" t="s">
-        <v>183</v>
+      <c r="C233" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D233" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6371,17 +7356,17 @@
       <c r="B234" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C234" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D234" s="6" t="s">
-        <v>183</v>
+      <c r="C234" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="D234" s="11" t="s">
+        <v>254</v>
       </c>
       <c r="G234" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6391,14 +7376,14 @@
       <c r="B235" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C235" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D235" s="6" t="s">
-        <v>227</v>
+      <c r="C235" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D235" s="11" t="s">
+        <v>298</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6408,14 +7393,14 @@
       <c r="B236" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C236" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D236" s="6" t="s">
-        <v>227</v>
+      <c r="C236" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D236" s="11" t="s">
+        <v>298</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6425,14 +7410,14 @@
       <c r="B237" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C237" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D237" s="6" t="s">
-        <v>227</v>
+      <c r="C237" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D237" s="11" t="s">
+        <v>298</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6442,14 +7427,14 @@
       <c r="B238" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C238" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D238" s="6" t="s">
-        <v>227</v>
+      <c r="C238" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D238" s="11" t="s">
+        <v>298</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6459,14 +7444,14 @@
       <c r="B239" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C239" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="D239" s="6" t="s">
-        <v>227</v>
+      <c r="C239" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D239" s="11" t="s">
+        <v>298</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6476,14 +7461,14 @@
       <c r="B240" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C240" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D240" s="6" t="s">
-        <v>229</v>
+      <c r="C240" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="D240" s="11" t="s">
+        <v>300</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6493,14 +7478,14 @@
       <c r="B241" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C241" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D241" s="6" t="s">
-        <v>229</v>
+      <c r="C241" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="D241" s="11" t="s">
+        <v>300</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6510,14 +7495,14 @@
       <c r="B242" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C242" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D242" s="6" t="s">
-        <v>229</v>
+      <c r="C242" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="D242" s="11" t="s">
+        <v>300</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6543,17 +7528,17 @@
       <c r="B245" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C245" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D245" s="6" t="s">
-        <v>231</v>
+      <c r="C245" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D245" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K245" s="1" t="s">
-        <v>232</v>
+        <v>303</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6563,17 +7548,17 @@
       <c r="B246" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C246" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D246" s="6" t="s">
-        <v>231</v>
+      <c r="C246" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D246" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K246" s="1" t="s">
-        <v>232</v>
+        <v>303</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6583,17 +7568,17 @@
       <c r="B247" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C247" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D247" s="6" t="s">
-        <v>231</v>
+      <c r="C247" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D247" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>232</v>
+        <v>303</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6603,17 +7588,17 @@
       <c r="B248" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C248" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D248" s="6" t="s">
-        <v>231</v>
+      <c r="C248" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D248" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>233</v>
+        <v>304</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6623,17 +7608,17 @@
       <c r="B249" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C249" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D249" s="6" t="s">
-        <v>231</v>
+      <c r="C249" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D249" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>233</v>
+        <v>304</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6643,17 +7628,17 @@
       <c r="B250" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C250" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D250" s="6" t="s">
-        <v>231</v>
+      <c r="C250" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D250" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K250" s="1" t="s">
-        <v>233</v>
+        <v>304</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6663,17 +7648,17 @@
       <c r="B251" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C251" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D251" s="6" t="s">
-        <v>231</v>
+      <c r="C251" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D251" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G251" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K251" s="1" t="s">
-        <v>234</v>
+        <v>305</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6683,17 +7668,17 @@
       <c r="B252" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C252" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D252" s="6" t="s">
-        <v>231</v>
+      <c r="C252" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D252" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G252" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>234</v>
+        <v>305</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6703,17 +7688,17 @@
       <c r="B253" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C253" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D253" s="6" t="s">
-        <v>231</v>
+      <c r="C253" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D253" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K253" s="1" t="s">
-        <v>234</v>
+        <v>305</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6723,17 +7708,17 @@
       <c r="B254" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C254" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D254" s="6" t="s">
-        <v>231</v>
+      <c r="C254" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D254" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G254" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K254" s="1" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6743,17 +7728,17 @@
       <c r="B255" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C255" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D255" s="6" t="s">
-        <v>231</v>
+      <c r="C255" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D255" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K255" s="1" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6763,17 +7748,17 @@
       <c r="B256" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C256" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D256" s="6" t="s">
-        <v>231</v>
+      <c r="C256" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D256" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G256" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K256" s="1" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6783,17 +7768,17 @@
       <c r="B257" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C257" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D257" s="6" t="s">
-        <v>231</v>
+      <c r="C257" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D257" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>236</v>
+        <v>307</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6803,17 +7788,17 @@
       <c r="B258" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C258" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D258" s="6" t="s">
-        <v>231</v>
+      <c r="C258" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D258" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>236</v>
+        <v>307</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6823,17 +7808,17 @@
       <c r="B259" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C259" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D259" s="6" t="s">
-        <v>231</v>
+      <c r="C259" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D259" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G259" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K259" s="1" t="s">
-        <v>236</v>
+        <v>307</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6843,17 +7828,17 @@
       <c r="B260" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C260" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D260" s="6" t="s">
-        <v>231</v>
+      <c r="C260" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D260" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K260" s="1" t="s">
-        <v>237</v>
+        <v>308</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6863,17 +7848,17 @@
       <c r="B261" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C261" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D261" s="6" t="s">
-        <v>231</v>
+      <c r="C261" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D261" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G261" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>237</v>
+        <v>308</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6883,17 +7868,17 @@
       <c r="B262" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C262" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D262" s="6" t="s">
-        <v>231</v>
+      <c r="C262" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D262" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K262" s="1" t="s">
-        <v>237</v>
+        <v>308</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6903,17 +7888,17 @@
       <c r="B263" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C263" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D263" s="6" t="s">
-        <v>231</v>
+      <c r="C263" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D263" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K263" s="7" t="s">
-        <v>238</v>
+        <v>309</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6923,17 +7908,17 @@
       <c r="B264" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C264" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D264" s="6" t="s">
-        <v>231</v>
+      <c r="C264" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D264" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K264" s="7" t="s">
-        <v>238</v>
+        <v>309</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6943,17 +7928,17 @@
       <c r="B265" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C265" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D265" s="6" t="s">
-        <v>231</v>
+      <c r="C265" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D265" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G265" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K265" s="7" t="s">
-        <v>238</v>
+        <v>309</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6963,17 +7948,17 @@
       <c r="B266" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C266" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D266" s="6" t="s">
-        <v>231</v>
+      <c r="C266" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D266" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K266" s="7" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6983,17 +7968,17 @@
       <c r="B267" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C267" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D267" s="6" t="s">
-        <v>231</v>
+      <c r="C267" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="D267" s="11" t="s">
+        <v>302</v>
       </c>
       <c r="G267" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K267" s="7" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7003,17 +7988,17 @@
       <c r="B268" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C268" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D268" s="6" t="s">
-        <v>241</v>
+      <c r="C268" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="D268" s="11" t="s">
+        <v>312</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K268" s="7" t="s">
-        <v>242</v>
+        <v>313</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7023,17 +8008,17 @@
       <c r="B269" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C269" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D269" s="6" t="s">
-        <v>241</v>
+      <c r="C269" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="D269" s="11" t="s">
+        <v>312</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K269" s="7" t="s">
-        <v>242</v>
+        <v>313</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7043,14 +8028,14 @@
       <c r="B270" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C270" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D270" s="6" t="s">
-        <v>241</v>
+      <c r="C270" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="D270" s="11" t="s">
+        <v>312</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7060,14 +8045,14 @@
       <c r="B271" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C271" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D271" s="6" t="s">
-        <v>241</v>
+      <c r="C271" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="D271" s="11" t="s">
+        <v>312</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7077,14 +8062,14 @@
       <c r="B272" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C272" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D272" s="6" t="s">
-        <v>241</v>
+      <c r="C272" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="D272" s="11" t="s">
+        <v>312</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7094,14 +8079,14 @@
       <c r="B273" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C273" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D273" s="6" t="s">
-        <v>244</v>
+      <c r="C273" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="D273" s="11" t="s">
+        <v>315</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7111,7 +8096,7 @@
       <c r="B274" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D274" s="6"/>
+      <c r="D274" s="11"/>
     </row>
     <row r="275" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="n">
@@ -7120,17 +8105,17 @@
       <c r="B275" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C275" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D275" s="6" t="s">
-        <v>246</v>
+      <c r="C275" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D275" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K275" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7140,17 +8125,17 @@
       <c r="B276" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C276" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D276" s="6" t="s">
-        <v>246</v>
+      <c r="C276" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D276" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K276" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7160,17 +8145,17 @@
       <c r="B277" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C277" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D277" s="6" t="s">
-        <v>246</v>
+      <c r="C277" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D277" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K277" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7180,17 +8165,17 @@
       <c r="B278" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C278" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D278" s="6" t="s">
-        <v>246</v>
+      <c r="C278" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D278" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K278" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7200,17 +8185,17 @@
       <c r="B279" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C279" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D279" s="6" t="s">
-        <v>246</v>
+      <c r="C279" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D279" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K279" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7220,17 +8205,17 @@
       <c r="B280" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C280" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D280" s="6" t="s">
-        <v>246</v>
+      <c r="C280" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D280" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K280" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7240,17 +8225,17 @@
       <c r="B281" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C281" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D281" s="6" t="s">
-        <v>246</v>
+      <c r="C281" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D281" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K281" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7260,17 +8245,17 @@
       <c r="B282" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C282" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D282" s="6" t="s">
-        <v>246</v>
+      <c r="C282" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D282" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K282" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7280,17 +8265,17 @@
       <c r="B283" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C283" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D283" s="6" t="s">
-        <v>246</v>
+      <c r="C283" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D283" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K283" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7300,17 +8285,17 @@
       <c r="B284" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C284" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D284" s="6" t="s">
-        <v>246</v>
+      <c r="C284" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D284" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K284" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7320,17 +8305,17 @@
       <c r="B285" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C285" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D285" s="6" t="s">
-        <v>246</v>
+      <c r="C285" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D285" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K285" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7340,17 +8325,17 @@
       <c r="B286" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C286" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D286" s="6" t="s">
-        <v>246</v>
+      <c r="C286" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D286" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K286" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7360,17 +8345,17 @@
       <c r="B287" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C287" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D287" s="6" t="s">
-        <v>246</v>
+      <c r="C287" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D287" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K287" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7380,17 +8365,17 @@
       <c r="B288" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C288" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D288" s="6" t="s">
-        <v>246</v>
+      <c r="C288" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D288" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K288" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7400,17 +8385,17 @@
       <c r="B289" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C289" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D289" s="6" t="s">
-        <v>246</v>
+      <c r="C289" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D289" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K289" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7420,17 +8405,17 @@
       <c r="B290" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C290" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D290" s="6" t="s">
-        <v>246</v>
+      <c r="C290" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D290" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K290" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7440,17 +8425,17 @@
       <c r="B291" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C291" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D291" s="6" t="s">
-        <v>246</v>
+      <c r="C291" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D291" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7460,17 +8445,17 @@
       <c r="B292" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C292" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D292" s="6" t="s">
-        <v>246</v>
+      <c r="C292" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D292" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K292" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7480,17 +8465,17 @@
       <c r="B293" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C293" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D293" s="6" t="s">
-        <v>246</v>
+      <c r="C293" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D293" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K293" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7500,17 +8485,17 @@
       <c r="B294" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C294" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D294" s="6" t="s">
-        <v>246</v>
+      <c r="C294" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D294" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K294" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7520,17 +8505,17 @@
       <c r="B295" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C295" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D295" s="6" t="s">
-        <v>246</v>
+      <c r="C295" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="D295" s="11" t="s">
+        <v>317</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7540,17 +8525,17 @@
       <c r="B296" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C296" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D296" s="6" t="s">
-        <v>249</v>
+      <c r="C296" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D296" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K296" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7560,17 +8545,17 @@
       <c r="B297" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C297" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D297" s="6" t="s">
-        <v>249</v>
+      <c r="C297" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D297" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K297" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7580,17 +8565,17 @@
       <c r="B298" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C298" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D298" s="6" t="s">
-        <v>249</v>
+      <c r="C298" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D298" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K298" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7600,17 +8585,17 @@
       <c r="B299" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C299" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D299" s="6" t="s">
-        <v>249</v>
+      <c r="C299" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D299" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K299" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7620,17 +8605,17 @@
       <c r="B300" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C300" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="D300" s="6" t="s">
-        <v>249</v>
+      <c r="C300" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D300" s="11" t="s">
+        <v>320</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K300" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7640,17 +8625,17 @@
       <c r="B301" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C301" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D301" s="6" t="s">
-        <v>251</v>
+      <c r="C301" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D301" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="K301" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7660,14 +8645,14 @@
       <c r="B302" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C302" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D302" s="6" t="s">
-        <v>251</v>
+      <c r="C302" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D302" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7677,14 +8662,14 @@
       <c r="B303" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C303" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D303" s="6" t="s">
-        <v>251</v>
+      <c r="C303" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D303" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7710,17 +8695,17 @@
       <c r="B306" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C306" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D306" s="6" t="s">
-        <v>253</v>
+      <c r="C306" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D306" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K306" s="1" t="s">
-        <v>254</v>
+        <v>325</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7730,17 +8715,17 @@
       <c r="B307" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C307" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D307" s="6" t="s">
-        <v>253</v>
+      <c r="C307" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D307" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K307" s="1" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7750,17 +8735,17 @@
       <c r="B308" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C308" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D308" s="6" t="s">
-        <v>253</v>
+      <c r="C308" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D308" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K308" s="1" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7770,17 +8755,17 @@
       <c r="B309" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C309" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D309" s="6" t="s">
-        <v>253</v>
+      <c r="C309" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D309" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K309" s="1" t="s">
-        <v>257</v>
+        <v>328</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7790,17 +8775,17 @@
       <c r="B310" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C310" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D310" s="6" t="s">
-        <v>253</v>
+      <c r="C310" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D310" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K310" s="1" t="s">
-        <v>258</v>
+        <v>329</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7810,17 +8795,17 @@
       <c r="B311" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C311" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D311" s="6" t="s">
-        <v>253</v>
+      <c r="C311" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D311" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K311" s="1" t="s">
-        <v>259</v>
+        <v>330</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7830,17 +8815,17 @@
       <c r="B312" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C312" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D312" s="6" t="s">
-        <v>253</v>
+      <c r="C312" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D312" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7850,17 +8835,17 @@
       <c r="B313" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C313" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D313" s="6" t="s">
-        <v>253</v>
+      <c r="C313" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D313" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K313" s="1" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7870,17 +8855,17 @@
       <c r="B314" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C314" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D314" s="6" t="s">
-        <v>253</v>
+      <c r="C314" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D314" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K314" s="1" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7890,17 +8875,17 @@
       <c r="B315" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C315" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D315" s="6" t="s">
-        <v>253</v>
+      <c r="C315" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D315" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K315" s="1" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7910,17 +8895,17 @@
       <c r="B316" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C316" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D316" s="6" t="s">
-        <v>253</v>
+      <c r="C316" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D316" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K316" s="1" t="s">
-        <v>257</v>
+        <v>328</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7930,17 +8915,17 @@
       <c r="B317" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C317" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D317" s="6" t="s">
-        <v>253</v>
+      <c r="C317" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D317" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K317" s="1" t="s">
-        <v>258</v>
+        <v>329</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7950,17 +8935,17 @@
       <c r="B318" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C318" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D318" s="6" t="s">
-        <v>253</v>
+      <c r="C318" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D318" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K318" s="1" t="s">
-        <v>259</v>
+        <v>330</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7970,17 +8955,17 @@
       <c r="B319" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C319" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D319" s="6" t="s">
-        <v>253</v>
+      <c r="C319" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D319" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K319" s="1" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7990,17 +8975,17 @@
       <c r="B320" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C320" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D320" s="6" t="s">
-        <v>253</v>
+      <c r="C320" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D320" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K320" s="1" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8010,17 +8995,17 @@
       <c r="B321" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C321" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D321" s="6" t="s">
-        <v>253</v>
+      <c r="C321" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D321" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K321" s="1" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8030,17 +9015,17 @@
       <c r="B322" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C322" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D322" s="6" t="s">
-        <v>253</v>
+      <c r="C322" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D322" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K322" s="1" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8050,17 +9035,17 @@
       <c r="B323" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C323" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D323" s="6" t="s">
-        <v>253</v>
+      <c r="C323" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D323" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K323" s="1" t="s">
-        <v>257</v>
+        <v>328</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8070,17 +9055,17 @@
       <c r="B324" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C324" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D324" s="6" t="s">
-        <v>253</v>
+      <c r="C324" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D324" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K324" s="1" t="s">
-        <v>258</v>
+        <v>329</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8090,17 +9075,17 @@
       <c r="B325" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C325" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D325" s="6" t="s">
-        <v>253</v>
+      <c r="C325" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D325" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K325" s="1" t="s">
-        <v>259</v>
+        <v>330</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8110,17 +9095,17 @@
       <c r="B326" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C326" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D326" s="6" t="s">
-        <v>253</v>
+      <c r="C326" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="D326" s="11" t="s">
+        <v>324</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K326" s="1" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8130,17 +9115,17 @@
       <c r="B327" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C327" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D327" s="6" t="s">
-        <v>263</v>
+      <c r="C327" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D327" s="11" t="s">
+        <v>334</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K327" s="1" t="s">
-        <v>261</v>
+        <v>332</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8150,17 +9135,17 @@
       <c r="B328" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C328" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D328" s="6" t="s">
-        <v>263</v>
+      <c r="C328" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D328" s="11" t="s">
+        <v>334</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K328" s="1" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8170,17 +9155,17 @@
       <c r="B329" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C329" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D329" s="6" t="s">
-        <v>263</v>
+      <c r="C329" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D329" s="11" t="s">
+        <v>334</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K329" s="1" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8190,17 +9175,17 @@
       <c r="B330" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C330" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D330" s="6" t="s">
-        <v>263</v>
+      <c r="C330" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D330" s="11" t="s">
+        <v>334</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K330" s="1" t="s">
-        <v>257</v>
+        <v>328</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8210,17 +9195,17 @@
       <c r="B331" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C331" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D331" s="6" t="s">
-        <v>263</v>
+      <c r="C331" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D331" s="11" t="s">
+        <v>334</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="K331" s="1" t="s">
-        <v>258</v>
+        <v>329</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8230,17 +9215,17 @@
       <c r="B332" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C332" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D332" s="6" t="s">
-        <v>265</v>
+      <c r="C332" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="D332" s="11" t="s">
+        <v>336</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="K332" s="1" t="s">
-        <v>259</v>
+        <v>330</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8250,17 +9235,17 @@
       <c r="B333" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C333" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D333" s="6" t="s">
-        <v>265</v>
+      <c r="C333" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="D333" s="11" t="s">
+        <v>336</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="K333" s="1" t="s">
-        <v>260</v>
+        <v>331</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8270,14 +9255,14 @@
       <c r="B334" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C334" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D334" s="6" t="s">
-        <v>265</v>
+      <c r="C334" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="D334" s="11" t="s">
+        <v>336</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8287,7 +9272,7 @@
       <c r="B335" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D335" s="6"/>
+      <c r="D335" s="11"/>
     </row>
     <row r="336" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="1" t="n">
@@ -8296,17 +9281,17 @@
       <c r="B336" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C336" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D336" s="6" t="s">
-        <v>267</v>
+      <c r="C336" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D336" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K336" s="1" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8316,17 +9301,17 @@
       <c r="B337" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C337" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D337" s="6" t="s">
-        <v>267</v>
+      <c r="C337" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D337" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K337" s="1" t="s">
-        <v>269</v>
+        <v>340</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8336,17 +9321,17 @@
       <c r="B338" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C338" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D338" s="6" t="s">
-        <v>267</v>
+      <c r="C338" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D338" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K338" s="1" t="s">
-        <v>269</v>
+        <v>340</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8356,17 +9341,17 @@
       <c r="B339" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C339" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D339" s="6" t="s">
-        <v>267</v>
+      <c r="C339" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D339" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K339" s="1" t="s">
-        <v>269</v>
+        <v>340</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8376,17 +9361,17 @@
       <c r="B340" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C340" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D340" s="6" t="s">
-        <v>267</v>
+      <c r="C340" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D340" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K340" s="1" t="s">
-        <v>270</v>
+        <v>341</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8396,17 +9381,17 @@
       <c r="B341" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C341" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D341" s="6" t="s">
-        <v>267</v>
+      <c r="C341" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D341" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K341" s="1" t="s">
-        <v>270</v>
+        <v>341</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8416,17 +9401,17 @@
       <c r="B342" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C342" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D342" s="6" t="s">
-        <v>267</v>
+      <c r="C342" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D342" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K342" s="1" t="s">
-        <v>270</v>
+        <v>341</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8436,17 +9421,17 @@
       <c r="B343" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C343" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D343" s="6" t="s">
-        <v>267</v>
+      <c r="C343" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D343" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K343" s="1" t="s">
-        <v>270</v>
+        <v>341</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8456,17 +9441,17 @@
       <c r="B344" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C344" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D344" s="6" t="s">
-        <v>267</v>
+      <c r="C344" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D344" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G344" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K344" s="1" t="s">
-        <v>271</v>
+        <v>342</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8476,17 +9461,17 @@
       <c r="B345" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C345" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D345" s="6" t="s">
-        <v>267</v>
+      <c r="C345" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D345" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G345" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K345" s="1" t="s">
-        <v>271</v>
+        <v>342</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8496,17 +9481,17 @@
       <c r="B346" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C346" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D346" s="6" t="s">
-        <v>267</v>
+      <c r="C346" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D346" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G346" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K346" s="1" t="s">
-        <v>271</v>
+        <v>342</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8516,17 +9501,17 @@
       <c r="B347" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C347" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D347" s="6" t="s">
-        <v>267</v>
+      <c r="C347" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D347" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K347" s="1" t="s">
-        <v>271</v>
+        <v>342</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8536,17 +9521,17 @@
       <c r="B348" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C348" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D348" s="6" t="s">
-        <v>267</v>
+      <c r="C348" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D348" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K348" s="1" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8556,17 +9541,17 @@
       <c r="B349" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C349" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D349" s="6" t="s">
-        <v>267</v>
+      <c r="C349" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D349" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K349" s="1" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8576,17 +9561,17 @@
       <c r="B350" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C350" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D350" s="6" t="s">
-        <v>267</v>
+      <c r="C350" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D350" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K350" s="1" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
     </row>
     <row r="351" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8596,17 +9581,17 @@
       <c r="B351" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C351" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D351" s="6" t="s">
-        <v>267</v>
+      <c r="C351" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D351" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K351" s="1" t="s">
-        <v>272</v>
+        <v>343</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8616,17 +9601,17 @@
       <c r="B352" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C352" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D352" s="6" t="s">
-        <v>267</v>
+      <c r="C352" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D352" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K352" s="1" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8636,17 +9621,17 @@
       <c r="B353" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C353" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D353" s="6" t="s">
-        <v>267</v>
+      <c r="C353" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D353" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K353" s="1" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8656,17 +9641,17 @@
       <c r="B354" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C354" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D354" s="6" t="s">
-        <v>267</v>
+      <c r="C354" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D354" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K354" s="1" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8676,11 +9661,11 @@
       <c r="B355" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C355" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D355" s="6" t="s">
-        <v>267</v>
+      <c r="C355" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D355" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>15</v>
@@ -8693,11 +9678,11 @@
       <c r="B356" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C356" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D356" s="6" t="s">
-        <v>267</v>
+      <c r="C356" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D356" s="11" t="s">
+        <v>338</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>15</v>
@@ -8710,14 +9695,14 @@
       <c r="B357" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C357" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D357" s="6" t="s">
-        <v>275</v>
+      <c r="C357" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D357" s="11" t="s">
+        <v>346</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8727,14 +9712,14 @@
       <c r="B358" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C358" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D358" s="6" t="s">
-        <v>275</v>
+      <c r="C358" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D358" s="11" t="s">
+        <v>346</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8744,14 +9729,14 @@
       <c r="B359" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C359" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D359" s="6" t="s">
-        <v>275</v>
+      <c r="C359" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D359" s="11" t="s">
+        <v>346</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8761,14 +9746,14 @@
       <c r="B360" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C360" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D360" s="6" t="s">
-        <v>275</v>
+      <c r="C360" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D360" s="11" t="s">
+        <v>346</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8778,14 +9763,14 @@
       <c r="B361" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C361" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D361" s="6" t="s">
-        <v>275</v>
+      <c r="C361" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D361" s="11" t="s">
+        <v>346</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8795,14 +9780,14 @@
       <c r="B362" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C362" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D362" s="6" t="s">
-        <v>277</v>
+      <c r="C362" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D362" s="11" t="s">
+        <v>348</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8812,14 +9797,14 @@
       <c r="B363" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C363" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D363" s="6" t="s">
-        <v>277</v>
+      <c r="C363" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D363" s="11" t="s">
+        <v>348</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8829,14 +9814,14 @@
       <c r="B364" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C364" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D364" s="6" t="s">
-        <v>277</v>
+      <c r="C364" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D364" s="11" t="s">
+        <v>348</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
     </row>
     <row r="365" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8846,7 +9831,7 @@
       <c r="B365" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D365" s="6"/>
+      <c r="D365" s="11"/>
     </row>
     <row r="366" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="n">
@@ -8858,7 +9843,22 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" display="https://www.youtube.com/watch?v=zZZKL-H-MXs"/>
+    <hyperlink ref="F3" r:id="rId1" display="Article 18: Responsibility of Parents&#10;Parents are the main people responsible for bringing up a child. When the child does not have any parents, another adult will have this responsibility and they are called a “guardian”. Parents and guardians should always consider what is best for that child. Governments should help them. Where a child has both parents, both of them should be responsible for bringing up the child.&#10;Link: https://www.youtube.com/watch?v=zZZKL-H-MXs"/>
+    <hyperlink ref="F7" r:id="rId2" display="Article 19: Protection from Abuse&#10;Governments must protect children from violence, abuse and being neglected by anyone who looks after them.&#10;Link: https://www.youtube.com/watch?v=qxmwXGruiWY&#10;"/>
+    <hyperlink ref="F9" r:id="rId3" display="Article 32: Child Labour&#10;Children have the right to be protected from doing work that is dangerous or bad for their education, health or development. If children work, they have the right to be safe and paid fairly.&#10;Link: https://elibrary.judiciary.gov.ph/thebookshelf/showdocs/2/1388 "/>
+    <hyperlink ref="F14" r:id="rId4" location="what-is-psa-birth-certificate" display="Article 7: Name and State Membership&#10;Children must be registered when they are born and given a name which is officially recognized by the government. Children must have a nationality (belong to a country). Whenever possible, children should know their parents and be looked after by them.&#10;Link: https://psahelpline.ph/psa-birth-certificate#what-is-psa-birth-certificate "/>
+    <hyperlink ref="F33" r:id="rId5" display="Read: Health Benefits of Malunggay: The Miracle Tree"/>
+    <hyperlink ref="F34" r:id="rId6" display="Read: Why Eggs Are the Best Protein for Kids"/>
+    <hyperlink ref="F35" r:id="rId7" display="Read: Bananas 101: Nutrition Facts and Health Benefits"/>
+    <hyperlink ref="F37" r:id="rId8" display="Read: Sweet Potatoes vs. White Potatoes: Which is Healthier?&#10;"/>
+    <hyperlink ref="F38" r:id="rId9" display="Read: Taro Root: Benefits and Nutritional Facts"/>
+    <hyperlink ref="F39" r:id="rId10" display="Read: Chayote (Sayote) Nutrition: Fiber, Folate, and More"/>
+    <hyperlink ref="F41" r:id="rId11" display="Read: Fiber and Teeth: Why Apples are Good for Gums"/>
+    <hyperlink ref="F44" r:id="rId12" display="Read: The Role of Zinc in Child Growth"/>
+    <hyperlink ref="F47" r:id="rId13" display="Read: Fortifying Instant Noodles with Moringa"/>
+    <hyperlink ref="F48" r:id="rId14" display=" Lycopene in Cooked Tomatoes: Why it's Healthier"/>
+    <hyperlink ref="F49" r:id="rId15" display=" The Immune-Boosting Benefits of Citrus"/>
+    <hyperlink ref="F51" r:id="rId16" display=" Homemade Vegetable Chips: Nutritional Tips"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
